--- a/naver-place-crawler/results_health/분당_PT.xlsx
+++ b/naver-place-crawler/results_health/분당_PT.xlsx
@@ -417,16 +417,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V21"/>
+  <dimension ref="A1:V13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="31" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="49" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -559,49 +559,49 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>스포츠,오락</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>크레이지핏 PT</t>
+          <t>구스짐 PT 판교점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>krazyfit@naver.com</t>
+          <t>chlgudrn1@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1488-5883</t>
+          <t>0507-1465-9683</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 정자일로198번길 6-5 3층 크레이지핏</t>
+          <t>경기도 성남시 분당구 판교로 374 스타식스코아2 3층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://m.booking.naver.com/booking/13/bizes/205740?theme=place&amp;entry=pll&amp;lang=ko&amp;area=pll</t>
+          <t>https://www.instagram.com/9s_gym_pangyo/</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -612,7 +612,7 @@
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>526</v>
+        <v>161</v>
       </c>
       <c r="Q2" t="n">
-        <v>1638</v>
+        <v>143</v>
       </c>
       <c r="R2" t="n">
-        <v>2164</v>
+        <v>304</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,51 +636,51 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1628554288</t>
+          <t>1088776551</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1628554288</t>
+          <t>https://m.place.naver.com/place/1088776551</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>스포츠,오락</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>베러댄 휘트니스 분당야탑점</t>
+          <t>자마이카피트니스 분당정자점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>56zqrwcwsv@naver.com</t>
+          <t>jamaica_jeongja@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1438-9698</t>
+          <t>0507-1383-8533</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 야탑로75번길 15 세화빌딩 4층</t>
+          <t>경기도 성남시 분당구 정자일로 121 지하 1층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/56zqrwcwsv</t>
+          <t>https://www.instagram.com/jamaica_bundang?igsh=MWY4cGIybjlodW11bw%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>382</v>
+        <v>1825</v>
       </c>
       <c r="Q3" t="n">
-        <v>2033</v>
+        <v>223</v>
       </c>
       <c r="R3" t="n">
-        <v>2415</v>
+        <v>2048</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,51 +730,51 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1013682807</t>
+          <t>1710539074</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1013682807</t>
+          <t>https://m.place.naver.com/place/1710539074</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>스포츠,오락</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>와이투짐 야탑역점</t>
+          <t>레조나헬스랩PT 서판교점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>y2gym2@naver.com</t>
+          <t>resonar_healthlab@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1352-8844</t>
+          <t>0507-1411-1104</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로 912 B1층</t>
+          <t>경기도 성남시 분당구 판교공원로2길 9 4층 레조나헬스랩PT 서판교점</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/y2gym2</t>
+          <t>https://blog.naver.com/resonar_healthlab</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -800,7 +800,7 @@
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -809,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>376</v>
+        <v>56</v>
       </c>
       <c r="Q4" t="n">
-        <v>1518</v>
+        <v>202</v>
       </c>
       <c r="R4" t="n">
-        <v>1894</v>
+        <v>258</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,56 +824,56 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1930702763</t>
+          <t>1644348689</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1930702763</t>
+          <t>https://m.place.naver.com/place/1644348689</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>스포츠,오락</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>쓰리핏PT 분당정자점</t>
+          <t>익스홀릭 가넷 미금점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3fits@naver.com</t>
+          <t>dydwk147@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1409-3559</t>
+          <t>0507-1429-2557</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 내정로113번길 4 2층 202호, 203-1호</t>
+          <t>경기도 성남시 분당구 돌마로 87 골드프라자 6층 가넷휘트니스</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://3fitpt.com</t>
+          <t>https://blog.naver.com/dydwk147</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -894,7 +894,7 @@
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -903,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>355</v>
+        <v>561</v>
       </c>
       <c r="Q5" t="n">
-        <v>797</v>
+        <v>1070</v>
       </c>
       <c r="R5" t="n">
-        <v>1152</v>
+        <v>1631</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,56 +918,60 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1845673431</t>
+          <t>12763227</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1845673431</t>
+          <t>https://m.place.naver.com/place/12763227</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>스포츠,오락</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>헬스보이짐 헬스 PT 판교역점</t>
+          <t>버핏그라운드 PT 판교</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>healthboygym78@naver.com</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>butfitground@naver.com</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>butfitseoul@butfitseoul.com</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1402-1275</t>
+          <t>0507-1417-1133</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 대왕판교로606번길 58 지하1층</t>
+          <t>경기도 성남시 분당구 판교역로 136 B3007호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/healthboygym78/223380215625</t>
+          <t>https://www.butfitground.com/4steppt</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -988,7 +992,7 @@
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -997,13 +1001,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2525</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2844</v>
+        <v>0</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,56 +1016,56 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1835201778</t>
+          <t>2029680813</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1835201778</t>
+          <t>https://m.place.naver.com/place/2029680813</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>스포츠,오락</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>쓰리핏 헬스&amp;PT 서현점</t>
+          <t>헬스보이짐 헬스 PT 판교역점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3fits@naver.com</t>
+          <t>healthboygym78@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1388-2211</t>
+          <t>0507-1402-1275</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 불정로 379 서현프라자 지하1층</t>
+          <t>경기도 성남시 분당구 대왕판교로606번길 58 지하1층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://3fitpt.com</t>
+          <t>https://blog.naver.com/healthboygym78/223380215625</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1082,7 +1086,7 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1091,13 +1095,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1028</v>
+        <v>2535</v>
       </c>
       <c r="Q7" t="n">
-        <v>924</v>
+        <v>322</v>
       </c>
       <c r="R7" t="n">
-        <v>1952</v>
+        <v>2857</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,51 +1110,35 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1181952796</t>
+          <t>1835201778</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1181952796</t>
+          <t>https://m.place.naver.com/place/1835201778</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>스포츠,오락</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>헬스보이짐&amp;필라걸 수내점</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>healthboy40@naver.com</t>
-        </is>
-      </c>
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0507-1380-2239</t>
-        </is>
-      </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 내정로173번길 49 5층</t>
+          <t>주소</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/healthboy40/223688037867</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1160,12 +1148,12 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1181,17 +1169,17 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>969</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>728</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1697</v>
+        <v>0</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1200,51 +1188,35 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1973151166</t>
+          <t>7544685</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1973151166</t>
+          <t>https://m.place.naver.com/place/7544685</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>스포츠,오락</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>험블 휘트니스 PT</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>humblefitness@naver.com</t>
-        </is>
-      </c>
+      <c r="A9" t="inlineStr"/>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>031-697-8768</t>
-        </is>
-      </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로331번길 3-3 701호</t>
+          <t>주소</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/humblefitness</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1254,12 +1226,12 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1275,17 +1247,17 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>137</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1422</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1559</v>
+        <v>0</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1294,51 +1266,35 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1134171602</t>
+          <t>2600001</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1134171602</t>
+          <t>https://m.place.naver.com/place/2600001</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>스포츠,오락</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>브레이브 휘트니스 분당정자점</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>bravefitness_jeongja@naver.com</t>
-        </is>
-      </c>
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0507-1484-0779</t>
-        </is>
-      </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 내정로17번길 2 지하1층</t>
+          <t>주소</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bravefitness_jeongja</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1348,12 +1304,12 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1369,17 +1325,17 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1414</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>893</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2307</v>
+        <v>0</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1388,51 +1344,35 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1043618213</t>
+          <t>7167332</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1043618213</t>
+          <t>https://m.place.naver.com/place/7167332</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>스포츠,오락</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>비율라이프 바디코치 여성전용 체형필라테스 PT 야탑점</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>rockrock1256@naver.com</t>
-        </is>
-      </c>
+      <c r="A11" t="inlineStr"/>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0507-1445-2430</t>
-        </is>
-      </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 야탑로69번길 8 2층 바디코치 야탑점</t>
+          <t>주소</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://myip.kr/GGbCY</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1442,7 +1382,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1463,17 +1403,17 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>203</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>785</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>988</v>
+        <v>0</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1482,66 +1422,50 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1723811790</t>
+          <t>7536599</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1723811790</t>
+          <t>https://m.place.naver.com/place/7536599</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>스포츠,오락</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>쓰리핏 PT 분당미금점</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>3fits@naver.com</t>
-        </is>
-      </c>
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0507-1302-3558</t>
-        </is>
-      </c>
+      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 돌마로 47 6층 607호</t>
+          <t>주소</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://3fitpt.com</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1552,22 +1476,22 @@
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>423</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>948</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1371</v>
+        <v>0</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1576,56 +1500,40 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1135214262</t>
+          <t>7540516</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1135214262</t>
+          <t>https://m.place.naver.com/place/7540516</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>스포츠,오락</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>리커브 피티 앤 본척척 재활 센터 야탑점</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>recurvept@naver.com</t>
-        </is>
-      </c>
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0507-1441-8303</t>
-        </is>
-      </c>
+      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로916번길 5 3층 302호</t>
+          <t>주소</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://m.booking.naver.com/booking/12/bizes/1590839</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1651,17 +1559,17 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>273</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>285</v>
+        <v>0</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1670,761 +1578,17 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2038767341</t>
+          <t>7181190</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2038767341</t>
+          <t>https://m.place.naver.com/place/7181190</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>스포츠,오락</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>바로선운동센터 판교점</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>coolksh11@naver.com</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>경기도 성남시 분당구 동판교로 61 2층 201호</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/coolksh11</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P14" t="n">
-        <v>19</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>148</v>
-      </c>
-      <c r="R14" t="n">
-        <v>167</v>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>2015061102</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/2015061102</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>스포츠,오락</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>피트니스웰시 헬스&amp;PT 분당정자점</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>health-pt@naver.com</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>0507-1489-7037</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>경기도 성남시 분당구 성남대로343번길 12-8 1동 4층</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/health-pt</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P15" t="n">
-        <v>525</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>485</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1010</v>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>1623406875</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1623406875</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>스포츠,오락</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>와이짐 PT 분당미금점</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>ygym3018@naver.com</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>0507-1325-3018</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>경기도 성남시 분당구 성남대로 165 2층 223호, 224호 와이짐 PT 분당미금점</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/ygym3018</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P16" t="n">
-        <v>1077</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>443</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1520</v>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>1598086500</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1598086500</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>스포츠,오락</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>피티세븐 퍼스널트레이닝</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>body2balance@naver.com</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>0507-1400-9428</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>경기도 성남시 분당구 황새울로132번길 22-1 1층 102호 피티세븐</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>http://www.pts7.com</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P17" t="n">
-        <v>290</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>287</v>
-      </c>
-      <c r="R17" t="n">
-        <v>577</v>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>13093618</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/13093618</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>스포츠,오락</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>밀라노짐 수내점</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>milanos_1@naver.com</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>0507-1335-9682</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>경기도 성남시 분당구 내정로166번길 5 원전빌딩 B1층</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>http://www.instagram.com/milanogym_s</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P18" t="n">
-        <v>1139</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>695</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1834</v>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>1843911670</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1843911670</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>스포츠,오락</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>그린공간운동센터 PT 분당미금점</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>greenplace2020@naver.com</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>경기도 성남시 분당구 미금일로90번길 32 웰파크 2층 201호</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/greenplace2020</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P19" t="n">
-        <v>157</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>271</v>
-      </c>
-      <c r="R19" t="n">
-        <v>428</v>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>1364310838</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1364310838</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>스포츠,오락</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>운동생활 PT 분당야탑점</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>an_athletic_life25@naver.com</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>031-701-1110</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>경기도 성남시 분당구 야탑로69번길 18 2층 202호</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/an_athletic_life25</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P20" t="n">
-        <v>87</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>551</v>
-      </c>
-      <c r="R20" t="n">
-        <v>638</v>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>1275463246</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1275463246</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>스포츠,오락</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>솔리드짐 PT 수내점</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>ppapers@naver.com</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>0507-1420-7858</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>경기도 성남시 분당구 황새울로258번길 10-7 403호</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/solid_gym1</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P21" t="n">
-        <v>145</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>623</v>
-      </c>
-      <c r="R21" t="n">
-        <v>768</v>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>1205679892</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1205679892</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/분당_PT.xlsx
+++ b/naver-place-crawler/results_health/분당_PT.xlsx
@@ -423,7 +423,7 @@
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="29" customWidth="1" min="3" max="3"/>
-    <col width="29" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="40" customWidth="1" min="7" max="7"/>
@@ -564,29 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>구스짐 PT 판교점</t>
+          <t>레조나헬스랩PT 서판교점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>chlgudrn1@naver.com</t>
+          <t>resonar_healthlab@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1465-9683</t>
+          <t>0507-1411-1104</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교로 374 스타식스코아2 3층</t>
+          <t>경기도 성남시 분당구 판교공원로2길 9 4층 레조나헬스랩PT 서판교점</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/9s_gym_pangyo/</t>
+          <t>https://blog.naver.com/resonar_healthlab</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>161</v>
+        <v>56</v>
       </c>
       <c r="Q2" t="n">
-        <v>143</v>
+        <v>202</v>
       </c>
       <c r="R2" t="n">
-        <v>304</v>
+        <v>258</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,51 +636,51 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1088776551</t>
+          <t>1644348689</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1088776551</t>
+          <t>https://m.place.naver.com/place/1644348689</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>자마이카피트니스 분당정자점</t>
+          <t>구스짐 PT 판교점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>jamaica_jeongja@naver.com</t>
+          <t>chlgudrn1@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1383-8533</t>
+          <t>0507-1465-9683</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 정자일로 121 지하 1층</t>
+          <t>경기도 성남시 분당구 판교로 374 스타식스코아2 3층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/jamaica_bundang?igsh=MWY4cGIybjlodW11bw%3D%3D&amp;utm_source=qr</t>
+          <t>https://www.instagram.com/9s_gym_pangyo/</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1825</v>
+        <v>162</v>
       </c>
       <c r="Q3" t="n">
-        <v>223</v>
+        <v>143</v>
       </c>
       <c r="R3" t="n">
-        <v>2048</v>
+        <v>305</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,51 +730,51 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1710539074</t>
+          <t>1088776551</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1710539074</t>
+          <t>https://m.place.naver.com/place/1088776551</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>레조나헬스랩PT 서판교점</t>
+          <t>익스홀릭 가넷 미금점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>resonar_healthlab@naver.com</t>
+          <t>dydwk147@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1411-1104</t>
+          <t>0507-1429-2557</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교공원로2길 9 4층 레조나헬스랩PT 서판교점</t>
+          <t>경기도 성남시 분당구 돌마로 87 골드프라자 6층 가넷휘트니스</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/resonar_healthlab</t>
+          <t>https://blog.naver.com/dydwk147</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -809,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>56</v>
+        <v>561</v>
       </c>
       <c r="Q4" t="n">
-        <v>202</v>
+        <v>1073</v>
       </c>
       <c r="R4" t="n">
-        <v>258</v>
+        <v>1634</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,51 +824,51 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1644348689</t>
+          <t>12763227</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1644348689</t>
+          <t>https://m.place.naver.com/place/12763227</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>익스홀릭 가넷 미금점</t>
+          <t>험블 휘트니스 PT</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>dydwk147@naver.com</t>
+          <t>humblefitness@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1429-2557</t>
+          <t>031-697-8768</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 돌마로 87 골드프라자 6층 가넷휘트니스</t>
+          <t>경기도 성남시 분당구 성남대로331번길 3-3 701호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dydwk147</t>
+          <t>https://blog.naver.com/humblefitness</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -903,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>561</v>
+        <v>141</v>
       </c>
       <c r="Q5" t="n">
-        <v>1070</v>
+        <v>1437</v>
       </c>
       <c r="R5" t="n">
-        <v>1631</v>
+        <v>1578</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,17 +918,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>12763227</t>
+          <t>1134171602</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/12763227</t>
+          <t>https://m.place.naver.com/place/1134171602</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -940,38 +940,34 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>버핏그라운드 PT 판교</t>
+          <t>헬스보이짐 헬스 PT 판교역점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>butfitground@naver.com</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>butfitseoul@butfitseoul.com</t>
-        </is>
-      </c>
+          <t>healthboygym78@naver.com</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1417-1133</t>
+          <t>0507-1402-1275</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 136 B3007호</t>
+          <t>경기도 성남시 분당구 대왕판교로606번길 58 지하1층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.butfitground.com/4steppt</t>
+          <t>https://blog.naver.com/healthboygym78/223380215625</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -992,7 +988,7 @@
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1001,13 +997,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2540</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>323</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2863</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1016,17 +1012,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2029680813</t>
+          <t>1835201778</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2029680813</t>
+          <t>https://m.place.naver.com/place/1835201778</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1038,34 +1034,34 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>헬스보이짐 헬스 PT 판교역점</t>
+          <t>쓰리핏PT 분당정자점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>healthboygym78@naver.com</t>
+          <t>3fits@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1402-1275</t>
+          <t>0507-1409-3559</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 대왕판교로606번길 58 지하1층</t>
+          <t>경기도 성남시 분당구 내정로113번길 4 2층 202호, 203-1호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/healthboygym78/223380215625</t>
+          <t>https://3fitpt.com</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1086,7 +1082,7 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1095,13 +1091,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2535</v>
+        <v>357</v>
       </c>
       <c r="Q7" t="n">
-        <v>322</v>
+        <v>800</v>
       </c>
       <c r="R7" t="n">
-        <v>2857</v>
+        <v>1157</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1110,17 +1106,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1835201778</t>
+          <t>1845673431</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1835201778</t>
+          <t>https://m.place.naver.com/place/1845673431</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1198,7 +1194,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1272,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1354,7 +1350,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1432,7 +1428,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1510,7 +1506,7 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1584,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/분당_PT.xlsx
+++ b/naver-place-crawler/results_health/분당_PT.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V13"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -426,13 +426,13 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="39" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -581,7 +581,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교공원로2길 9 4층 레조나헬스랩PT 서판교점</t>
+          <t>경기 성남시 분당구 판교공원로2길 9 4층 레조나헬스랩PT 서판교점</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -606,10 +606,14 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w42t22</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -675,7 +679,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교로 374 스타식스코아2 3층</t>
+          <t>경기 성남시 분당구 판교로 374 스타식스코아2 3층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -700,10 +704,14 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wyuehl2</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -715,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q3" t="n">
         <v>143</v>
       </c>
       <c r="R3" t="n">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -769,7 +777,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 돌마로 87 골드프라자 6층 가넷휘트니스</t>
+          <t>경기 성남시 분당구 돌마로 87 골드프라자 6층 가넷휘트니스</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -794,10 +802,14 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4n5lk</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -812,10 +824,10 @@
         <v>561</v>
       </c>
       <c r="Q4" t="n">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="R4" t="n">
-        <v>1634</v>
+        <v>1635</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -957,7 +969,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 대왕판교로606번길 58 지하1층</t>
+          <t>경기 성남시 분당구 대왕판교로606번길 58 지하1층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -982,10 +994,14 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wi2wapb</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1027,51 +1043,35 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>쓰리핏PT 분당정자점</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>3fits@naver.com</t>
-        </is>
-      </c>
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0507-1409-3559</t>
-        </is>
-      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 내정로113번길 4 2층 202호, 203-1호</t>
+          <t>주소</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://3fitpt.com</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1082,22 +1082,22 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>357</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1157</v>
+        <v>0</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,12 +1106,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1845673431</t>
+          <t>7544685</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1845673431</t>
+          <t>https://m.place.naver.com/place/7544685</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1184,12 +1184,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>7544685</t>
+          <t>2600001</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/7544685</t>
+          <t>https://m.place.naver.com/place/2600001</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1262,12 +1262,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2600001</t>
+          <t>7167332</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2600001</t>
+          <t>https://m.place.naver.com/place/7167332</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1340,12 +1340,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>7167332</t>
+          <t>7536599</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/7167332</t>
+          <t>https://m.place.naver.com/place/7536599</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1418,12 +1418,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>7536599</t>
+          <t>7540516</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/7536599</t>
+          <t>https://m.place.naver.com/place/7540516</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1496,93 +1496,15 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>7540516</t>
+          <t>7181190</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/7540516</t>
+          <t>https://m.place.naver.com/place/7181190</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr"/>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>주소</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>7181190</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/7181190</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
         <is>
           <t>2026-04-26</t>
         </is>

--- a/naver-place-crawler/results_health/분당_PT.xlsx
+++ b/naver-place-crawler/results_health/분당_PT.xlsx
@@ -417,22 +417,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:V13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="29" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="39" customWidth="1" min="7" max="7"/>
+    <col width="49" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="35" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -564,29 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>레조나헬스랩PT 서판교점</t>
+          <t>구스짐 PT 판교점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>resonar_healthlab@naver.com</t>
+          <t>chlgudrn1@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1411-1104</t>
+          <t>0507-1465-9683</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기 성남시 분당구 판교공원로2길 9 4층 레조나헬스랩PT 서판교점</t>
+          <t>경기도 성남시 분당구 판교로 374 스타식스코아2 3층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/resonar_healthlab</t>
+          <t>https://www.instagram.com/9s_gym_pangyo/</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -601,19 +601,15 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w42t22</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -625,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>56</v>
+        <v>163</v>
       </c>
       <c r="Q2" t="n">
-        <v>202</v>
+        <v>143</v>
       </c>
       <c r="R2" t="n">
-        <v>258</v>
+        <v>306</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,12 +636,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1644348689</t>
+          <t>1088776551</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1644348689</t>
+          <t>https://m.place.naver.com/place/1088776551</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -662,29 +658,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>구스짐 PT 판교점</t>
+          <t>레조나헬스랩PT 서판교점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>chlgudrn1@naver.com</t>
+          <t>resonar_healthlab@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1465-9683</t>
+          <t>0507-1411-1104</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기 성남시 분당구 판교로 374 스타식스코아2 3층</t>
+          <t>경기도 성남시 분당구 판교공원로2길 9 4층 레조나헬스랩PT 서판교점</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/9s_gym_pangyo/</t>
+          <t>https://blog.naver.com/resonar_healthlab</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -699,19 +695,15 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wyuehl2</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -723,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>163</v>
+        <v>56</v>
       </c>
       <c r="Q3" t="n">
-        <v>143</v>
+        <v>202</v>
       </c>
       <c r="R3" t="n">
-        <v>306</v>
+        <v>258</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -738,12 +730,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1088776551</t>
+          <t>1644348689</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1088776551</t>
+          <t>https://m.place.naver.com/place/1644348689</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -755,34 +747,34 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>익스홀릭 가넷 미금점</t>
+          <t>레조나헬스랩PT 정자역점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>dydwk147@naver.com</t>
+          <t>resonar_healthlab2@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1429-2557</t>
+          <t>0507-1415-7374</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기 성남시 분당구 돌마로 87 골드프라자 6층 가넷휘트니스</t>
+          <t>경기도 성남시 분당구 성남대로331번길 11-15 봉우빌딩 3층 301호 레조나헬스랩</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dydwk147</t>
+          <t>https://www.instagram.com/resonar_healthlab</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -797,19 +789,15 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4n5lk</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -821,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>561</v>
+        <v>27</v>
       </c>
       <c r="Q4" t="n">
-        <v>1074</v>
+        <v>258</v>
       </c>
       <c r="R4" t="n">
-        <v>1635</v>
+        <v>285</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -836,12 +824,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>12763227</t>
+          <t>1265132759</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/12763227</t>
+          <t>https://m.place.naver.com/place/1265132759</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -853,34 +841,38 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>험블 휘트니스 PT</t>
+          <t>버핏그라운드 판교</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>humblefitness@naver.com</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>butfitground@naver.com</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>partner@butfitseoul.com</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>031-697-8768</t>
+          <t>0507-1329-4325</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로331번길 3-3 701호</t>
+          <t>경기도 성남시 분당구 판교역로 136 B3007</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/humblefitness</t>
+          <t>https://pt.butfitground.com/</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -906,7 +898,7 @@
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -915,13 +907,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>141</v>
+        <v>1765</v>
       </c>
       <c r="Q5" t="n">
-        <v>1437</v>
+        <v>250</v>
       </c>
       <c r="R5" t="n">
-        <v>1578</v>
+        <v>2015</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -930,12 +922,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1134171602</t>
+          <t>1136752576</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1134171602</t>
+          <t>https://m.place.naver.com/place/1136752576</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -952,29 +944,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>헬스보이짐 헬스 PT 판교역점</t>
+          <t>험블 휘트니스 PT</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>healthboygym78@naver.com</t>
+          <t>humblefitness@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1402-1275</t>
+          <t>031-697-8768</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기 성남시 분당구 대왕판교로606번길 58 지하1층</t>
+          <t>경기도 성남시 분당구 성남대로331번길 3-3 701호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/healthboygym78/223380215625</t>
+          <t>https://blog.naver.com/humblefitness</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -994,14 +986,10 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wi2wapb</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1013,13 +1001,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2540</v>
+        <v>141</v>
       </c>
       <c r="Q6" t="n">
-        <v>323</v>
+        <v>1437</v>
       </c>
       <c r="R6" t="n">
-        <v>2863</v>
+        <v>1578</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1028,12 +1016,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1835201778</t>
+          <t>1134171602</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1835201778</t>
+          <t>https://m.place.naver.com/place/1134171602</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1043,20 +1031,36 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>헬스보이짐 헬스 PT 판교역점</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>healthboygym78@naver.com</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0507-1402-1275</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>주소</t>
+          <t>경기도 성남시 분당구 대왕판교로606번길 58 지하1층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/healthboygym78/223380215625</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1066,12 +1070,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1087,17 +1091,17 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2540</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>323</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2863</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,12 +1110,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>7544685</t>
+          <t>1835201778</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/7544685</t>
+          <t>https://m.place.naver.com/place/1835201778</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1184,12 +1188,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2600001</t>
+          <t>7544685</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2600001</t>
+          <t>https://m.place.naver.com/place/7544685</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1262,12 +1266,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>7167332</t>
+          <t>2600001</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/7167332</t>
+          <t>https://m.place.naver.com/place/2600001</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1340,12 +1344,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>7536599</t>
+          <t>7167332</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/7536599</t>
+          <t>https://m.place.naver.com/place/7167332</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1418,12 +1422,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>7540516</t>
+          <t>7536599</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/7540516</t>
+          <t>https://m.place.naver.com/place/7536599</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1496,15 +1500,93 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
+          <t>7540516</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/7540516</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>주소</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
           <t>7181190</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>https://m.place.naver.com/place/7181190</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>2026-04-26</t>
         </is>

--- a/naver-place-crawler/results_health/분당_PT.xlsx
+++ b/naver-place-crawler/results_health/분당_PT.xlsx
@@ -417,16 +417,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V13"/>
+  <dimension ref="A1:V76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
     <col width="25" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="49" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -564,44 +564,44 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>구스짐 PT 판교점</t>
+          <t>크레이지핏 PT</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>chlgudrn1@naver.com</t>
+          <t>krazyfit@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1465-9683</t>
+          <t>0507-1488-5883</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교로 374 스타식스코아2 3층</t>
+          <t>경기도 성남시 분당구 정자일로198번길 6-5 3층 크레이지핏</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/9s_gym_pangyo/</t>
+          <t>https://m.booking.naver.com/booking/13/bizes/205740?theme=place&amp;entry=pll&amp;lang=ko&amp;area=pll</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -612,7 +612,7 @@
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>163</v>
+        <v>535</v>
       </c>
       <c r="Q2" t="n">
-        <v>143</v>
+        <v>1437</v>
       </c>
       <c r="R2" t="n">
-        <v>306</v>
+        <v>1972</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,12 +636,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1088776551</t>
+          <t>1628554288</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1088776551</t>
+          <t>https://m.place.naver.com/place/1628554288</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -653,34 +653,34 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>레조나헬스랩PT 서판교점</t>
+          <t>와이피트니스 헬스&amp;PT 분당야탑점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>resonar_healthlab@naver.com</t>
+          <t>yfitness02@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1411-1104</t>
+          <t>0507-1430-1729</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교공원로2길 9 4층 레조나헬스랩PT 서판교점</t>
+          <t>경기도 성남시 분당구 벌말로40번길 5-1 지하1층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/resonar_healthlab</t>
+          <t>https://www.instagram.com/yfitness02?igsh=MTR6dDl6cW5sNWNxMg%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -706,7 +706,7 @@
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>56</v>
+        <v>105</v>
       </c>
       <c r="Q3" t="n">
-        <v>202</v>
+        <v>55</v>
       </c>
       <c r="R3" t="n">
-        <v>258</v>
+        <v>160</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,12 +730,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1644348689</t>
+          <t>2013735870</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1644348689</t>
+          <t>https://m.place.naver.com/place/2013735870</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -752,29 +752,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>레조나헬스랩PT 정자역점</t>
+          <t>리,무브먼트</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>resonar_healthlab2@naver.com</t>
+          <t>sujin6735@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1415-7374</t>
+          <t>0507-1310-5661</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로331번길 11-15 봉우빌딩 3층 301호 레조나헬스랩</t>
+          <t>경기도 성남시 분당구 운중로 140 메트로골드 203호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/resonar_healthlab</t>
+          <t>https://www.instagram.com/re__movement</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -809,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>27</v>
+        <v>242</v>
       </c>
       <c r="Q4" t="n">
-        <v>258</v>
+        <v>246</v>
       </c>
       <c r="R4" t="n">
-        <v>285</v>
+        <v>488</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,12 +824,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1265132759</t>
+          <t>1149465061</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1265132759</t>
+          <t>https://m.place.naver.com/place/1149465061</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -841,38 +841,34 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>버핏그라운드 판교</t>
+          <t>린바디핏 PT 판교본점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>butfitground@naver.com</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>partner@butfitseoul.com</t>
-        </is>
-      </c>
+          <t>leanbodyfitv2@naver.com</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1329-4325</t>
+          <t>0507-1302-8312</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 136 B3007</t>
+          <t>경기도 성남시 분당구 대왕판교로 670 지하113호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://pt.butfitground.com/</t>
+          <t>https://blog.naver.com/leanbodyfitv2</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -903,17 +899,17 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1765</v>
+        <v>135</v>
       </c>
       <c r="Q5" t="n">
-        <v>250</v>
+        <v>108</v>
       </c>
       <c r="R5" t="n">
-        <v>2015</v>
+        <v>243</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -922,12 +918,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1136752576</t>
+          <t>1699238533</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1136752576</t>
+          <t>https://m.place.naver.com/place/1699238533</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -944,44 +940,44 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>험블 휘트니스 PT</t>
+          <t>리커브 피티 앤 본척척 재활 센터 야탑점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>humblefitness@naver.com</t>
+          <t>recurvept@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>031-697-8768</t>
+          <t>0507-1441-8303</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로331번길 3-3 701호</t>
+          <t>경기도 성남시 분당구 성남대로916번길 5 3층 302호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/humblefitness</t>
+          <t>https://m.booking.naver.com/booking/12/bizes/1590839</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1001,13 +997,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>141</v>
+        <v>13</v>
       </c>
       <c r="Q6" t="n">
-        <v>1437</v>
+        <v>248</v>
       </c>
       <c r="R6" t="n">
-        <v>1578</v>
+        <v>261</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1016,12 +1012,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1134171602</t>
+          <t>2038767341</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1134171602</t>
+          <t>https://m.place.naver.com/place/2038767341</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1038,34 +1034,34 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>헬스보이짐 헬스 PT 판교역점</t>
+          <t>쓰리핏 PT 분당미금점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>healthboygym78@naver.com</t>
+          <t>3fits@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1402-1275</t>
+          <t>0507-1302-3558</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 대왕판교로606번길 58 지하1층</t>
+          <t>경기도 성남시 분당구 돌마로 47 6층 607호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/healthboygym78/223380215625</t>
+          <t>https://3fitpt.com</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1086,7 +1082,7 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1095,13 +1091,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2540</v>
+        <v>427</v>
       </c>
       <c r="Q7" t="n">
-        <v>323</v>
+        <v>954</v>
       </c>
       <c r="R7" t="n">
-        <v>2863</v>
+        <v>1381</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1110,12 +1106,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1835201778</t>
+          <t>1135214262</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1835201778</t>
+          <t>https://m.place.naver.com/place/1135214262</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1125,20 +1121,36 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>유앤바디PT 분당수내점</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>unbody@naver.com</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>031-714-4729</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>주소</t>
+          <t>경기도 성남시 분당구 백현로101번길 12 세인프라자 402호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/unbody</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1148,12 +1160,12 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1169,17 +1181,17 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>118</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>166</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>284</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1188,12 +1200,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>7544685</t>
+          <t>1853394852</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/7544685</t>
+          <t>https://m.place.naver.com/place/1853394852</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1203,20 +1215,36 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr"/>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>런던피트니스&amp;필라테스 분당이매점</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>londoner83@naver.com</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0507-1406-9679</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>주소</t>
+          <t>경기도 성남시 분당구 성남대로779번길 13 오성프라자빌딩 5층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/londoner83</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1226,12 +1254,12 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1247,17 +1275,17 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1340</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>473</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1813</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1266,12 +1294,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2600001</t>
+          <t>13530251</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2600001</t>
+          <t>https://m.place.naver.com/place/13530251</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1281,20 +1309,36 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr"/>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>머슬짐 PT 분당정자점</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>musclegym9679@naver.com</t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0507-1405-9679</t>
+        </is>
+      </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>주소</t>
+          <t>경기도 성남시 분당구 성남대로343번길 10-6 동원빌딩 4층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/musclegym9679</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1304,12 +1348,12 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1329,13 +1373,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>215</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>281</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>496</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1344,12 +1388,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>7167332</t>
+          <t>1975809201</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/7167332</t>
+          <t>https://m.place.naver.com/place/1975809201</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1359,20 +1403,32 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>렛미PT&amp;필라테스스튜디오 분당야탑점</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>let_me_pt_official@naver.com</t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>주소</t>
+          <t>경기도 성남시 분당구 야탑로69번길 21 영진다이비스상가 2층 210호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/let_me_pt_official</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1382,12 +1438,12 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1403,17 +1459,17 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>129</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1422,12 +1478,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>7536599</t>
+          <t>1049956503</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/7536599</t>
+          <t>https://m.place.naver.com/place/1049956503</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1437,20 +1493,36 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr"/>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>스포애니 야탑역점</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>spoany90@naver.com</t>
+        </is>
+      </c>
       <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1337-9618</t>
+        </is>
+      </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>주소</t>
+          <t>경기도 성남시 분당구 성남대로 926 메트로빌딩 8층</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://m.spoany.co.kr/branch/branch_detail.html?base_seq=MTA1</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1460,7 +1532,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1481,17 +1553,17 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>707</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>1499</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>2206</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1500,12 +1572,12 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>7540516</t>
+          <t>1115298912</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/7540516</t>
+          <t>https://m.place.naver.com/place/1115298912</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -1515,20 +1587,36 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr"/>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>레조나헬스랩PT 정자역점</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>resonar_healthlab2@naver.com</t>
+        </is>
+      </c>
       <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0507-1415-7374</t>
+        </is>
+      </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>주소</t>
+          <t>경기도 성남시 분당구 성남대로331번길 11-15 봉우빌딩 3층 301호 레조나헬스랩</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/resonar_healthlab</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1538,7 +1626,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1559,17 +1647,17 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>258</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>285</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1578,15 +1666,5921 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>7181190</t>
+          <t>1265132759</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/7181190</t>
+          <t>https://m.place.naver.com/place/1265132759</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>올뉴바디 운동맛집PT 야탑점</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>allnewbody@naver.com</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0507-1329-3987</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 벌말로 44 401호</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/allnewbody</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>600</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>618</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1218</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>1203378061</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1203378061</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>H GYM PT GT 판교2호점</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>hgym9408@naver.com</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0507-1353-9408</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 운중로 233 302호</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>https://hgym.imweb.me</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>279</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>420</v>
+      </c>
+      <c r="R15" t="n">
+        <v>699</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>1850894755</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1850894755</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>체온 PT &amp; 필라테스</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>cheonpt@naver.com</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>031-701-2162</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 서현로 216 오벨리스크 상가 202호 체온PT&amp;필라테스</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/cheonpt</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>84</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>403</v>
+      </c>
+      <c r="R16" t="n">
+        <v>487</v>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>1080351846</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1080351846</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>제이치피트니스 헬스&amp;PT 미금점</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>redgym_migeum@naver.com</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>0507-1332-4462</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 성남대로 165 지하1층</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/jhfitness_migeum?igsh</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>1285</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>274</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1559</v>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>1109176574</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1109176574</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>헬스보이짐&amp;필라걸&amp;골프인 분당정자점</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>healthboy90_@naver.com</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>0507-1419-2436</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 성남대로331번길 13 7층 701-706호</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/healthboy90_/223799590825</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>457</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>751</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1208</v>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>1989525945</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1989525945</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>바로선운동센터 판교점</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>coolksh11@naver.com</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 동판교로 61 2층 201호</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/coolksh11</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>185</v>
+      </c>
+      <c r="R19" t="n">
+        <v>207</v>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>2015061102</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2015061102</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>헬스보이짐&amp;필라걸 수내점</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>healthboy40@naver.com</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>0507-1380-2239</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 내정로173번길 49 5층</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/healthboy40/223688037867</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>968</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>734</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1702</v>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>1973151166</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1973151166</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>비율라이프 바디코치 여성전용 체형필라테스 PT 야탑점</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>rockrock1256@naver.com</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>0507-1445-2430</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 야탑로69번길 8 2층 바디코치 야탑점</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/official_bodycoach?igsh=MTF6cmlnd240MTdwMg%3D%3D&amp;utm_source=qr</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>203</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>786</v>
+      </c>
+      <c r="R21" t="n">
+        <v>989</v>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>1723811790</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1723811790</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>피트니스비엠 분당 서현점</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>ksk2023@naver.com</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>0507-1443-0942</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 돌마로 482 주영빌딩 지하 1층</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/fitnessbm._.hyoja</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>513</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>684</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1197</v>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>36333115</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/36333115</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>스포애니 수내점</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>spoany012@naver.com</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>031-712-3362</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 돌마로 364 현대제일상가 B1층</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>https://m.spoany.co.kr/branch/branch_detail.html?base_seq=MjE=</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>296</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1548</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1844</v>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>31849989</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/31849989</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>와이짐 PT 분당미금점</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>ygym3018@naver.com</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>0507-1325-3018</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 성남대로 165 2층 223호, 224호 와이짐 PT 분당미금점</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/ygym3018</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>1077</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>446</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1523</v>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>1598086500</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1598086500</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>운동생활 PT 분당야탑점</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>an_athletic_life25@naver.com</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>031-701-1110</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 야탑로69번길 18 2층 202호</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/an_athletic_life25</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>86</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>549</v>
+      </c>
+      <c r="R25" t="n">
+        <v>635</v>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>1275463246</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1275463246</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>브레이브 휘트니스 분당정자점</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>bravefitness_jeongja@naver.com</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>0507-1484-0779</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 내정로17번길 2 지하1층</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/bravefitness_jeongja</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>1418</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>1226</v>
+      </c>
+      <c r="R26" t="n">
+        <v>2644</v>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>1043618213</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1043618213</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>구스짐 PT 판교점</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>chlgudrn1@naver.com</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>0507-1465-9683</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교로 374 스타식스코아2 3층</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/9s_gym_pangyo/</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>163</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>143</v>
+      </c>
+      <c r="R27" t="n">
+        <v>306</v>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>1088776551</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1088776551</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>휘트니스클럽S 수내점</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>fitnessclubs12@naver.com</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>0507-1311-1188</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 백현로101번길 11 5층</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/fitnessclubs12</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>309</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>917</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1226</v>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>1228787055</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1228787055</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>F45 정자</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>eunzzori@naver.com</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 정자일로198번길 24 2층</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/f45_jeongja</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
+        <v>117</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>42</v>
+      </c>
+      <c r="R29" t="n">
+        <v>159</v>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>1893893702</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1893893702</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>그린공간운동센터 PT 분당미금점</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>greenplace2020@naver.com</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 미금일로90번길 32 웰파크 2층 201호</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/greenplace2020</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
+        <v>157</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>292</v>
+      </c>
+      <c r="R30" t="n">
+        <v>449</v>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>1364310838</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1364310838</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>피트니스웰시 헬스&amp;PT 분당정자점</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>health-pt@naver.com</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>0507-1489-7037</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 성남대로343번길 12-8 1동 4층</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/health-pt</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P31" t="n">
+        <v>531</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>469</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>1623406875</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1623406875</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>리파인짐 PT 분당야탑점</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>ksw8591@naver.com</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>0507-1380-1864</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 성남대로926번길 6 302호</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/ksw8591</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
+        <v>142</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>310</v>
+      </c>
+      <c r="R32" t="n">
+        <v>452</v>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>1297851351</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1297851351</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>D gym PT 수내역점</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>hyenggoo1@naver.com</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>0507-1438-1374</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 황새울로200번길 34 205, 206호</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/dgym_official/?igshid=YmMyMTA2M2Y%3D</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P33" t="n">
+        <v>156</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>367</v>
+      </c>
+      <c r="R33" t="n">
+        <v>523</v>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>1234729561</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1234729561</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>비전휘트니스 분당점</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>visionfitness555@naver.com</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>0507-1439-8755</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 돌마로 46 광천프라자 2층</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>https://litt.ly/visionfitness05</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P34" t="n">
+        <v>2471</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>1919</v>
+      </c>
+      <c r="R34" t="n">
+        <v>4390</v>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>1765794431</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1765794431</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>카인드짐 휘트니스 헬스&amp;PT 야탑역점</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>kindgym28@naver.com</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>0507-1361-3615</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 야탑로81번길 10 아미고타워 B1층 카인드짐 휘트니스 헬스&amp;PT 야탑역점</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/kindgym28</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P35" t="n">
+        <v>2034</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>1577</v>
+      </c>
+      <c r="R35" t="n">
+        <v>3611</v>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>36230651</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/36230651</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>빌드업피트니스 PT 야탑점</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>buildupfitness02@naver.com</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>0507-1329-7003</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 장미로 198 B1 빌드업피트니스PT 야탑점</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>https://www.buildupfitness.co.kr</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P36" t="n">
+        <v>2435</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>1017</v>
+      </c>
+      <c r="R36" t="n">
+        <v>3452</v>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>1233503897</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1233503897</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>바디밸런스 PT 미금점</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>xodbs2384@naver.com</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>0507-1369-2582</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 미금일로 65 지하1층 바디밸런스</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/xodbs2384/221996918084</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P37" t="n">
+        <v>153</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>840</v>
+      </c>
+      <c r="R37" t="n">
+        <v>993</v>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>1400263548</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1400263548</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>렛츠핏 야탑점 헬스&amp;PT</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>sm8893@naver.com</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>0507-1305-0298</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 벌말로 37 4층 1, 2호</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>https://bmarket.broj.co.kr/groups/413620357</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P38" t="n">
+        <v>917</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>1289</v>
+      </c>
+      <c r="R38" t="n">
+        <v>2206</v>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>1320604673</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1320604673</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>헤일로짐24시 헬스 PT 판교점</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>halogym02@naver.com</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>0507-1315-8840</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 대왕판교로 660 유스페이스1 지하1층 127호</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>https://booking.naver.com/booking/6/bizes/933331</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P39" t="n">
+        <v>663</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>929</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1592</v>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>1806695299</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1806695299</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>뭉트니스 야탑</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>mtns1@naver.com</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 장미로 55 장미마을 지하1층</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/mtns_leader</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P40" t="n">
+        <v>284</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>1036</v>
+      </c>
+      <c r="R40" t="n">
+        <v>1320</v>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>1657314482</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1657314482</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>비아핏</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>viafit@naver.com</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>0507-1379-7507</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교대장로7길 15-2 지하1층,지상1층</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/viafit_no.1</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P41" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>24</v>
+      </c>
+      <c r="R41" t="n">
+        <v>50</v>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>1772663783</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1772663783</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>팀제이맥스 피티 서현점</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>teamjmax_sh@naver.com</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>031-702-8296</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 서현로180번길 13 2층 206호</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/teamjmax_sh</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P42" t="n">
+        <v>911</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>549</v>
+      </c>
+      <c r="R42" t="n">
+        <v>1460</v>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>1639683746</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1639683746</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>짐휴 PT 분당미금점</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>gym_hue@naver.com</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>0507-1369-1180</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 돌마로 47 이코노샤르망 5층 509호, 510호</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/gym_hue</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P43" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>247</v>
+      </c>
+      <c r="R43" t="n">
+        <v>432</v>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>1527774793</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1527774793</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>블랙스미스짐 헬스PT 판교점</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>emmaholic1@naver.com</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>0507-1352-4388</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교역로 136 지하2층 비2147호, 비2148호</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>http://blacksmithgym.kr/</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P44" t="n">
+        <v>107</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>194</v>
+      </c>
+      <c r="R44" t="n">
+        <v>301</v>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>1462760829</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1462760829</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>팀윤짐 헬스PT</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>teamyoonsh@naver.com</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>0507-1363-8855</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 황새울로342번길 23 기영프라자 8층</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/teamyoonsh</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P45" t="n">
+        <v>91</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>485</v>
+      </c>
+      <c r="R45" t="n">
+        <v>576</v>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>35523795</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/35523795</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>밀라노짐 수내점</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>milanos_1@naver.com</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>0507-1335-9682</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 내정로166번길 5 원전빌딩 B1층</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/milanogym_s</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P46" t="n">
+        <v>1141</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>696</v>
+      </c>
+      <c r="R46" t="n">
+        <v>1837</v>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>1843911670</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1843911670</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>피티세븐 퍼스널트레이닝</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>body2balance@naver.com</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0507-1400-9428</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 황새울로132번길 22-1 1층 102호 피티세븐</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>http://www.pts7.com</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P47" t="n">
+        <v>302</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>291</v>
+      </c>
+      <c r="R47" t="n">
+        <v>593</v>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>13093618</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/13093618</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>바른몸PT센터</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>wlsrkfdl1@naver.com</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0507-1337-9711</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 백현로101번길 20 3층 301호</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/wlsrkfdl1</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P48" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>70</v>
+      </c>
+      <c r="R48" t="n">
+        <v>75</v>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>2090651326</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2090651326</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>쿼드짐</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>quadgym@naver.com</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0507-1303-9415</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 정자일로 121 더샵스타파크 상가1층 b-18호</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/quadgym</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P49" t="n">
+        <v>82</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>102</v>
+      </c>
+      <c r="R49" t="n">
+        <v>184</v>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>1759307500</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1759307500</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>와이투짐 야탑역점</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>y2gym2@naver.com</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0507-1352-8844</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 성남대로 912 B1층</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/y2gym2</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P50" t="n">
+        <v>380</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>1572</v>
+      </c>
+      <c r="R50" t="n">
+        <v>1952</v>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>1930702763</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1930702763</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>쓰리핏 헬스&amp;PT 서현점</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>3fits@naver.com</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0507-1388-2211</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 불정로 379 서현프라자 지하1층</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>https://3fitpt.com</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P51" t="n">
+        <v>1030</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>929</v>
+      </c>
+      <c r="R51" t="n">
+        <v>1959</v>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>1181952796</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1181952796</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>스포애니 서현역점</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>spoany22@naver.com</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>031-706-8522</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 황새울로 324 좋은상호저축은행빌딩 B1층</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/spoany22</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P52" t="n">
+        <v>951</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>2036</v>
+      </c>
+      <c r="R52" t="n">
+        <v>2987</v>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>13025013</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/13025013</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>석세스짐&amp;PT 분당무지개마을점</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>successgym-b3@naver.com</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>0507-1331-7127</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 미금로 36 브리엘프라자 4층</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/successgym-b3</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P53" t="n">
+        <v>103</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>336</v>
+      </c>
+      <c r="R53" t="n">
+        <v>439</v>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>1860293712</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1860293712</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>더바디핏PT 분당야탑2호점</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>thebodyfitpt@naver.com</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>0507-1302-9149</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 성남대로916번길 7 205호 더바디핏PT</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/thebodyfitpt</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P54" t="n">
+        <v>452</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>723</v>
+      </c>
+      <c r="R54" t="n">
+        <v>1175</v>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>1564371057</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1564371057</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>피쓰리짐 PT</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>p3gym@naver.com</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>0507-1346-9079</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 정자로 13 월드비터 B1 피쓰리짐</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/p3gym</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P55" t="n">
+        <v>75</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>512</v>
+      </c>
+      <c r="R55" t="n">
+        <v>587</v>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>1847926774</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1847926774</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>포랩 이즈메디운동센터</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>for_lab2017@naver.com</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>0507-1432-1575</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 서현로 192 야베스밸리 9층</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/for_lab2017</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P56" t="n">
+        <v>289</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>158</v>
+      </c>
+      <c r="R56" t="n">
+        <v>447</v>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>917204514</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/917204514</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>베러댄 휘트니스 분당야탑점</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>56zqrwcwsv@naver.com</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>0507-1438-9698</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 야탑로75번길 15 세화빌딩 4층</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/56zqrwcwsv</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P57" t="n">
+        <v>382</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>2088</v>
+      </c>
+      <c r="R57" t="n">
+        <v>2470</v>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>1013682807</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1013682807</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>험블 휘트니스 PT</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>humblefitness@naver.com</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>031-697-8768</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 성남대로331번길 3-3 701호</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/humblefitness</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P58" t="n">
+        <v>141</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>1437</v>
+      </c>
+      <c r="R58" t="n">
+        <v>1578</v>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>1134171602</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1134171602</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>버핏그라운드 판교</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>butfitground@naver.com</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>partner@butfitseoul.com</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>0507-1329-4325</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교역로 136 B3007</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>https://pt.butfitground.com/</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P59" t="n">
+        <v>1765</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>250</v>
+      </c>
+      <c r="R59" t="n">
+        <v>2015</v>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>1136752576</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1136752576</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>제로업PT</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>axus2000@naver.com</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>031-623-2775</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 느티로 16 7층</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/zero____up/</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P60" t="n">
+        <v>767</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>715</v>
+      </c>
+      <c r="R60" t="n">
+        <v>1482</v>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>1975822360</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1975822360</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>업투 휘트니스 분당판교점</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>uptofitness-@naver.com</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>0507-1343-8274</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 동판교로 59 6층 601-605호</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/uptofitness-</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P61" t="n">
+        <v>619</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>291</v>
+      </c>
+      <c r="R61" t="n">
+        <v>910</v>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>1928497638</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1928497638</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>핏슈브 분당이매점</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>9_bonhyuk@naver.com</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>0507-1486-9921</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교로 475 4층 404호</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/9_bonhyuk</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P62" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>163</v>
+      </c>
+      <c r="R62" t="n">
+        <v>180</v>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>2032296152</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2032296152</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>데스런 판교점</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>deslun@naver.com</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>0507-1412-6347</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교역로2번길 38</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>http://www.deslun.co.kr</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P63" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>398</v>
+      </c>
+      <c r="R63" t="n">
+        <v>420</v>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>31469573</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/31469573</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>써트짐 PT</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>certgym@naver.com</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>0507-1367-7665</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 황새울로214번길 8 207호(수내동, MS프라자)</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/cert.gym.official</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P64" t="n">
+        <v>49</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>237</v>
+      </c>
+      <c r="R64" t="n">
+        <v>286</v>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>1331332549</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1331332549</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>펠릭스짐 분당점</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>felixgym1@naver.com</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>0507-1393-3039</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 장안로 39 2층 201호</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/felixgym__</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P65" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>45</v>
+      </c>
+      <c r="R65" t="n">
+        <v>69</v>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>1125789234</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1125789234</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>스포애니 미금점</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>spoany_14s@naver.com</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>0507-1474-5855</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 돌마로 75 미금프라자 8층</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/spoany14/</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P66" t="n">
+        <v>1084</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>1821</v>
+      </c>
+      <c r="R66" t="n">
+        <v>2905</v>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>20065928</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/20065928</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>리조트휘트니스 PT 판교점</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>resort_5@naver.com</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>0507-1438-0677</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 운중로 142 판교메디칼타워 6층, 7층</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/resortfitness__pangyo/</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P67" t="n">
+        <v>413</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>714</v>
+      </c>
+      <c r="R67" t="n">
+        <v>1127</v>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>35524502</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/35524502</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>머슬짐 PT 분당서현점</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>musclegym_@naver.com</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>0507-1436-9680</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 황새울로342번길 19 유성그린빌딩 6층</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/musclegym_</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P68" t="n">
+        <v>200</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>367</v>
+      </c>
+      <c r="R68" t="n">
+        <v>567</v>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>1208748555</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1208748555</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>하이클래스짐 서현점 헬스 PT</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>highclassgym2@naver.com</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 불정로 382 3층</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>https://link.inpock.co.kr/highclassgym2</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P69" t="n">
+        <v>1336</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>1814</v>
+      </c>
+      <c r="R69" t="n">
+        <v>3150</v>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>1974917013</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1974917013</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>에버그린PT</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>evergreen_pt@naver.com</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>0507-1314-9993</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 불정로376번길 7 3층일부(304호)</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/evergreen_pt</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P70" t="n">
+        <v>81</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>252</v>
+      </c>
+      <c r="R70" t="n">
+        <v>333</v>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>1749890190</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1749890190</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>좋은습관PTSTUDIO 판교운중</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>goodhabitpg@naver.com</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>0507-1480-0677</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 운중로 142 6층</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/goodhabit_pangyo/</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P71" t="n">
+        <v>63</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>29</v>
+      </c>
+      <c r="R71" t="n">
+        <v>92</v>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>1070284726</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1070284726</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>피트니스비엠 분당 장안타운점</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>fitnessbm77@naver.com</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>0507-1397-6556</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 분당로263번길 35 서현굿모닝프라자</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/fitnessbm77</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P72" t="n">
+        <v>279</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>786</v>
+      </c>
+      <c r="R72" t="n">
+        <v>1065</v>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>20099119</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/20099119</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>핏불짐 판교점</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>fitbullgym@naver.com</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>0507-1430-9683</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 동판교로 61 자유퍼스트프라자2 3층 304호</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>https://linktr.ee/fitbullgym</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P73" t="n">
+        <v>92</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>283</v>
+      </c>
+      <c r="R73" t="n">
+        <v>375</v>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>37814535</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37814535</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>헬스보이짐 헬스 PT 판교역점</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>healthboygym78@naver.com</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>0507-1402-1275</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 대왕판교로606번길 58 지하1층</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/healthboygym78/223380215625</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P74" t="n">
+        <v>2540</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>323</v>
+      </c>
+      <c r="R74" t="n">
+        <v>2863</v>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>1835201778</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1835201778</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>솔리드짐 PT 수내점</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>ppapers@naver.com</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>0507-1420-7858</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 황새울로258번길 10-7 403호</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/solid_gym1</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P75" t="n">
+        <v>145</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>652</v>
+      </c>
+      <c r="R75" t="n">
+        <v>797</v>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>1205679892</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1205679892</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>쓰리핏PT 분당정자점</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>3fits@naver.com</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>0507-1409-3559</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 내정로113번길 4 2층 202호, 203-1호</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>https://3fitpt.com</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P76" t="n">
+        <v>357</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>800</v>
+      </c>
+      <c r="R76" t="n">
+        <v>1157</v>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>1845673431</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1845673431</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
         <is>
           <t>2026-04-26</t>
         </is>

--- a/naver-place-crawler/results_health/분당_PT.xlsx
+++ b/naver-place-crawler/results_health/분당_PT.xlsx
@@ -432,7 +432,7 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -646,41 +646,41 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>와이피트니스 헬스&amp;PT 분당야탑점</t>
+          <t>팀윤짐 헬스PT</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>yfitness02@naver.com</t>
+          <t>teamyoonsh@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1430-1729</t>
+          <t>0507-1363-8855</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 벌말로40번길 5-1 지하1층</t>
+          <t>경기도 성남시 분당구 황새울로342번길 23 기영프라자 8층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/yfitness02?igsh=MTR6dDl6cW5sNWNxMg%3D%3D&amp;utm_source=qr</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -690,7 +690,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -700,28 +700,32 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wc6ysr</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>105</v>
+        <v>91</v>
       </c>
       <c r="Q3" t="n">
-        <v>55</v>
+        <v>485</v>
       </c>
       <c r="R3" t="n">
-        <v>160</v>
+        <v>576</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,17 +734,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2013735870</t>
+          <t>35523795</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2013735870</t>
+          <t>https://m.place.naver.com/place/35523795</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -752,29 +756,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>리,무브먼트</t>
+          <t>운동생활 PT 분당야탑점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>sujin6735@naver.com</t>
+          <t>an_athletic_life25@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1310-5661</t>
+          <t>031-701-1110</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 운중로 140 메트로골드 203호</t>
+          <t>경기도 성남시 분당구 야탑로69번길 18 2층 202호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/re__movement</t>
+          <t>https://blog.naver.com/an_athletic_life25</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -789,7 +793,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -805,17 +809,17 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>242</v>
+        <v>86</v>
       </c>
       <c r="Q4" t="n">
-        <v>246</v>
+        <v>549</v>
       </c>
       <c r="R4" t="n">
-        <v>488</v>
+        <v>635</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,51 +828,51 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1149465061</t>
+          <t>1275463246</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1149465061</t>
+          <t>https://m.place.naver.com/place/1275463246</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>린바디핏 PT 판교본점</t>
+          <t>제이치피트니스 헬스&amp;PT 미금점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>leanbodyfitv2@naver.com</t>
+          <t>redgym_migeum@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1302-8312</t>
+          <t>0507-1332-4462</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 대왕판교로 670 지하113호</t>
+          <t>경기도 성남시 분당구 성남대로 165 지하1층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/leanbodyfitv2</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -878,38 +882,42 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wzxrxow</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>135</v>
+        <v>1285</v>
       </c>
       <c r="Q5" t="n">
-        <v>108</v>
+        <v>274</v>
       </c>
       <c r="R5" t="n">
-        <v>243</v>
+        <v>1559</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,56 +926,56 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1699238533</t>
+          <t>1109176574</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1699238533</t>
+          <t>https://m.place.naver.com/place/1109176574</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>리커브 피티 앤 본척척 재활 센터 야탑점</t>
+          <t>스포애니 서현역점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>recurvept@naver.com</t>
+          <t>spoany22@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1441-8303</t>
+          <t>031-706-8522</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로916번길 5 3층 302호</t>
+          <t>경기도 성남시 분당구 황새울로 324 좋은상호저축은행빌딩 B1층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://m.booking.naver.com/booking/12/bizes/1590839</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -982,10 +990,14 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w40q6m</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -997,13 +1009,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>13</v>
+        <v>952</v>
       </c>
       <c r="Q6" t="n">
-        <v>248</v>
+        <v>2036</v>
       </c>
       <c r="R6" t="n">
-        <v>261</v>
+        <v>2988</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,17 +1024,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2038767341</t>
+          <t>13025013</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2038767341</t>
+          <t>https://m.place.naver.com/place/13025013</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1034,29 +1046,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>쓰리핏 PT 분당미금점</t>
+          <t>데스런 판교점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3fits@naver.com</t>
+          <t>deslun@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1302-3558</t>
+          <t>0507-1412-6347</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 돌마로 47 6층 607호</t>
+          <t>경기도 성남시 분당구 판교역로2번길 38</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://3fitpt.com</t>
+          <t>http://www.deslun.co.kr</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1071,18 +1083,22 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5ty8f</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1091,13 +1107,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>427</v>
+        <v>22</v>
       </c>
       <c r="Q7" t="n">
-        <v>954</v>
+        <v>399</v>
       </c>
       <c r="R7" t="n">
-        <v>1381</v>
+        <v>421</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,51 +1122,51 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1135214262</t>
+          <t>31469573</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1135214262</t>
+          <t>https://m.place.naver.com/place/31469573</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>유앤바디PT 분당수내점</t>
+          <t>스포애니 수내점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>unbody@naver.com</t>
+          <t>spoany012@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>031-714-4729</t>
+          <t>031-712-3362</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 백현로101번길 12 세인프라자 402호</t>
+          <t>경기도 성남시 분당구 돌마로 364 현대제일상가 B1층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/unbody</t>
+          <t>https://m.spoany.co.kr/branch/branch_detail.html?base_seq=MjE=</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1165,15 +1181,19 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w40bmg</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1185,13 +1205,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>118</v>
+        <v>296</v>
       </c>
       <c r="Q8" t="n">
-        <v>166</v>
+        <v>1548</v>
       </c>
       <c r="R8" t="n">
-        <v>284</v>
+        <v>1844</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1200,51 +1220,51 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1853394852</t>
+          <t>31849989</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1853394852</t>
+          <t>https://m.place.naver.com/place/31849989</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>런던피트니스&amp;필라테스 분당이매점</t>
+          <t>리조트휘트니스 PT 판교점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>londoner83@naver.com</t>
+          <t>resort_5@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1406-9679</t>
+          <t>0507-1438-0677</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로779번길 13 오성프라자빌딩 5층</t>
+          <t>경기도 성남시 분당구 운중로 142 판교메디칼타워 6층, 7층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/londoner83</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1254,20 +1274,24 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5ixpk</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1279,13 +1303,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1340</v>
+        <v>413</v>
       </c>
       <c r="Q9" t="n">
-        <v>473</v>
+        <v>714</v>
       </c>
       <c r="R9" t="n">
-        <v>1813</v>
+        <v>1127</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1294,51 +1318,51 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>13530251</t>
+          <t>35524502</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13530251</t>
+          <t>https://m.place.naver.com/place/35524502</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>머슬짐 PT 분당정자점</t>
+          <t>피트니스비엠 분당 서현점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>musclegym9679@naver.com</t>
+          <t>ksk2023@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1405-9679</t>
+          <t>0507-1443-0942</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로343번길 10-6 동원빌딩 4층</t>
+          <t>경기도 성남시 분당구 돌마로 482 주영빌딩 지하 1층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/musclegym9679</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1348,20 +1372,24 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wf09ma8</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1369,17 +1397,17 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>215</v>
+        <v>513</v>
       </c>
       <c r="Q10" t="n">
-        <v>281</v>
+        <v>684</v>
       </c>
       <c r="R10" t="n">
-        <v>496</v>
+        <v>1197</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1388,17 +1416,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1975809201</t>
+          <t>36333115</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1975809201</t>
+          <t>https://m.place.naver.com/place/36333115</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1410,25 +1438,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>렛미PT&amp;필라테스스튜디오 분당야탑점</t>
+          <t>핏불짐 판교점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>let_me_pt_official@naver.com</t>
+          <t>fitbullgym@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0507-1430-9683</t>
+        </is>
+      </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 야탑로69번길 21 영진다이비스상가 2층 210호</t>
+          <t>경기도 성남시 분당구 동판교로 61 자유퍼스트프라자2 3층 304호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/let_me_pt_official</t>
+          <t>https://linktr.ee/fitbullgym</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1448,10 +1480,14 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4eqla</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
           <t>X</t>
@@ -1463,13 +1499,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="Q11" t="n">
-        <v>49</v>
+        <v>283</v>
       </c>
       <c r="R11" t="n">
-        <v>129</v>
+        <v>375</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1478,51 +1514,51 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1049956503</t>
+          <t>37814535</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1049956503</t>
+          <t>https://m.place.naver.com/place/37814535</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>스포애니 야탑역점</t>
+          <t>비율라이프 바디코치 여성전용 체형필라테스 PT 야탑점</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>spoany90@naver.com</t>
+          <t>rockrock1256@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1337-9618</t>
+          <t>0507-1445-2430</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로 926 메트로빌딩 8층</t>
+          <t>경기도 성남시 분당구 야탑로69번길 8 2층 바디코치 야탑점</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>http://m.spoany.co.kr/branch/branch_detail.html?base_seq=MTA1</t>
+          <t>https://www.instagram.com/official_bodycoach?igsh=MTF6cmlnd240MTdwMg%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1557,13 +1593,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>707</v>
+        <v>203</v>
       </c>
       <c r="Q12" t="n">
-        <v>1499</v>
+        <v>786</v>
       </c>
       <c r="R12" t="n">
-        <v>2206</v>
+        <v>989</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1572,17 +1608,17 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1115298912</t>
+          <t>1723811790</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1115298912</t>
+          <t>https://m.place.naver.com/place/1723811790</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1594,29 +1630,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>레조나헬스랩PT 정자역점</t>
+          <t>바른몸PT센터</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>resonar_healthlab2@naver.com</t>
+          <t>wlsrkfdl1@naver.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0507-1415-7374</t>
+          <t>0507-1337-9711</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로331번길 11-15 봉우빌딩 3층 301호 레조나헬스랩</t>
+          <t>경기도 성남시 분당구 백현로101번길 20 3층 301호</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/resonar_healthlab</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1626,7 +1662,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1636,10 +1672,14 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4frie</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr">
         <is>
           <t>X</t>
@@ -1651,13 +1691,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="Q13" t="n">
-        <v>258</v>
+        <v>70</v>
       </c>
       <c r="R13" t="n">
-        <v>285</v>
+        <v>75</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1666,17 +1706,17 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1265132759</t>
+          <t>2090651326</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1265132759</t>
+          <t>https://m.place.naver.com/place/2090651326</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1688,29 +1728,29 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>올뉴바디 운동맛집PT 야탑점</t>
+          <t>핏슈브 분당이매점</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>allnewbody@naver.com</t>
+          <t>9_bonhyuk@naver.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0507-1329-3987</t>
+          <t>0507-1486-9921</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 벌말로 44 401호</t>
+          <t>경기도 성남시 분당구 판교로 475 4층 404호</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/allnewbody</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1720,20 +1760,24 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wn6zvel</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr">
         <is>
           <t>X</t>
@@ -1745,13 +1789,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>600</v>
+        <v>17</v>
       </c>
       <c r="Q14" t="n">
-        <v>618</v>
+        <v>163</v>
       </c>
       <c r="R14" t="n">
-        <v>1218</v>
+        <v>180</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1760,17 +1804,17 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>1203378061</t>
+          <t>2032296152</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1203378061</t>
+          <t>https://m.place.naver.com/place/2032296152</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1782,34 +1826,34 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>H GYM PT GT 판교2호점</t>
+          <t>레조나헬스랩PT 정자역점</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>hgym9408@naver.com</t>
+          <t>resonar_healthlab@naver.com</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0507-1353-9408</t>
+          <t>0507-1415-7374</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 운중로 233 302호</t>
+          <t>경기도 성남시 분당구 성남대로331번길 11-15 봉우빌딩 3층 301호 레조나헬스랩</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://hgym.imweb.me</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1819,15 +1863,19 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wc1oegu</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr">
         <is>
           <t>X</t>
@@ -1839,13 +1887,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>279</v>
+        <v>27</v>
       </c>
       <c r="Q15" t="n">
-        <v>420</v>
+        <v>258</v>
       </c>
       <c r="R15" t="n">
-        <v>699</v>
+        <v>285</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1854,17 +1902,17 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>1850894755</t>
+          <t>1265132759</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1850894755</t>
+          <t>https://m.place.naver.com/place/1265132759</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1876,34 +1924,34 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>체온 PT &amp; 필라테스</t>
+          <t>쓰리핏PT 분당정자점</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>cheonpt@naver.com</t>
+          <t>3fitpt@naver.com</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>031-701-2162</t>
+          <t>0507-1409-3559</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 서현로 216 오벨리스크 상가 202호 체온PT&amp;필라테스</t>
+          <t>경기도 성남시 분당구 내정로113번길 4 2층 202호, 203-1호</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/cheonpt</t>
+          <t>https://3fitpt.com</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1918,28 +1966,32 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5vrph</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>84</v>
+        <v>356</v>
       </c>
       <c r="Q16" t="n">
-        <v>403</v>
+        <v>800</v>
       </c>
       <c r="R16" t="n">
-        <v>487</v>
+        <v>1156</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1948,51 +2000,51 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>1080351846</t>
+          <t>1845673431</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1080351846</t>
+          <t>https://m.place.naver.com/place/1845673431</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>제이치피트니스 헬스&amp;PT 미금점</t>
+          <t>쿼드짐</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>redgym_migeum@naver.com</t>
+          <t>quadgym@naver.com</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0507-1332-4462</t>
+          <t>0507-1303-9415</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로 165 지하1층</t>
+          <t>경기도 성남시 분당구 정자일로 121 더샵스타파크 상가1층 b-18호</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/jhfitness_migeum?igsh</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2002,7 +2054,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -2012,10 +2064,14 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wc5w2o</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr">
         <is>
           <t>X</t>
@@ -2027,13 +2083,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1285</v>
+        <v>82</v>
       </c>
       <c r="Q17" t="n">
-        <v>274</v>
+        <v>102</v>
       </c>
       <c r="R17" t="n">
-        <v>1559</v>
+        <v>184</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2042,51 +2098,51 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>1109176574</t>
+          <t>1759307500</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1109176574</t>
+          <t>https://m.place.naver.com/place/1759307500</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>헬스보이짐&amp;필라걸&amp;골프인 분당정자점</t>
+          <t>피트니스웰시 헬스&amp;PT 분당정자점</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>healthboy90_@naver.com</t>
+          <t>healthy-pt@naver.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0507-1419-2436</t>
+          <t>0507-1489-7037</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로331번길 13 7층 701-706호</t>
+          <t>경기도 성남시 분당구 성남대로343번길 12-8 1동 4층</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/healthboy90_/223799590825</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2096,20 +2152,24 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w35x8wg</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr">
         <is>
           <t>X</t>
@@ -2121,13 +2181,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>457</v>
+        <v>531</v>
       </c>
       <c r="Q18" t="n">
-        <v>751</v>
+        <v>469</v>
       </c>
       <c r="R18" t="n">
-        <v>1208</v>
+        <v>1000</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2136,34 +2196,34 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>1989525945</t>
+          <t>1623406875</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1989525945</t>
+          <t>https://m.place.naver.com/place/1623406875</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>바로선운동센터 판교점</t>
+          <t>뭉트니스 야탑</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>coolksh11@naver.com</t>
+          <t>mtns1@naver.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -2171,12 +2231,12 @@
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 동판교로 61 2층 201호</t>
+          <t>경기도 성남시 분당구 장미로 55 장미마을 지하1층</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/coolksh11</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2186,12 +2246,12 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2211,13 +2271,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>22</v>
+        <v>284</v>
       </c>
       <c r="Q19" t="n">
-        <v>185</v>
+        <v>1037</v>
       </c>
       <c r="R19" t="n">
-        <v>207</v>
+        <v>1321</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2226,51 +2286,51 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2015061102</t>
+          <t>1657314482</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2015061102</t>
+          <t>https://m.place.naver.com/place/1657314482</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>헬스보이짐&amp;필라걸 수내점</t>
+          <t>헬스보이짐&amp;필라걸&amp;골프인 분당정자점</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>healthboy40@naver.com</t>
+          <t>healthboy90_@naver.com</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0507-1380-2239</t>
+          <t>0507-1419-2436</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 내정로173번길 49 5층</t>
+          <t>경기도 성남시 분당구 성남대로331번길 13 7층 701-706호</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/healthboy40/223688037867</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2280,20 +2340,24 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wli4sqi</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr">
         <is>
           <t>X</t>
@@ -2305,13 +2369,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>968</v>
+        <v>457</v>
       </c>
       <c r="Q20" t="n">
-        <v>734</v>
+        <v>751</v>
       </c>
       <c r="R20" t="n">
-        <v>1702</v>
+        <v>1208</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -2320,17 +2384,17 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>1973151166</t>
+          <t>1989525945</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1973151166</t>
+          <t>https://m.place.naver.com/place/1989525945</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -2342,29 +2406,29 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>비율라이프 바디코치 여성전용 체형필라테스 PT 야탑점</t>
+          <t>피쓰리짐 PT</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>rockrock1256@naver.com</t>
+          <t>p3gym@naver.com</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0507-1445-2430</t>
+          <t>0507-1346-9079</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 야탑로69번길 8 2층 바디코치 야탑점</t>
+          <t>경기도 성남시 분당구 정자로 13 월드비터 B1 피쓰리짐</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/official_bodycoach?igsh=MTF6cmlnd240MTdwMg%3D%3D&amp;utm_source=qr</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2374,7 +2438,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -2384,10 +2448,14 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w49ipv</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr">
         <is>
           <t>X</t>
@@ -2399,13 +2467,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>203</v>
+        <v>75</v>
       </c>
       <c r="Q21" t="n">
-        <v>786</v>
+        <v>512</v>
       </c>
       <c r="R21" t="n">
-        <v>989</v>
+        <v>587</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2414,51 +2482,51 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>1723811790</t>
+          <t>1847926774</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1723811790</t>
+          <t>https://m.place.naver.com/place/1847926774</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>피트니스비엠 분당 서현점</t>
+          <t>휘트니스클럽S 수내점</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ksk2023@naver.com</t>
+          <t>fitnessclubs12@naver.com</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0507-1443-0942</t>
+          <t>0507-1311-1188</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 돌마로 482 주영빌딩 지하 1층</t>
+          <t>경기도 성남시 분당구 백현로101번길 11 5층</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/fitnessbm._.hyoja</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2468,7 +2536,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -2478,10 +2546,14 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w49zvx</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr">
         <is>
           <t>X</t>
@@ -2493,13 +2565,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>513</v>
+        <v>309</v>
       </c>
       <c r="Q22" t="n">
-        <v>684</v>
+        <v>917</v>
       </c>
       <c r="R22" t="n">
-        <v>1197</v>
+        <v>1226</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -2508,17 +2580,17 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>36333115</t>
+          <t>1228787055</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36333115</t>
+          <t>https://m.place.naver.com/place/1228787055</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -2530,29 +2602,29 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>스포애니 수내점</t>
+          <t>피트니스비엠 분당 장안타운점</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>spoany012@naver.com</t>
+          <t>fitnessbm77@naver.com</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>031-712-3362</t>
+          <t>0507-1397-6556</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 돌마로 364 현대제일상가 B1층</t>
+          <t>경기도 성남시 분당구 분당로263번길 35 서현굿모닝프라자</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://m.spoany.co.kr/branch/branch_detail.html?base_seq=MjE=</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2562,7 +2634,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2572,10 +2644,14 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w488ca</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr">
         <is>
           <t>X</t>
@@ -2587,13 +2663,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>296</v>
+        <v>279</v>
       </c>
       <c r="Q23" t="n">
-        <v>1548</v>
+        <v>786</v>
       </c>
       <c r="R23" t="n">
-        <v>1844</v>
+        <v>1065</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -2602,51 +2678,55 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>31849989</t>
+          <t>20099119</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/31849989</t>
+          <t>https://m.place.naver.com/place/20099119</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>와이짐 PT 분당미금점</t>
+          <t>버핏그라운드 판교</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ygym3018@naver.com</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
+          <t>butfitground@naver.com</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>partner@butfitseoul.com</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0507-1325-3018</t>
+          <t>0507-1329-4325</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로 165 2층 223호, 224호 와이짐 PT 분당미금점</t>
+          <t>경기도 성남시 분당구 판교역로 136 B3007</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ygym3018</t>
+          <t>https://pt.butfitground.com/</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2666,13 +2746,17 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w42raj</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -2681,13 +2765,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1077</v>
+        <v>1765</v>
       </c>
       <c r="Q24" t="n">
-        <v>446</v>
+        <v>250</v>
       </c>
       <c r="R24" t="n">
-        <v>1523</v>
+        <v>2015</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -2696,17 +2780,17 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>1598086500</t>
+          <t>1136752576</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1598086500</t>
+          <t>https://m.place.naver.com/place/1136752576</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -2718,29 +2802,29 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>운동생활 PT 분당야탑점</t>
+          <t>험블 휘트니스 PT</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>an_athletic_life25@naver.com</t>
+          <t>humblefitness@naver.com</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>031-701-1110</t>
+          <t>031-697-8768</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 야탑로69번길 18 2층 202호</t>
+          <t>경기도 성남시 분당구 성남대로331번길 3-3 701호</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/an_athletic_life25</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2750,20 +2834,24 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wnvkt3b</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr">
         <is>
           <t>X</t>
@@ -2771,17 +2859,17 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P25" t="n">
-        <v>86</v>
+        <v>141</v>
       </c>
       <c r="Q25" t="n">
-        <v>549</v>
+        <v>1437</v>
       </c>
       <c r="R25" t="n">
-        <v>635</v>
+        <v>1578</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -2790,17 +2878,17 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>1275463246</t>
+          <t>1134171602</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1275463246</t>
+          <t>https://m.place.naver.com/place/1134171602</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -2812,29 +2900,29 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>브레이브 휘트니스 분당정자점</t>
+          <t>비아핏</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>bravefitness_jeongja@naver.com</t>
+          <t>viafit@naver.com</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0507-1484-0779</t>
+          <t>0507-1379-7507</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 내정로17번길 2 지하1층</t>
+          <t>경기도 성남시 분당구 판교대장로7길 15-2 지하1층,지상1층</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bravefitness_jeongja</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2844,20 +2932,24 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w37pnp4</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr">
         <is>
           <t>X</t>
@@ -2869,13 +2961,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1418</v>
+        <v>26</v>
       </c>
       <c r="Q26" t="n">
-        <v>1226</v>
+        <v>24</v>
       </c>
       <c r="R26" t="n">
-        <v>2644</v>
+        <v>50</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -2884,17 +2976,17 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>1043618213</t>
+          <t>1772663783</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1043618213</t>
+          <t>https://m.place.naver.com/place/1772663783</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -2906,34 +2998,34 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>구스짐 PT 판교점</t>
+          <t>피티세븐 퍼스널트레이닝</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>chlgudrn1@naver.com</t>
+          <t>body2balance@naver.com</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0507-1465-9683</t>
+          <t>0507-1400-9428</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교로 374 스타식스코아2 3층</t>
+          <t>경기도 성남시 분당구 황새울로132번길 22-1 1층 102호 피티세븐</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/9s_gym_pangyo/</t>
+          <t>http://www.pts7.com</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2948,13 +3040,17 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4bej5</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -2963,13 +3059,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>163</v>
+        <v>302</v>
       </c>
       <c r="Q27" t="n">
-        <v>143</v>
+        <v>291</v>
       </c>
       <c r="R27" t="n">
-        <v>306</v>
+        <v>593</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -2978,17 +3074,17 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>1088776551</t>
+          <t>13093618</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1088776551</t>
+          <t>https://m.place.naver.com/place/13093618</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -3000,29 +3096,29 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>휘트니스클럽S 수내점</t>
+          <t>헬스보이짐&amp;필라걸 수내점</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>fitnessclubs12@naver.com</t>
+          <t>healthboy40@naver.com</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0507-1311-1188</t>
+          <t>0507-1380-2239</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 백현로101번길 11 5층</t>
+          <t>경기도 성남시 분당구 내정로173번길 49 5층</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://smartstore.naver.com/fitnessclubs12</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3032,7 +3128,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -3042,10 +3138,14 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4laa0</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr">
         <is>
           <t>X</t>
@@ -3057,13 +3157,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>309</v>
+        <v>968</v>
       </c>
       <c r="Q28" t="n">
-        <v>917</v>
+        <v>734</v>
       </c>
       <c r="R28" t="n">
-        <v>1226</v>
+        <v>1702</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -3072,34 +3172,34 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>1228787055</t>
+          <t>1973151166</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1228787055</t>
+          <t>https://m.place.naver.com/place/1973151166</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>F45 정자</t>
+          <t>그린공간운동센터 PT 분당미금점</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>eunzzori@naver.com</t>
+          <t>greenplace2020@naver.com</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -3107,12 +3207,12 @@
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 정자일로198번길 24 2층</t>
+          <t>경기도 성남시 분당구 미금일로90번길 32 웰파크 2층 201호</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/f45_jeongja</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3122,7 +3222,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -3147,13 +3247,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>117</v>
+        <v>157</v>
       </c>
       <c r="Q29" t="n">
-        <v>42</v>
+        <v>292</v>
       </c>
       <c r="R29" t="n">
-        <v>159</v>
+        <v>449</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -3162,17 +3262,17 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>1893893702</t>
+          <t>1364310838</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1893893702</t>
+          <t>https://m.place.naver.com/place/1364310838</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -3184,25 +3284,29 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>그린공간운동센터 PT 분당미금점</t>
+          <t>브레이브 휘트니스 분당정자점</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>greenplace2020@naver.com</t>
+          <t>bravefitness_jeongja@naver.com</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>0507-1484-0779</t>
+        </is>
+      </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 미금일로90번길 32 웰파크 2층 201호</t>
+          <t>경기도 성남시 분당구 내정로17번길 2 지하1층</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/greenplace2020</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3212,20 +3316,24 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4lsiz</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr">
         <is>
           <t>X</t>
@@ -3237,13 +3345,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>157</v>
+        <v>1418</v>
       </c>
       <c r="Q30" t="n">
-        <v>292</v>
+        <v>1227</v>
       </c>
       <c r="R30" t="n">
-        <v>449</v>
+        <v>2645</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -3252,56 +3360,56 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>1364310838</t>
+          <t>1043618213</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1364310838</t>
+          <t>https://m.place.naver.com/place/1043618213</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>피트니스웰시 헬스&amp;PT 분당정자점</t>
+          <t>빌드업피트니스 PT 야탑점</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>health-pt@naver.com</t>
+          <t>b2fitness@naver.com</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0507-1489-7037</t>
+          <t>0507-1329-7003</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로343번길 12-8 1동 4층</t>
+          <t>경기도 성남시 분당구 장미로 198 B1 빌드업피트니스PT 야탑점</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/health-pt</t>
+          <t>https://www.buildupfitness.co.kr</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3316,10 +3424,14 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w405jm</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr">
         <is>
           <t>X</t>
@@ -3331,13 +3443,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>531</v>
+        <v>2435</v>
       </c>
       <c r="Q31" t="n">
-        <v>469</v>
+        <v>1017</v>
       </c>
       <c r="R31" t="n">
-        <v>1000</v>
+        <v>3452</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -3346,17 +3458,17 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>1623406875</t>
+          <t>1233503897</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1623406875</t>
+          <t>https://m.place.naver.com/place/1233503897</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -3368,29 +3480,29 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>리파인짐 PT 분당야탑점</t>
+          <t>솔리드짐 PT 수내점</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ksw8591@naver.com</t>
+          <t>ppapers@naver.com</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0507-1380-1864</t>
+          <t>0507-1420-7858</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로926번길 6 302호</t>
+          <t>경기도 성남시 분당구 황새울로258번길 10-7 403호</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ksw8591</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3400,20 +3512,24 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5tbft</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr">
         <is>
           <t>X</t>
@@ -3421,17 +3537,17 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P32" t="n">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="Q32" t="n">
-        <v>310</v>
+        <v>652</v>
       </c>
       <c r="R32" t="n">
-        <v>452</v>
+        <v>797</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -3440,17 +3556,17 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>1297851351</t>
+          <t>1205679892</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1297851351</t>
+          <t>https://m.place.naver.com/place/1205679892</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -3462,29 +3578,29 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>D gym PT 수내역점</t>
+          <t>더바디핏PT 분당야탑2호점</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>hyenggoo1@naver.com</t>
+          <t>xhakxhqk@naver.com</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0507-1438-1374</t>
+          <t>0507-1302-9149</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 황새울로200번길 34 205, 206호</t>
+          <t>경기도 성남시 분당구 성남대로916번길 7 205호 더바디핏PT</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/dgym_official/?igshid=YmMyMTA2M2Y%3D</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3494,7 +3610,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -3504,10 +3620,14 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w1vowru</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr">
         <is>
           <t>X</t>
@@ -3519,13 +3639,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>156</v>
+        <v>452</v>
       </c>
       <c r="Q33" t="n">
-        <v>367</v>
+        <v>723</v>
       </c>
       <c r="R33" t="n">
-        <v>523</v>
+        <v>1175</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -3534,61 +3654,61 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>1234729561</t>
+          <t>1564371057</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1234729561</t>
+          <t>https://m.place.naver.com/place/1564371057</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>비전휘트니스 분당점</t>
+          <t>체온 PT &amp; 필라테스</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>visionfitness555@naver.com</t>
+          <t>juhyunkk717@naver.com</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0507-1439-8755</t>
+          <t>031-701-2162</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 돌마로 46 광천프라자 2층</t>
+          <t>경기도 성남시 분당구 서현로 216 오벨리스크 상가 202호 체온PT&amp;필라테스</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://litt.ly/visionfitness05</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -3598,10 +3718,14 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w47bjf</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr">
         <is>
           <t>X</t>
@@ -3609,17 +3733,17 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P34" t="n">
-        <v>2471</v>
+        <v>84</v>
       </c>
       <c r="Q34" t="n">
-        <v>1919</v>
+        <v>403</v>
       </c>
       <c r="R34" t="n">
-        <v>4390</v>
+        <v>487</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -3628,51 +3752,51 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>1765794431</t>
+          <t>1080351846</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1765794431</t>
+          <t>https://m.place.naver.com/place/1080351846</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>카인드짐 휘트니스 헬스&amp;PT 야탑역점</t>
+          <t>바디밸런스 PT 미금점</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>kindgym28@naver.com</t>
+          <t>xodbs2384@naver.com</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0507-1361-3615</t>
+          <t>0507-1369-2582</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 야탑로81번길 10 아미고타워 B1층 카인드짐 휘트니스 헬스&amp;PT 야탑역점</t>
+          <t>경기도 성남시 분당구 미금일로 65 지하1층 바디밸런스</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/kindgym28</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3682,20 +3806,24 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4ik0d</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr">
         <is>
           <t>X</t>
@@ -3707,13 +3835,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>2034</v>
+        <v>153</v>
       </c>
       <c r="Q35" t="n">
-        <v>1577</v>
+        <v>840</v>
       </c>
       <c r="R35" t="n">
-        <v>3611</v>
+        <v>993</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -3722,74 +3850,78 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>36230651</t>
+          <t>1400263548</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36230651</t>
+          <t>https://m.place.naver.com/place/1400263548</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>빌드업피트니스 PT 야탑점</t>
+          <t>밀라노짐 수내점</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>buildupfitness02@naver.com</t>
+          <t>milanos_1@naver.com</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0507-1329-7003</t>
+          <t>0507-1335-9682</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 장미로 198 B1 빌드업피트니스PT 야탑점</t>
+          <t>경기도 성남시 분당구 내정로166번길 5 원전빌딩 B1층</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://www.buildupfitness.co.kr</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5tvi5</t>
+        </is>
+      </c>
       <c r="N36" t="inlineStr">
         <is>
           <t>X</t>
@@ -3801,13 +3933,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>2435</v>
+        <v>1141</v>
       </c>
       <c r="Q36" t="n">
-        <v>1017</v>
+        <v>696</v>
       </c>
       <c r="R36" t="n">
-        <v>3452</v>
+        <v>1837</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -3816,17 +3948,17 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>1233503897</t>
+          <t>1843911670</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1233503897</t>
+          <t>https://m.place.naver.com/place/1843911670</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -3838,29 +3970,25 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>바디밸런스 PT 미금점</t>
+          <t>렛미PT&amp;필라테스스튜디오 분당야탑점</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>xodbs2384@naver.com</t>
+          <t>let_me_pt_official@naver.com</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>0507-1369-2582</t>
-        </is>
-      </c>
+      <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 미금일로 65 지하1층 바디밸런스</t>
+          <t>경기도 성남시 분당구 야탑로69번길 21 영진다이비스상가 2층 210호</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/xodbs2384/221996918084</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3870,20 +3998,24 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w42m9n</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr">
         <is>
           <t>X</t>
@@ -3895,13 +4027,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>153</v>
+        <v>80</v>
       </c>
       <c r="Q37" t="n">
-        <v>840</v>
+        <v>49</v>
       </c>
       <c r="R37" t="n">
-        <v>993</v>
+        <v>129</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -3910,17 +4042,17 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>1400263548</t>
+          <t>1049956503</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1400263548</t>
+          <t>https://m.place.naver.com/place/1049956503</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -3932,29 +4064,29 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>렛츠핏 야탑점 헬스&amp;PT</t>
+          <t>비전휘트니스 분당점</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>sm8893@naver.com</t>
+          <t>visionfitness555@naver.com</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0507-1305-0298</t>
+          <t>0507-1439-8755</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 벌말로 37 4층 1, 2호</t>
+          <t>경기도 성남시 분당구 돌마로 46 광천프라자 2층</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://bmarket.broj.co.kr/groups/413620357</t>
+          <t>https://litt.ly/visionfitness05</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3974,10 +4106,14 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4gl28</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr">
         <is>
           <t>X</t>
@@ -3989,13 +4125,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>917</v>
+        <v>2471</v>
       </c>
       <c r="Q38" t="n">
-        <v>1289</v>
+        <v>1919</v>
       </c>
       <c r="R38" t="n">
-        <v>2206</v>
+        <v>4390</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -4004,17 +4140,17 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>1320604673</t>
+          <t>1765794431</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1320604673</t>
+          <t>https://m.place.naver.com/place/1765794431</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -4026,29 +4162,25 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>헤일로짐24시 헬스 PT 판교점</t>
+          <t>하이클래스짐 서현점 헬스 PT</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>halogym02@naver.com</t>
+          <t>highclassgym2@naver.com</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>0507-1315-8840</t>
-        </is>
-      </c>
+      <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 대왕판교로 660 유스페이스1 지하1층 127호</t>
+          <t>경기도 성남시 분당구 불정로 382 3층</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://booking.naver.com/booking/6/bizes/933331</t>
+          <t>https://link.inpock.co.kr/highclassgym2</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4058,7 +4190,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -4074,22 +4206,22 @@
       <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P39" t="n">
-        <v>663</v>
+        <v>1336</v>
       </c>
       <c r="Q39" t="n">
-        <v>929</v>
+        <v>1814</v>
       </c>
       <c r="R39" t="n">
-        <v>1592</v>
+        <v>3150</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -4098,34 +4230,34 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>1806695299</t>
+          <t>1974917013</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1806695299</t>
+          <t>https://m.place.naver.com/place/1974917013</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>뭉트니스 야탑</t>
+          <t>바로선운동센터 판교점</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>mtns1@naver.com</t>
+          <t>coolksh11@naver.com</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
@@ -4133,12 +4265,12 @@
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 장미로 55 장미마을 지하1층</t>
+          <t>경기도 성남시 분당구 동판교로 61 2층 201호</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/mtns_leader</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4148,7 +4280,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -4158,10 +4290,14 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wve1811</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr">
         <is>
           <t>X</t>
@@ -4173,13 +4309,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>284</v>
+        <v>22</v>
       </c>
       <c r="Q40" t="n">
-        <v>1036</v>
+        <v>185</v>
       </c>
       <c r="R40" t="n">
-        <v>1320</v>
+        <v>207</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -4188,17 +4324,17 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>1657314482</t>
+          <t>2015061102</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1657314482</t>
+          <t>https://m.place.naver.com/place/2015061102</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -4210,29 +4346,29 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>비아핏</t>
+          <t>머슬짐 PT 분당정자점</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>viafit@naver.com</t>
+          <t>musclegympt_jeongja@naver.com</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0507-1379-7507</t>
+          <t>0507-1405-9679</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교대장로7길 15-2 지하1층,지상1층</t>
+          <t>경기도 성남시 분당구 성남대로343번길 10-6 동원빌딩 4층</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/viafit_no.1</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4242,7 +4378,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -4252,10 +4388,14 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w8j7lk2</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr">
         <is>
           <t>X</t>
@@ -4263,17 +4403,17 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P41" t="n">
-        <v>26</v>
+        <v>215</v>
       </c>
       <c r="Q41" t="n">
-        <v>24</v>
+        <v>281</v>
       </c>
       <c r="R41" t="n">
-        <v>50</v>
+        <v>496</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -4282,51 +4422,47 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>1772663783</t>
+          <t>1975809201</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1772663783</t>
+          <t>https://m.place.naver.com/place/1975809201</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>팀제이맥스 피티 서현점</t>
+          <t>F45 정자</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>teamjmax_sh@naver.com</t>
+          <t>eunzzori@naver.com</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>031-702-8296</t>
-        </is>
-      </c>
+      <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 서현로180번길 13 2층 206호</t>
+          <t>경기도 성남시 분당구 정자일로198번길 24 2층</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/teamjmax_sh</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4336,12 +4472,12 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -4361,13 +4497,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>911</v>
+        <v>117</v>
       </c>
       <c r="Q42" t="n">
-        <v>549</v>
+        <v>42</v>
       </c>
       <c r="R42" t="n">
-        <v>1460</v>
+        <v>159</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -4376,17 +4512,17 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>1639683746</t>
+          <t>1893893702</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1639683746</t>
+          <t>https://m.place.naver.com/place/1893893702</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -4398,52 +4534,56 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>짐휴 PT 분당미금점</t>
+          <t>H GYM PT GT 판교2호점</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>gym_hue@naver.com</t>
+          <t>hgym9408@naver.com</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0507-1369-1180</t>
+          <t>0507-1353-9408</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 돌마로 47 이코노샤르망 5층 509호, 510호</t>
+          <t>경기도 성남시 분당구 운중로 233 302호</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/gym_hue</t>
+          <t>https://hgym.imweb.me</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w47alh</t>
+        </is>
+      </c>
       <c r="N43" t="inlineStr">
         <is>
           <t>X</t>
@@ -4455,13 +4595,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>185</v>
+        <v>279</v>
       </c>
       <c r="Q43" t="n">
-        <v>247</v>
+        <v>420</v>
       </c>
       <c r="R43" t="n">
-        <v>432</v>
+        <v>699</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -4470,17 +4610,17 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>1527774793</t>
+          <t>1850894755</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1527774793</t>
+          <t>https://m.place.naver.com/place/1850894755</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -4492,29 +4632,29 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>블랙스미스짐 헬스PT 판교점</t>
+          <t>머슬짐 PT 분당서현점</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>emmaholic1@naver.com</t>
+          <t>musclegym_@naver.com</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0507-1352-4388</t>
+          <t>0507-1436-9680</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 136 지하2층 비2147호, 비2148호</t>
+          <t>경기도 성남시 분당구 황새울로342번길 19 유성그린빌딩 6층</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>http://blacksmithgym.kr/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4524,7 +4664,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -4534,10 +4674,14 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wgye1u3</t>
+        </is>
+      </c>
       <c r="N44" t="inlineStr">
         <is>
           <t>X</t>
@@ -4549,13 +4693,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>107</v>
+        <v>200</v>
       </c>
       <c r="Q44" t="n">
-        <v>194</v>
+        <v>367</v>
       </c>
       <c r="R44" t="n">
-        <v>301</v>
+        <v>567</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -4564,17 +4708,17 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>1462760829</t>
+          <t>1208748555</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1462760829</t>
+          <t>https://m.place.naver.com/place/1208748555</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -4586,29 +4730,29 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>팀윤짐 헬스PT</t>
+          <t>베러댄 휘트니스 분당야탑점</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>teamyoonsh@naver.com</t>
+          <t>56zqrwcwsv@naver.com</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0507-1363-8855</t>
+          <t>0507-1438-9698</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 황새울로342번길 23 기영프라자 8층</t>
+          <t>경기도 성남시 분당구 야탑로75번길 15 세화빌딩 4층</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/teamyoonsh</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -4618,20 +4762,24 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4o2xj</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr">
         <is>
           <t>X</t>
@@ -4639,17 +4787,17 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P45" t="n">
-        <v>91</v>
+        <v>382</v>
       </c>
       <c r="Q45" t="n">
-        <v>485</v>
+        <v>2093</v>
       </c>
       <c r="R45" t="n">
-        <v>576</v>
+        <v>2475</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -4658,17 +4806,17 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>35523795</t>
+          <t>1013682807</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35523795</t>
+          <t>https://m.place.naver.com/place/1013682807</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -4680,29 +4828,29 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>밀라노짐 수내점</t>
+          <t>짐휴 PT 분당미금점</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>milanos_1@naver.com</t>
+          <t>gym_hue@naver.com</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0507-1335-9682</t>
+          <t>0507-1369-1180</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 내정로166번길 5 원전빌딩 B1층</t>
+          <t>경기도 성남시 분당구 돌마로 47 이코노샤르망 5층 509호, 510호</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/milanogym_s</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4712,7 +4860,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -4722,10 +4870,14 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w486ct</t>
+        </is>
+      </c>
       <c r="N46" t="inlineStr">
         <is>
           <t>X</t>
@@ -4737,13 +4889,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1141</v>
+        <v>186</v>
       </c>
       <c r="Q46" t="n">
-        <v>696</v>
+        <v>247</v>
       </c>
       <c r="R46" t="n">
-        <v>1837</v>
+        <v>433</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -4752,61 +4904,61 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>1843911670</t>
+          <t>1527774793</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1843911670</t>
+          <t>https://m.place.naver.com/place/1527774793</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>피티세븐 퍼스널트레이닝</t>
+          <t>스포애니 미금점</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>body2balance@naver.com</t>
+          <t>spoany_14s@naver.com</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>0507-1400-9428</t>
+          <t>0507-1474-5855</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 황새울로132번길 22-1 1층 102호 피티세븐</t>
+          <t>경기도 성남시 분당구 돌마로 75 미금프라자 8층</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>http://www.pts7.com</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -4816,13 +4968,17 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4hvwb</t>
+        </is>
+      </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
@@ -4831,13 +4987,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>302</v>
+        <v>1084</v>
       </c>
       <c r="Q47" t="n">
-        <v>291</v>
+        <v>1821</v>
       </c>
       <c r="R47" t="n">
-        <v>593</v>
+        <v>2905</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -4846,17 +5002,17 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>13093618</t>
+          <t>20065928</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13093618</t>
+          <t>https://m.place.naver.com/place/20065928</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -4868,29 +5024,29 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>바른몸PT센터</t>
+          <t>좋은습관PTSTUDIO 판교운중</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>wlsrkfdl1@naver.com</t>
+          <t>goodhabitpg@naver.com</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>0507-1337-9711</t>
+          <t>0507-1480-0677</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 백현로101번길 20 3층 301호</t>
+          <t>경기도 성남시 분당구 운중로 142 6층</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/wlsrkfdl1</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -4900,20 +5056,24 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5wyz9</t>
+        </is>
+      </c>
       <c r="N48" t="inlineStr">
         <is>
           <t>X</t>
@@ -4925,13 +5085,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>5</v>
+        <v>63</v>
       </c>
       <c r="Q48" t="n">
-        <v>70</v>
+        <v>29</v>
       </c>
       <c r="R48" t="n">
-        <v>75</v>
+        <v>92</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -4940,17 +5100,17 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>2090651326</t>
+          <t>1070284726</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2090651326</t>
+          <t>https://m.place.naver.com/place/1070284726</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -4962,29 +5122,29 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>쿼드짐</t>
+          <t>리,무브먼트</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>quadgym@naver.com</t>
+          <t>sujin6735@naver.com</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>0507-1303-9415</t>
+          <t>0507-1310-5661</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 정자일로 121 더샵스타파크 상가1층 b-18호</t>
+          <t>경기도 성남시 분당구 운중로 140 메트로골드 203호</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/quadgym</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -4994,20 +5154,24 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4ag69</t>
+        </is>
+      </c>
       <c r="N49" t="inlineStr">
         <is>
           <t>X</t>
@@ -5019,13 +5183,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>82</v>
+        <v>242</v>
       </c>
       <c r="Q49" t="n">
-        <v>102</v>
+        <v>246</v>
       </c>
       <c r="R49" t="n">
-        <v>184</v>
+        <v>488</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -5034,17 +5198,17 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>1759307500</t>
+          <t>1149465061</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1759307500</t>
+          <t>https://m.place.naver.com/place/1149465061</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -5056,29 +5220,29 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>와이투짐 야탑역점</t>
+          <t>포랩 이즈메디운동센터</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>y2gym2@naver.com</t>
+          <t>for_lab2017@naver.com</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>0507-1352-8844</t>
+          <t>0507-1432-1575</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로 912 B1층</t>
+          <t>경기도 성남시 분당구 서현로 192 야베스밸리 9층</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/y2gym2</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -5088,23 +5252,27 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wc1hom</t>
+        </is>
+      </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
@@ -5113,13 +5281,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>380</v>
+        <v>289</v>
       </c>
       <c r="Q50" t="n">
-        <v>1572</v>
+        <v>158</v>
       </c>
       <c r="R50" t="n">
-        <v>1952</v>
+        <v>447</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -5128,17 +5296,17 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>1930702763</t>
+          <t>917204514</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1930702763</t>
+          <t>https://m.place.naver.com/place/917204514</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -5150,55 +5318,59 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>쓰리핏 헬스&amp;PT 서현점</t>
+          <t>와이투짐 야탑역점</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>3fits@naver.com</t>
+          <t>y2gym2@naver.com</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>0507-1388-2211</t>
+          <t>0507-1352-8844</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 불정로 379 서현프라자 지하1층</t>
+          <t>경기도 성남시 분당구 성남대로 912 B1층</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://3fitpt.com</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M51" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4dbfc</t>
+        </is>
+      </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
@@ -5207,13 +5379,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1030</v>
+        <v>380</v>
       </c>
       <c r="Q51" t="n">
-        <v>929</v>
+        <v>1577</v>
       </c>
       <c r="R51" t="n">
-        <v>1959</v>
+        <v>1957</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -5222,51 +5394,51 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>1181952796</t>
+          <t>1930702763</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1181952796</t>
+          <t>https://m.place.naver.com/place/1930702763</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>스포애니 서현역점</t>
+          <t>D gym PT 수내역점</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>spoany22@naver.com</t>
+          <t>hyenggoo1@naver.com</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>031-706-8522</t>
+          <t>0507-1438-1374</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 황새울로 324 좋은상호저축은행빌딩 B1층</t>
+          <t>경기도 성남시 분당구 황새울로200번길 34 205, 206호</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/spoany22</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -5276,20 +5448,24 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M52" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w40pej</t>
+        </is>
+      </c>
       <c r="N52" t="inlineStr">
         <is>
           <t>X</t>
@@ -5301,13 +5477,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>951</v>
+        <v>156</v>
       </c>
       <c r="Q52" t="n">
-        <v>2036</v>
+        <v>367</v>
       </c>
       <c r="R52" t="n">
-        <v>2987</v>
+        <v>523</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -5316,17 +5492,17 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>13025013</t>
+          <t>1234729561</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13025013</t>
+          <t>https://m.place.naver.com/place/1234729561</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -5338,29 +5514,29 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>석세스짐&amp;PT 분당무지개마을점</t>
+          <t>업투 휘트니스 분당판교점</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>successgym-b3@naver.com</t>
+          <t>uptofitness-@naver.com</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>0507-1331-7127</t>
+          <t>0507-1343-8274</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 미금로 36 브리엘프라자 4층</t>
+          <t>경기도 성남시 분당구 동판교로 59 6층 601-605호</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/successgym-b3</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -5370,20 +5546,24 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M53" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5ijhg</t>
+        </is>
+      </c>
       <c r="N53" t="inlineStr">
         <is>
           <t>X</t>
@@ -5395,13 +5575,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>103</v>
+        <v>619</v>
       </c>
       <c r="Q53" t="n">
-        <v>336</v>
+        <v>291</v>
       </c>
       <c r="R53" t="n">
-        <v>439</v>
+        <v>910</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -5410,17 +5590,17 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>1860293712</t>
+          <t>1928497638</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1860293712</t>
+          <t>https://m.place.naver.com/place/1928497638</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -5432,29 +5612,29 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>더바디핏PT 분당야탑2호점</t>
+          <t>팀제이맥스 피티 서현점</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>thebodyfitpt@naver.com</t>
+          <t>linefit91@naver.com</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>0507-1302-9149</t>
+          <t>031-702-8296</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로916번길 7 205호 더바디핏PT</t>
+          <t>경기도 성남시 분당구 서현로180번길 13 2층 206호</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/thebodyfitpt</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -5464,12 +5644,12 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -5489,13 +5669,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>452</v>
+        <v>911</v>
       </c>
       <c r="Q54" t="n">
-        <v>723</v>
+        <v>549</v>
       </c>
       <c r="R54" t="n">
-        <v>1175</v>
+        <v>1460</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -5504,17 +5684,17 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>1564371057</t>
+          <t>1639683746</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1564371057</t>
+          <t>https://m.place.naver.com/place/1639683746</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -5526,29 +5706,29 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>피쓰리짐 PT</t>
+          <t>펠릭스짐 분당점</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>p3gym@naver.com</t>
+          <t>felixgym1@naver.com</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>0507-1346-9079</t>
+          <t>0507-1393-3039</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 정자로 13 월드비터 B1 피쓰리짐</t>
+          <t>경기도 성남시 분당구 장안로 39 2층 201호</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/p3gym</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5558,20 +5738,24 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M55" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w43lts</t>
+        </is>
+      </c>
       <c r="N55" t="inlineStr">
         <is>
           <t>X</t>
@@ -5583,13 +5767,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>75</v>
+        <v>24</v>
       </c>
       <c r="Q55" t="n">
-        <v>512</v>
+        <v>45</v>
       </c>
       <c r="R55" t="n">
-        <v>587</v>
+        <v>69</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -5598,17 +5782,17 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>1847926774</t>
+          <t>1125789234</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1847926774</t>
+          <t>https://m.place.naver.com/place/1125789234</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -5620,29 +5804,29 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>포랩 이즈메디운동센터</t>
+          <t>리파인짐 PT 분당야탑점</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>for_lab2017@naver.com</t>
+          <t>wnszh1864@naver.com</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>0507-1432-1575</t>
+          <t>0507-1380-1864</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 서현로 192 야베스밸리 9층</t>
+          <t>경기도 성남시 분당구 성남대로926번길 6 302호</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/for_lab2017</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5652,20 +5836,24 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M56" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5y773</t>
+        </is>
+      </c>
       <c r="N56" t="inlineStr">
         <is>
           <t>X</t>
@@ -5673,17 +5861,17 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P56" t="n">
-        <v>289</v>
+        <v>142</v>
       </c>
       <c r="Q56" t="n">
-        <v>158</v>
+        <v>310</v>
       </c>
       <c r="R56" t="n">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -5692,17 +5880,17 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>917204514</t>
+          <t>1297851351</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/917204514</t>
+          <t>https://m.place.naver.com/place/1297851351</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -5714,29 +5902,29 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>베러댄 휘트니스 분당야탑점</t>
+          <t>써트짐 PT</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>56zqrwcwsv@naver.com</t>
+          <t>certgym@naver.com</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>0507-1438-9698</t>
+          <t>0507-1367-7665</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 야탑로75번길 15 세화빌딩 4층</t>
+          <t>경기도 성남시 분당구 황새울로214번길 8 207호(수내동, MS프라자)</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/56zqrwcwsv</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -5746,20 +5934,24 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M57" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4dpxc</t>
+        </is>
+      </c>
       <c r="N57" t="inlineStr">
         <is>
           <t>X</t>
@@ -5771,13 +5963,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>382</v>
+        <v>49</v>
       </c>
       <c r="Q57" t="n">
-        <v>2088</v>
+        <v>237</v>
       </c>
       <c r="R57" t="n">
-        <v>2470</v>
+        <v>286</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -5786,17 +5978,17 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>1013682807</t>
+          <t>1331332549</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1013682807</t>
+          <t>https://m.place.naver.com/place/1331332549</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -5808,29 +6000,29 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>험블 휘트니스 PT</t>
+          <t>헬스보이짐 헬스 PT 판교역점</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>humblefitness@naver.com</t>
+          <t>healthboygym78@naver.com</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>031-697-8768</t>
+          <t>0507-1402-1275</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로331번길 3-3 701호</t>
+          <t>경기도 성남시 분당구 대왕판교로606번길 58 지하1층</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/humblefitness</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -5840,20 +6032,24 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M58" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wi2wapb</t>
+        </is>
+      </c>
       <c r="N58" t="inlineStr">
         <is>
           <t>X</t>
@@ -5865,13 +6061,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>141</v>
+        <v>2540</v>
       </c>
       <c r="Q58" t="n">
-        <v>1437</v>
+        <v>323</v>
       </c>
       <c r="R58" t="n">
-        <v>1578</v>
+        <v>2863</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -5880,60 +6076,56 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>1134171602</t>
+          <t>1835201778</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1134171602</t>
+          <t>https://m.place.naver.com/place/1835201778</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>버핏그라운드 판교</t>
+          <t>쓰리핏 헬스&amp;PT 서현점</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>butfitground@naver.com</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>partner@butfitseoul.com</t>
-        </is>
-      </c>
+          <t>3fitpt@naver.com</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>0507-1329-4325</t>
+          <t>0507-1388-2211</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 136 B3007</t>
+          <t>경기도 성남시 분당구 불정로 379 서현프라자 지하1층</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://pt.butfitground.com/</t>
+          <t>https://3fitpt.com</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -5948,10 +6140,14 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M59" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/we9jvgk</t>
+        </is>
+      </c>
       <c r="N59" t="inlineStr">
         <is>
           <t>O</t>
@@ -5963,13 +6159,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>1765</v>
+        <v>1030</v>
       </c>
       <c r="Q59" t="n">
-        <v>250</v>
+        <v>929</v>
       </c>
       <c r="R59" t="n">
-        <v>2015</v>
+        <v>1959</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -5978,17 +6174,17 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>1136752576</t>
+          <t>1181952796</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1136752576</t>
+          <t>https://m.place.naver.com/place/1181952796</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -6000,29 +6196,29 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>제로업PT</t>
+          <t>구스짐 PT 판교점</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>axus2000@naver.com</t>
+          <t>chlgudrn1@naver.com</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>031-623-2775</t>
+          <t>0507-1465-9683</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 느티로 16 7층</t>
+          <t>경기도 성남시 분당구 판교로 374 스타식스코아2 3층</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/zero____up/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -6032,7 +6228,7 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -6042,10 +6238,14 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M60" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wyuehl2</t>
+        </is>
+      </c>
       <c r="N60" t="inlineStr">
         <is>
           <t>X</t>
@@ -6057,13 +6257,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>767</v>
+        <v>163</v>
       </c>
       <c r="Q60" t="n">
-        <v>715</v>
+        <v>143</v>
       </c>
       <c r="R60" t="n">
-        <v>1482</v>
+        <v>306</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -6072,17 +6272,17 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>1975822360</t>
+          <t>1088776551</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1975822360</t>
+          <t>https://m.place.naver.com/place/1088776551</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -6094,29 +6294,29 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>업투 휘트니스 분당판교점</t>
+          <t>린바디핏 PT 판교본점</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>uptofitness-@naver.com</t>
+          <t>leanbodyfitv2@naver.com</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>0507-1343-8274</t>
+          <t>0507-1302-8312</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 동판교로 59 6층 601-605호</t>
+          <t>경기도 성남시 분당구 대왕판교로 670 지하113호</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/uptofitness-</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -6126,38 +6326,42 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M61" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w3fqoyd</t>
+        </is>
+      </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P61" t="n">
-        <v>619</v>
+        <v>135</v>
       </c>
       <c r="Q61" t="n">
-        <v>291</v>
+        <v>108</v>
       </c>
       <c r="R61" t="n">
-        <v>910</v>
+        <v>243</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -6166,17 +6370,17 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>1928497638</t>
+          <t>1699238533</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1928497638</t>
+          <t>https://m.place.naver.com/place/1699238533</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -6188,29 +6392,29 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>핏슈브 분당이매점</t>
+          <t>에버그린PT</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>9_bonhyuk@naver.com</t>
+          <t>evergreen_pt@naver.com</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>0507-1486-9921</t>
+          <t>0507-1314-9993</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교로 475 4층 404호</t>
+          <t>경기도 성남시 분당구 불정로376번길 7 3층일부(304호)</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/9_bonhyuk</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -6220,20 +6424,24 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M62" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w9aimuo</t>
+        </is>
+      </c>
       <c r="N62" t="inlineStr">
         <is>
           <t>X</t>
@@ -6245,13 +6453,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>17</v>
+        <v>81</v>
       </c>
       <c r="Q62" t="n">
-        <v>163</v>
+        <v>252</v>
       </c>
       <c r="R62" t="n">
-        <v>180</v>
+        <v>333</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -6260,51 +6468,51 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>2032296152</t>
+          <t>1749890190</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2032296152</t>
+          <t>https://m.place.naver.com/place/1749890190</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>데스런 판교점</t>
+          <t>렛츠핏 야탑점 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>deslun@naver.com</t>
+          <t>sm8893@naver.com</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>0507-1412-6347</t>
+          <t>0507-1305-0298</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로2번길 38</t>
+          <t>경기도 성남시 분당구 벌말로 37 4층 1, 2호</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>http://www.deslun.co.kr</t>
+          <t>https://bmarket.broj.co.kr/groups/413620357</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -6324,10 +6532,14 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M63" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4w1w0</t>
+        </is>
+      </c>
       <c r="N63" t="inlineStr">
         <is>
           <t>X</t>
@@ -6339,13 +6551,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>22</v>
+        <v>917</v>
       </c>
       <c r="Q63" t="n">
-        <v>398</v>
+        <v>1289</v>
       </c>
       <c r="R63" t="n">
-        <v>420</v>
+        <v>2206</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -6354,17 +6566,17 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>31469573</t>
+          <t>1320604673</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/31469573</t>
+          <t>https://m.place.naver.com/place/1320604673</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -6376,29 +6588,29 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>써트짐 PT</t>
+          <t>올뉴바디 운동맛집PT 야탑점</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>certgym@naver.com</t>
+          <t>allnewbody@naver.com</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>0507-1367-7665</t>
+          <t>0507-1329-3987</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 황새울로214번길 8 207호(수내동, MS프라자)</t>
+          <t>경기도 성남시 분당구 벌말로 44 401호</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/cert.gym.official</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -6408,7 +6620,7 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -6418,10 +6630,14 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M64" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4mcia</t>
+        </is>
+      </c>
       <c r="N64" t="inlineStr">
         <is>
           <t>X</t>
@@ -6433,13 +6649,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>49</v>
+        <v>600</v>
       </c>
       <c r="Q64" t="n">
-        <v>237</v>
+        <v>618</v>
       </c>
       <c r="R64" t="n">
-        <v>286</v>
+        <v>1218</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -6448,51 +6664,51 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>1331332549</t>
+          <t>1203378061</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1331332549</t>
+          <t>https://m.place.naver.com/place/1203378061</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>펠릭스짐 분당점</t>
+          <t>카인드짐 휘트니스 헬스&amp;PT 야탑역점</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>felixgym1@naver.com</t>
+          <t>kindgym28@naver.com</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>0507-1393-3039</t>
+          <t>0507-1361-3615</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 장안로 39 2층 201호</t>
+          <t>경기도 성남시 분당구 야탑로81번길 10 아미고타워 B1층 카인드짐 휘트니스 헬스&amp;PT 야탑역점</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/felixgym__</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -6502,7 +6718,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -6512,10 +6728,14 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M65" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wmuqdfb</t>
+        </is>
+      </c>
       <c r="N65" t="inlineStr">
         <is>
           <t>X</t>
@@ -6527,13 +6747,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>24</v>
+        <v>2034</v>
       </c>
       <c r="Q65" t="n">
-        <v>45</v>
+        <v>1577</v>
       </c>
       <c r="R65" t="n">
-        <v>69</v>
+        <v>3611</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -6542,17 +6762,17 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>1125789234</t>
+          <t>36230651</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1125789234</t>
+          <t>https://m.place.naver.com/place/36230651</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -6564,29 +6784,29 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>스포애니 미금점</t>
+          <t>헤일로짐24시 헬스 PT 판교점</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>spoany_14s@naver.com</t>
+          <t>halogym02@naver.com</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>0507-1474-5855</t>
+          <t>0507-1315-8840</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 돌마로 75 미금프라자 8층</t>
+          <t>경기도 성남시 분당구 대왕판교로 660 유스페이스1 지하1층 127호</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/spoany14/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6596,7 +6816,7 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -6606,28 +6826,32 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M66" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wcfevb4</t>
+        </is>
+      </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P66" t="n">
-        <v>1084</v>
+        <v>663</v>
       </c>
       <c r="Q66" t="n">
-        <v>1821</v>
+        <v>930</v>
       </c>
       <c r="R66" t="n">
-        <v>2905</v>
+        <v>1593</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -6636,17 +6860,17 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>20065928</t>
+          <t>1806695299</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/20065928</t>
+          <t>https://m.place.naver.com/place/1806695299</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -6658,29 +6882,29 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>리조트휘트니스 PT 판교점</t>
+          <t>블랙스미스짐 헬스PT 판교점</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>resort_5@naver.com</t>
+          <t>emmaholic1@naver.com</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>0507-1438-0677</t>
+          <t>0507-1352-4388</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 운중로 142 판교메디칼타워 6층, 7층</t>
+          <t>경기도 성남시 분당구 판교역로 136 지하2층 비2147호, 비2148호</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/resortfitness__pangyo/</t>
+          <t>http://blacksmithgym.kr/</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -6700,10 +6924,14 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M67" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w41p6u</t>
+        </is>
+      </c>
       <c r="N67" t="inlineStr">
         <is>
           <t>X</t>
@@ -6715,13 +6943,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>413</v>
+        <v>107</v>
       </c>
       <c r="Q67" t="n">
-        <v>714</v>
+        <v>194</v>
       </c>
       <c r="R67" t="n">
-        <v>1127</v>
+        <v>301</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -6730,17 +6958,17 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>35524502</t>
+          <t>1462760829</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35524502</t>
+          <t>https://m.place.naver.com/place/1462760829</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -6752,29 +6980,29 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>머슬짐 PT 분당서현점</t>
+          <t>제로업PT</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>musclegym_@naver.com</t>
+          <t>linefit91@naver.com</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>0507-1436-9680</t>
+          <t>031-623-2775</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 황새울로342번길 19 유성그린빌딩 6층</t>
+          <t>경기도 성남시 분당구 느티로 16 7층</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/musclegym_</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -6784,12 +7012,12 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -6809,13 +7037,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>200</v>
+        <v>767</v>
       </c>
       <c r="Q68" t="n">
-        <v>367</v>
+        <v>715</v>
       </c>
       <c r="R68" t="n">
-        <v>567</v>
+        <v>1482</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -6824,70 +7052,78 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>1208748555</t>
+          <t>1975822360</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1208748555</t>
+          <t>https://m.place.naver.com/place/1975822360</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>하이클래스짐 서현점 헬스 PT</t>
+          <t>와이짐 PT 분당미금점</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>highclassgym2@naver.com</t>
+          <t>ygym3018@naver.com</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
-      <c r="E69" t="inlineStr"/>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>0507-1325-3018</t>
+        </is>
+      </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 불정로 382 3층</t>
+          <t>경기도 성남시 분당구 성남대로 165 2층 223호, 224호 와이짐 PT 분당미금점</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>https://link.inpock.co.kr/highclassgym2</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M69" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wc3fm7</t>
+        </is>
+      </c>
       <c r="N69" t="inlineStr">
         <is>
           <t>X</t>
@@ -6899,13 +7135,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>1336</v>
+        <v>1077</v>
       </c>
       <c r="Q69" t="n">
-        <v>1814</v>
+        <v>446</v>
       </c>
       <c r="R69" t="n">
-        <v>3150</v>
+        <v>1523</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -6914,17 +7150,17 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>1974917013</t>
+          <t>1598086500</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1974917013</t>
+          <t>https://m.place.naver.com/place/1598086500</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -6936,34 +7172,34 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>에버그린PT</t>
+          <t>쓰리핏 PT 분당미금점</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>evergreen_pt@naver.com</t>
+          <t>3fitpt@naver.com</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>0507-1314-9993</t>
+          <t>0507-1302-3558</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 불정로376번길 7 3층일부(304호)</t>
+          <t>경기도 성남시 분당구 돌마로 47 6층 607호</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/evergreen_pt</t>
+          <t>https://3fitpt.com</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -6978,13 +7214,17 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M70" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5wfyo</t>
+        </is>
+      </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
@@ -6993,13 +7233,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>81</v>
+        <v>427</v>
       </c>
       <c r="Q70" t="n">
-        <v>252</v>
+        <v>954</v>
       </c>
       <c r="R70" t="n">
-        <v>333</v>
+        <v>1381</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -7008,17 +7248,17 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>1749890190</t>
+          <t>1135214262</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1749890190</t>
+          <t>https://m.place.naver.com/place/1135214262</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -7030,29 +7270,29 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>좋은습관PTSTUDIO 판교운중</t>
+          <t>유앤바디PT 분당수내점</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>goodhabitpg@naver.com</t>
+          <t>unbody@naver.com</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>0507-1480-0677</t>
+          <t>031-714-4729</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 운중로 142 6층</t>
+          <t>경기도 성남시 분당구 백현로101번길 12 세인프라자 402호</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/goodhabit_pangyo/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -7062,7 +7302,7 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -7072,10 +7312,14 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M71" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4b6la</t>
+        </is>
+      </c>
       <c r="N71" t="inlineStr">
         <is>
           <t>X</t>
@@ -7087,13 +7331,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>63</v>
+        <v>118</v>
       </c>
       <c r="Q71" t="n">
-        <v>29</v>
+        <v>167</v>
       </c>
       <c r="R71" t="n">
-        <v>92</v>
+        <v>285</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -7102,74 +7346,78 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>1070284726</t>
+          <t>1853394852</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1070284726</t>
+          <t>https://m.place.naver.com/place/1853394852</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>피트니스비엠 분당 장안타운점</t>
+          <t>석세스짐&amp;PT 분당무지개마을점</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>fitnessbm77@naver.com</t>
+          <t>successgym-b3@naver.com</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>0507-1397-6556</t>
+          <t>0507-1331-7127</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 분당로263번길 35 서현굿모닝프라자</t>
+          <t>경기도 성남시 분당구 미금로 36 브리엘프라자 4층</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/fitnessbm77</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M72" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w45gyo</t>
+        </is>
+      </c>
       <c r="N72" t="inlineStr">
         <is>
           <t>X</t>
@@ -7181,13 +7429,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>279</v>
+        <v>103</v>
       </c>
       <c r="Q72" t="n">
-        <v>786</v>
+        <v>336</v>
       </c>
       <c r="R72" t="n">
-        <v>1065</v>
+        <v>439</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -7196,51 +7444,51 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>20099119</t>
+          <t>1860293712</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/20099119</t>
+          <t>https://m.place.naver.com/place/1860293712</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>핏불짐 판교점</t>
+          <t>와이피트니스 헬스&amp;PT 분당야탑점</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>fitbullgym@naver.com</t>
+          <t>yfitness02@naver.com</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>0507-1430-9683</t>
+          <t>0507-1430-1729</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 동판교로 61 자유퍼스트프라자2 3층 304호</t>
+          <t>경기도 성남시 분당구 벌말로40번길 5-1 지하1층</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://linktr.ee/fitbullgym</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -7250,23 +7498,27 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M73" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w92hhxq</t>
+        </is>
+      </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
@@ -7275,13 +7527,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="Q73" t="n">
-        <v>283</v>
+        <v>55</v>
       </c>
       <c r="R73" t="n">
-        <v>375</v>
+        <v>160</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
@@ -7290,51 +7542,51 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>37814535</t>
+          <t>2013735870</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37814535</t>
+          <t>https://m.place.naver.com/place/2013735870</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>헬스보이짐 헬스 PT 판교역점</t>
+          <t>스포애니 야탑역점</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>healthboygym78@naver.com</t>
+          <t>spoany90@naver.com</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>0507-1402-1275</t>
+          <t>0507-1337-9618</t>
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 대왕판교로606번길 58 지하1층</t>
+          <t>경기도 성남시 분당구 성남대로 926 메트로빌딩 8층</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/healthboygym78/223380215625</t>
+          <t>http://m.spoany.co.kr/branch/branch_detail.html?base_seq=MTA1</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -7349,15 +7601,19 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M74" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5il7f</t>
+        </is>
+      </c>
       <c r="N74" t="inlineStr">
         <is>
           <t>X</t>
@@ -7369,13 +7625,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>2540</v>
+        <v>707</v>
       </c>
       <c r="Q74" t="n">
-        <v>323</v>
+        <v>1499</v>
       </c>
       <c r="R74" t="n">
-        <v>2863</v>
+        <v>2206</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -7384,51 +7640,51 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>1835201778</t>
+          <t>1115298912</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1835201778</t>
+          <t>https://m.place.naver.com/place/1115298912</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>솔리드짐 PT 수내점</t>
+          <t>런던피트니스&amp;필라테스 분당이매점</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>ppapers@naver.com</t>
+          <t>londoner83@naver.com</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>0507-1420-7858</t>
+          <t>0507-1406-9679</t>
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 황새울로258번길 10-7 403호</t>
+          <t>경기도 성남시 분당구 성남대로779번길 13 오성프라자빌딩 5층</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/solid_gym1</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -7438,7 +7694,7 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -7448,10 +7704,14 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M75" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4pnpp</t>
+        </is>
+      </c>
       <c r="N75" t="inlineStr">
         <is>
           <t>X</t>
@@ -7463,13 +7723,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>145</v>
+        <v>1340</v>
       </c>
       <c r="Q75" t="n">
-        <v>652</v>
+        <v>473</v>
       </c>
       <c r="R75" t="n">
-        <v>797</v>
+        <v>1813</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
@@ -7478,17 +7738,17 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>1205679892</t>
+          <t>13530251</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1205679892</t>
+          <t>https://m.place.naver.com/place/13530251</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -7500,55 +7760,59 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>쓰리핏PT 분당정자점</t>
+          <t>리커브 피티 앤 본척척 재활 센터 야탑점</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>3fits@naver.com</t>
+          <t>recurvept@naver.com</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>0507-1409-3559</t>
+          <t>0507-1441-8303</t>
         </is>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 내정로113번길 4 2층 202호, 203-1호</t>
+          <t>경기도 성남시 분당구 성남대로916번길 5 3층 302호</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>https://3fitpt.com</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M76" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4gwff2</t>
+        </is>
+      </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
@@ -7557,13 +7821,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>357</v>
+        <v>13</v>
       </c>
       <c r="Q76" t="n">
-        <v>800</v>
+        <v>248</v>
       </c>
       <c r="R76" t="n">
-        <v>1157</v>
+        <v>261</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -7572,17 +7836,17 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>1845673431</t>
+          <t>2038767341</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1845673431</t>
+          <t>https://m.place.naver.com/place/2038767341</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/분당_PT.xlsx
+++ b/naver-place-crawler/results_health/분당_PT.xlsx
@@ -422,12 +422,12 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="49" customWidth="1" min="7" max="7"/>
-    <col width="45" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="Q2" t="n">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="R2" t="n">
-        <v>1257</v>
+        <v>1259</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -747,34 +747,38 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>레조나헬스랩PT 정자역점</t>
+          <t>버핏그라운드 판교</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>resonar_healthlab2@naver.com</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>butfitground@naver.com</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>partner@butfitseoul.com</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1415-7374</t>
+          <t>0507-1329-4325</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로331번길 11-15 봉우빌딩 3층 301호 레조나헬스랩</t>
+          <t>경기도 성남시 분당구 판교역로 136 B3007</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/resonar_healthlab</t>
+          <t>https://pt.butfitground.com/</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -789,7 +793,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -800,7 +804,7 @@
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -809,13 +813,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>27</v>
+        <v>1765</v>
       </c>
       <c r="Q4" t="n">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="R4" t="n">
-        <v>285</v>
+        <v>2015</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,12 +828,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1265132759</t>
+          <t>1136752576</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1265132759</t>
+          <t>https://m.place.naver.com/place/1136752576</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -846,34 +850,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>구스짐 PT 판교점</t>
+          <t>버핏그라운드 PT 판교</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>chlgudrn1@naver.com</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>butfitground@naver.com</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>butfitseoul@butfitseoul.com</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1465-9683</t>
+          <t>0507-1417-1133</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교로 374 스타식스코아2 3층</t>
+          <t>경기도 성남시 분당구 판교역로 136 B3007호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/9s_gym_pangyo/</t>
+          <t>https://www.butfitground.com/4steppt</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -883,7 +891,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -894,7 +902,7 @@
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -903,13 +911,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>163</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>143</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>306</v>
+        <v>0</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,12 +926,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1088776551</t>
+          <t>2029680813</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1088776551</t>
+          <t>https://m.place.naver.com/place/2029680813</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">

--- a/naver-place-crawler/results_health/분당_PT.xlsx
+++ b/naver-place-crawler/results_health/분당_PT.xlsx
@@ -417,22 +417,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:V76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="29" customWidth="1" min="3" max="3"/>
-    <col width="29" customWidth="1" min="4" max="4"/>
+    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
-    <col width="42" customWidth="1" min="8" max="8"/>
+    <col width="50" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -564,29 +564,25 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>메이크어바디 헬스 PT 미금점</t>
+          <t>뭉트니스 야탑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>makeabody1@naver.com</t>
+          <t>mtns1@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0507-1407-3242</t>
-        </is>
-      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 돌마로 67 5층</t>
+          <t>경기도 성남시 분당구 장미로 55 장미마을 지하1층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/make_a__body</t>
+          <t>https://www.instagram.com/mtns_leader</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -621,13 +617,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>475</v>
+        <v>284</v>
       </c>
       <c r="Q2" t="n">
-        <v>784</v>
+        <v>1037</v>
       </c>
       <c r="R2" t="n">
-        <v>1259</v>
+        <v>1321</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,17 +632,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1315101138</t>
+          <t>1657314482</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1315101138</t>
+          <t>https://m.place.naver.com/place/1657314482</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -658,29 +654,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>레조나헬스랩PT 서판교점</t>
+          <t>밀라노짐 수내점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>resonar_healthlab@naver.com</t>
+          <t>milanos_1@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1411-1104</t>
+          <t>0507-1335-9682</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교공원로2길 9 4층 레조나헬스랩PT 서판교점</t>
+          <t>경기도 성남시 분당구 내정로166번길 5 원전빌딩 B1층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/resonar_healthlab</t>
+          <t>http://www.instagram.com/milanogym_s</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -695,7 +691,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -715,13 +711,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>56</v>
+        <v>1141</v>
       </c>
       <c r="Q3" t="n">
-        <v>202</v>
+        <v>696</v>
       </c>
       <c r="R3" t="n">
-        <v>258</v>
+        <v>1837</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,55 +726,51 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1644348689</t>
+          <t>1843911670</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1644348689</t>
+          <t>https://m.place.naver.com/place/1843911670</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>버핏그라운드 판교</t>
+          <t>리,무브먼트</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>butfitground@naver.com</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>partner@butfitseoul.com</t>
-        </is>
-      </c>
+          <t>sujin6735@naver.com</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1329-4325</t>
+          <t>0507-1310-5661</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 136 B3007</t>
+          <t>경기도 성남시 분당구 운중로 140 메트로골드 203호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://pt.butfitground.com/</t>
+          <t>https://www.instagram.com/re__movement</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -793,7 +785,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -804,7 +796,7 @@
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -813,13 +805,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1765</v>
+        <v>242</v>
       </c>
       <c r="Q4" t="n">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="R4" t="n">
-        <v>2015</v>
+        <v>488</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -828,60 +820,56 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1136752576</t>
+          <t>1149465061</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1136752576</t>
+          <t>https://m.place.naver.com/place/1149465061</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>버핏그라운드 PT 판교</t>
+          <t>스포애니 미금점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>butfitground@naver.com</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>butfitseoul@butfitseoul.com</t>
-        </is>
-      </c>
+          <t>spoany_14s@naver.com</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1417-1133</t>
+          <t>0507-1474-5855</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 136 B3007호</t>
+          <t>경기도 성남시 분당구 돌마로 75 미금프라자 8층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.butfitground.com/4steppt</t>
+          <t>https://www.instagram.com/spoany14/</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -891,7 +879,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -902,7 +890,7 @@
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -911,13 +899,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1086</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>1825</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2911</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -926,35 +914,51 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2029680813</t>
+          <t>20065928</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2029680813</t>
+          <t>https://m.place.naver.com/place/20065928</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>머슬짐 PT 분당정자점</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>musclegym9679@naver.com</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0507-1405-9679</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>주소</t>
+          <t>경기도 성남시 분당구 성남대로343번길 10-6 동원빌딩 4층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/musclegym9679</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -964,12 +968,12 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -989,13 +993,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>215</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>281</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>496</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1004,35 +1008,51 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>7544685</t>
+          <t>1975809201</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/7544685</t>
+          <t>https://m.place.naver.com/place/1975809201</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>업투 휘트니스 분당판교점</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>uptofitness-@naver.com</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0507-1343-8274</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>주소</t>
+          <t>경기도 성남시 분당구 동판교로 59 6층 601-605호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/uptofitness-</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1042,12 +1062,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1063,17 +1083,17 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>620</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>291</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>911</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1082,35 +1102,51 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2600001</t>
+          <t>1928497638</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2600001</t>
+          <t>https://m.place.naver.com/place/1928497638</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>피트니스비엠 분당 서현점</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>ksk2023@naver.com</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0507-1443-0942</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>주소</t>
+          <t>경기도 성남시 분당구 돌마로 482 주영빌딩 지하 1층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/fitnessbm._.hyoja</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1120,7 +1156,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1141,17 +1177,17 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>515</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>684</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1199</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1160,35 +1196,51 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>7167332</t>
+          <t>36333115</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/7167332</t>
+          <t>https://m.place.naver.com/place/36333115</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr"/>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>헬스보이짐&amp;필라걸 수내점</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>healthboy40@naver.com</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0507-1380-2239</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>주소</t>
+          <t>경기도 성남시 분당구 내정로173번길 49 5층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/healthboy40/223688037867</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1198,12 +1250,12 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1219,17 +1271,17 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>968</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>737</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1705</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1238,35 +1290,51 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>7540516</t>
+          <t>1973151166</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/7540516</t>
+          <t>https://m.place.naver.com/place/1973151166</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr"/>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>체온 PT &amp; 필라테스</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>cheonpt@naver.com</t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>031-701-2162</t>
+        </is>
+      </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>주소</t>
+          <t>경기도 성남시 분당구 서현로 216 오벨리스크 상가 202호 체온PT&amp;필라테스</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/cheonpt</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1276,12 +1344,12 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1301,13 +1369,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>408</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>492</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1316,35 +1384,51 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>7536599</t>
+          <t>1080351846</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/7536599</t>
+          <t>https://m.place.naver.com/place/1080351846</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>포랩 이즈메디운동센터</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>for_lab2017@naver.com</t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0507-1432-1575</t>
+        </is>
+      </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>주소</t>
+          <t>경기도 성남시 분당구 서현로 192 야베스밸리 9층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/for_lab2017</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1354,12 +1438,12 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1375,17 +1459,17 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>289</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>158</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>447</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1394,35 +1478,51 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2400001</t>
+          <t>917204514</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2400001</t>
+          <t>https://m.place.naver.com/place/917204514</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr"/>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>운동생활 PT 분당야탑점</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>an_athletic_life25@naver.com</t>
+        </is>
+      </c>
       <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>031-701-1110</t>
+        </is>
+      </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>주소</t>
+          <t>경기도 성남시 분당구 야탑로69번길 18 2층 202호</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/an_athletic_life25</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1432,12 +1532,12 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1457,13 +1557,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>549</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>635</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1472,17 +1572,6141 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>7619261</t>
+          <t>1275463246</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/7619261</t>
+          <t>https://m.place.naver.com/place/1275463246</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>유앤바디PT 분당수내점</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>unbody@naver.com</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>031-714-4729</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 백현로101번길 12 세인프라자 402호</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/unbody</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>118</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>167</v>
+      </c>
+      <c r="R13" t="n">
+        <v>285</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>1853394852</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1853394852</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>카인드짐 휘트니스 헬스&amp;PT 야탑역점</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>kindgym28@naver.com</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0507-1361-3615</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 야탑로81번길 10 아미고타워 B1층 카인드짐 휘트니스 헬스&amp;PT 야탑역점</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/kindgym28</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>2033</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1581</v>
+      </c>
+      <c r="R14" t="n">
+        <v>3614</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>36230651</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/36230651</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>하이클래스짐 서현점 헬스 PT</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>highclassgym2@naver.com</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 불정로 382 3층</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>https://link.inpock.co.kr/highclassgym2</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>1338</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1815</v>
+      </c>
+      <c r="R15" t="n">
+        <v>3153</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>1974917013</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1974917013</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>비율라이프 바디코치 여성전용 체형필라테스 PT 야탑점</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>rockrock1256@naver.com</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0507-1445-2430</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 야탑로69번길 8 2층 바디코치 야탑점</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/official_bodycoach?igsh=MTF6cmlnd240MTdwMg%3D%3D&amp;utm_source=qr</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>203</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>787</v>
+      </c>
+      <c r="R16" t="n">
+        <v>990</v>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>1723811790</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1723811790</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>렛미PT&amp;필라테스스튜디오 분당야탑점</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>let_me_pt_official@naver.com</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 야탑로69번길 21 영진다이비스상가 2층 210호</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/let_me_pt_official</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>80</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>49</v>
+      </c>
+      <c r="R17" t="n">
+        <v>129</v>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>1049956503</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1049956503</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>쓰리핏PT 분당정자점</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>3fits@naver.com</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>0507-1409-3559</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 내정로113번길 4 2층 202호, 203-1호</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>https://3fitpt.com</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>357</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>800</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1157</v>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>1845673431</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1845673431</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>핏불짐 판교점</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>fitbullgym@naver.com</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0507-1430-9683</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 동판교로 61 자유퍼스트프라자2 3층 304호</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>https://linktr.ee/fitbullgym</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>92</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>284</v>
+      </c>
+      <c r="R19" t="n">
+        <v>376</v>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>37814535</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37814535</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>스포애니 수내점</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>spoany012@naver.com</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>031-712-3362</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 돌마로 364 현대제일상가 B1층</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>https://m.spoany.co.kr/branch/branch_detail.html?base_seq=MjE=</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>296</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1550</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1846</v>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>31849989</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/31849989</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>머슬짐 PT 분당서현점</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>musclegym_@naver.com</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>0507-1436-9680</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 황새울로342번길 19 유성그린빌딩 6층</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/musclegym_</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>200</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>367</v>
+      </c>
+      <c r="R21" t="n">
+        <v>567</v>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>1208748555</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1208748555</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>올뉴바디 운동맛집PT 야탑점</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>allnewbody@naver.com</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>0507-1329-3987</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 벌말로 44 401호</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/allnewbody</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>601</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>618</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1219</v>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>1203378061</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1203378061</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>리파인짐 PT 분당야탑점</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>ksw8591@naver.com</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>0507-1380-1864</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 성남대로926번길 6 302호</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/ksw8591</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>142</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>311</v>
+      </c>
+      <c r="R23" t="n">
+        <v>453</v>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>1297851351</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1297851351</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>구스짐 PT 판교점</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>chlgudrn1@naver.com</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>0507-1465-9683</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교로 374 스타식스코아2 3층</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/9s_gym_pangyo/</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>164</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>143</v>
+      </c>
+      <c r="R24" t="n">
+        <v>307</v>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>1088776551</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1088776551</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>솔리드짐 PT 수내점</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>ppapers@naver.com</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>0507-1420-7858</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 황새울로258번길 10-7 403호</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/solid_gym1</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>145</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>652</v>
+      </c>
+      <c r="R25" t="n">
+        <v>797</v>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>1205679892</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1205679892</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>리커브 피티 앤 본척척 재활 센터 야탑점</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>recurvept@naver.com</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>0507-1441-8303</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 성남대로916번길 5 3층 302호</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>https://m.booking.naver.com/booking/12/bizes/1590839</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>249</v>
+      </c>
+      <c r="R26" t="n">
+        <v>262</v>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>2038767341</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2038767341</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>스포애니 서현역점</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>spoany22@naver.com</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>031-706-8522</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 황새울로 324 좋은상호저축은행빌딩 B1층</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/spoany22</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>953</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>2039</v>
+      </c>
+      <c r="R27" t="n">
+        <v>2992</v>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>13025013</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/13025013</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>크레이지핏 PT</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>krazyfit@naver.com</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>0507-1488-5883</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 정자일로198번길 6-5 3층 크레이지핏</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>https://m.booking.naver.com/booking/13/bizes/205740?theme=place&amp;entry=pll&amp;lang=ko&amp;area=pll</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>538</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>1438</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1976</v>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>1628554288</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1628554288</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>헬스보이짐&amp;필라걸&amp;골프인 분당정자점</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>healthboy90_@naver.com</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>0507-1419-2436</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 성남대로331번길 13 7층 701-706호</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/healthboy90_/223799590825</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
+        <v>457</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>753</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1210</v>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>1989525945</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1989525945</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>비전휘트니스 분당점</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>visionfitness555@naver.com</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>0507-1439-8755</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 돌마로 46 광천프라자 2층</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>https://litt.ly/visionfitness05</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
+        <v>2472</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>1917</v>
+      </c>
+      <c r="R30" t="n">
+        <v>4389</v>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>1765794431</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1765794431</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>와이피트니스 헬스&amp;PT 분당야탑점</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>yfitness02@naver.com</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>0507-1430-1729</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 벌말로40번길 5-1 지하1층</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/yfitness02?igsh=MTR6dDl6cW5sNWNxMg%3D%3D&amp;utm_source=qr</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P31" t="n">
+        <v>105</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>55</v>
+      </c>
+      <c r="R31" t="n">
+        <v>160</v>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>2013735870</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2013735870</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>데스런 판교점</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>deslun@naver.com</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>0507-1412-6347</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교역로2번길 38</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>http://www.deslun.co.kr</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>415</v>
+      </c>
+      <c r="R32" t="n">
+        <v>437</v>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>31469573</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/31469573</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>험블 휘트니스 PT</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>humblefitness@naver.com</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>031-697-8768</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 성남대로331번길 3-3 701호</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/humblefitness</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P33" t="n">
+        <v>141</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>1438</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1579</v>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>1134171602</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1134171602</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>석세스짐&amp;PT 분당무지개마을점</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>successgym-b3@naver.com</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>0507-1331-7127</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 미금로 36 브리엘프라자 4층</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/successgym-b3</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P34" t="n">
+        <v>103</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>336</v>
+      </c>
+      <c r="R34" t="n">
+        <v>439</v>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>1860293712</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1860293712</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>휘트니스클럽S 수내점</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>fitnessclubs12@naver.com</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>0507-1311-1188</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 백현로101번길 11 5층</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/fitnessclubs12</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P35" t="n">
+        <v>308</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>917</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1225</v>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>1228787055</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1228787055</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>H GYM PT GT 판교2호점</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>hgym9408@naver.com</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>0507-1353-9408</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 운중로 233 302호</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>https://hgym.imweb.me</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P36" t="n">
+        <v>279</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>421</v>
+      </c>
+      <c r="R36" t="n">
+        <v>700</v>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>1850894755</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1850894755</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>D gym PT 수내역점</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>hyenggoo1@naver.com</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>0507-1438-1374</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 황새울로200번길 34 205, 206호</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/dgym_official/?igshid=YmMyMTA2M2Y%3D</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P37" t="n">
+        <v>156</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>367</v>
+      </c>
+      <c r="R37" t="n">
+        <v>523</v>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>1234729561</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1234729561</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>레조나헬스랩PT 정자역점</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>resonar_healthlab2@naver.com</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>0507-1415-7374</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 성남대로331번길 11-15 봉우빌딩 3층 301호 레조나헬스랩</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/resonar_healthlab</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P38" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>258</v>
+      </c>
+      <c r="R38" t="n">
+        <v>285</v>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>1265132759</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1265132759</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>리조트휘트니스 PT 판교점</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>resort_5@naver.com</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>0507-1438-0677</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 운중로 142 판교메디칼타워 6층, 7층</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/resortfitness__pangyo/</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P39" t="n">
+        <v>413</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>715</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1128</v>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>35524502</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/35524502</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>빌드업피트니스 PT 야탑점</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>buildupfitness02@naver.com</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>0507-1329-7003</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 장미로 198 B1 빌드업피트니스PT 야탑점</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>https://www.buildupfitness.co.kr</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P40" t="n">
+        <v>2436</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>1018</v>
+      </c>
+      <c r="R40" t="n">
+        <v>3454</v>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>1233503897</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1233503897</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>써트짐 PT</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>certgym@naver.com</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>0507-1367-7665</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 황새울로214번길 8 207호(수내동, MS프라자)</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4dpxc</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P41" t="n">
+        <v>49</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>237</v>
+      </c>
+      <c r="R41" t="n">
+        <v>286</v>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>1331332549</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1331332549</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>팀윤짐 헬스PT</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>teamyoonsh@naver.com</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>0507-1363-8855</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 황새울로342번길 23 기영프라자 8층</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wc6ysr</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P42" t="n">
+        <v>91</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>485</v>
+      </c>
+      <c r="R42" t="n">
+        <v>576</v>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>35523795</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/35523795</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>쓰리핏 PT 분당미금점</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>3fitpt@naver.com</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>0507-1302-3558</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 돌마로 47 6층 607호</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>https://3fitpt.com</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5wfyo</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P43" t="n">
+        <v>427</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>954</v>
+      </c>
+      <c r="R43" t="n">
+        <v>1381</v>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>1135214262</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1135214262</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>그린공간운동센터 PT 분당미금점</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>greenplace2020@naver.com</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 미금일로90번길 32 웰파크 2층 201호</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P44" t="n">
+        <v>157</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>292</v>
+      </c>
+      <c r="R44" t="n">
+        <v>449</v>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>1364310838</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1364310838</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>쓰리핏 헬스&amp;PT 서현점</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>3fitpt@naver.com</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>0507-1388-2211</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 불정로 379 서현프라자 지하1층</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>https://3fitpt.com</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/we9jvgk</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P45" t="n">
+        <v>1030</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>929</v>
+      </c>
+      <c r="R45" t="n">
+        <v>1959</v>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>1181952796</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1181952796</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>와이투짐 야탑역점</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>y2gym2@naver.com</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>0507-1352-8844</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 성남대로 912 B1층</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4dbfc</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P46" t="n">
+        <v>382</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>1577</v>
+      </c>
+      <c r="R46" t="n">
+        <v>1959</v>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>1930702763</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1930702763</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>더바디핏PT 분당야탑2호점</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>xhakxhqk@naver.com</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0507-1302-9149</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 성남대로916번길 7 205호 더바디핏PT</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w1vowru</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P47" t="n">
+        <v>452</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>720</v>
+      </c>
+      <c r="R47" t="n">
+        <v>1172</v>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>1564371057</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1564371057</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>피트니스비엠 분당 장안타운점</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>fitnessbm77@naver.com</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0507-1397-6556</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 분당로263번길 35 서현굿모닝프라자</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w488ca</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P48" t="n">
+        <v>279</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>786</v>
+      </c>
+      <c r="R48" t="n">
+        <v>1065</v>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>20099119</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/20099119</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>피트니스웰시 헬스&amp;PT 분당정자점</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>healthy-pt@naver.com</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0507-1489-7037</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 성남대로343번길 12-8 1동 4층</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w35x8wg</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P49" t="n">
+        <v>534</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>470</v>
+      </c>
+      <c r="R49" t="n">
+        <v>1004</v>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>1623406875</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1623406875</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>헬스보이짐 헬스 PT 판교역점</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>healthboygym78@naver.com</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0507-1402-1275</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 대왕판교로606번길 58 지하1층</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wi2wapb</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P50" t="n">
+        <v>2543</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>323</v>
+      </c>
+      <c r="R50" t="n">
+        <v>2866</v>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>1835201778</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1835201778</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>브레이브 휘트니스 분당정자점</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>bravefitness_jeongja@naver.com</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0507-1484-0779</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 내정로17번길 2 지하1층</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4lsiz</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P51" t="n">
+        <v>1419</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>1253</v>
+      </c>
+      <c r="R51" t="n">
+        <v>2672</v>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>1043618213</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1043618213</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>라룬리픽스 재활운동PT센터</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>crewj99@naver.com</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0507-1327-0804</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 느티로 16 젤존타워1 302호 라룬리픽스클리닉</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>https://www.lalunerefix.com</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wc51p4</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P52" t="n">
+        <v>47</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>231</v>
+      </c>
+      <c r="R52" t="n">
+        <v>278</v>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>1679722203</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1679722203</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>베러댄 휘트니스 분당야탑점</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>56zqrwcwsv@naver.com</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>0507-1438-9698</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 야탑로75번길 15 세화빌딩 4층</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4o2xj</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P53" t="n">
+        <v>382</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>2093</v>
+      </c>
+      <c r="R53" t="n">
+        <v>2475</v>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>1013682807</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1013682807</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>바로선운동센터 판교점</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>coolksh11@naver.com</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 동판교로 61 2층 201호</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wve1811</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P54" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>187</v>
+      </c>
+      <c r="R54" t="n">
+        <v>209</v>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>2015061102</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2015061102</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>피쓰리짐 PT</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>p3gym@naver.com</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>0507-1346-9079</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 정자로 13 월드비터 B1 피쓰리짐</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w49ipv</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P55" t="n">
+        <v>75</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>513</v>
+      </c>
+      <c r="R55" t="n">
+        <v>588</v>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>1847926774</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1847926774</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>제로업PT</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>linefit91@naver.com</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>031-623-2775</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 느티로 16 7층</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P56" t="n">
+        <v>772</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>723</v>
+      </c>
+      <c r="R56" t="n">
+        <v>1495</v>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>1975822360</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1975822360</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>비아핏</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>viafit@naver.com</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>0507-1379-7507</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교대장로7길 15-2 지하1층,지상1층</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w37pnp4</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P57" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>24</v>
+      </c>
+      <c r="R57" t="n">
+        <v>50</v>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>1772663783</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1772663783</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>좋은습관PTSTUDIO 판교운중</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>goodhabitpg@naver.com</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>0507-1480-0677</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 운중로 142 6층</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5wyz9</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P58" t="n">
+        <v>63</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>29</v>
+      </c>
+      <c r="R58" t="n">
+        <v>92</v>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>1070284726</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1070284726</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>바른몸PT센터</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>wlsrkfdl1@naver.com</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>0507-1337-9711</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 백현로101번길 20 3층 301호</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4frie</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P59" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>70</v>
+      </c>
+      <c r="R59" t="n">
+        <v>75</v>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>2090651326</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2090651326</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>피티세븐 퍼스널트레이닝</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>body2balance@naver.com</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>0507-1400-9428</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 황새울로132번길 22-1 1층 102호 피티세븐</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>http://www.pts7.com</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4bej5</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P60" t="n">
+        <v>302</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>290</v>
+      </c>
+      <c r="R60" t="n">
+        <v>592</v>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>13093618</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/13093618</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>에버그린PT</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>evergreen_pt@naver.com</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>0507-1314-9993</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 불정로376번길 7 3층일부(304호)</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w9aimuo</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P61" t="n">
+        <v>81</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>252</v>
+      </c>
+      <c r="R61" t="n">
+        <v>333</v>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>1749890190</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1749890190</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>헤일로짐24시 헬스 PT 판교점</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>halogym02@naver.com</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>0507-1315-8840</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 대왕판교로 660 유스페이스1 지하1층 127호</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wcfevb4</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P62" t="n">
+        <v>663</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>933</v>
+      </c>
+      <c r="R62" t="n">
+        <v>1596</v>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>1806695299</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1806695299</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>펠릭스짐 분당점</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>felixgym1@naver.com</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>0507-1393-3039</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 장안로 39 2층 201호</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w43lts</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P63" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>45</v>
+      </c>
+      <c r="R63" t="n">
+        <v>69</v>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>1125789234</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1125789234</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>짐휴 PT 분당미금점</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>gym_hue@naver.com</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>0507-1369-1180</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 돌마로 47 이코노샤르망 5층 509호, 510호</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w486ct</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P64" t="n">
+        <v>187</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>247</v>
+      </c>
+      <c r="R64" t="n">
+        <v>434</v>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>1527774793</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1527774793</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>제이치피트니스 헬스&amp;PT 미금점</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>redgym_migeum@naver.com</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>0507-1332-4462</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 성남대로 165 지하1층</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wzxrxow</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P65" t="n">
+        <v>1286</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>274</v>
+      </c>
+      <c r="R65" t="n">
+        <v>1560</v>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>1109176574</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1109176574</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>바디밸런스 PT 미금점</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>xodbs2384@naver.com</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>0507-1369-2582</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 미금일로 65 지하1층 바디밸런스</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4ik0d</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P66" t="n">
+        <v>153</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>840</v>
+      </c>
+      <c r="R66" t="n">
+        <v>993</v>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>1400263548</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1400263548</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>쿼드짐</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>quadgym@naver.com</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>0507-1303-9415</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 정자일로 121 더샵스타파크 상가1층 b-18호</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wc5w2o</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P67" t="n">
+        <v>82</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>102</v>
+      </c>
+      <c r="R67" t="n">
+        <v>184</v>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>1759307500</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1759307500</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>린바디핏 PT 판교본점</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>leanbodyfitv2@naver.com</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>0507-1302-8312</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 대왕판교로 670 지하113호</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w3fqoyd</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P68" t="n">
+        <v>135</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>108</v>
+      </c>
+      <c r="R68" t="n">
+        <v>243</v>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>1699238533</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1699238533</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>렛츠핏 야탑점 헬스&amp;PT</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>sm8893@naver.com</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>0507-1305-0298</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 벌말로 37 4층 1, 2호</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>https://bmarket.broj.co.kr/groups/413620357</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4w1w0</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P69" t="n">
+        <v>917</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>1291</v>
+      </c>
+      <c r="R69" t="n">
+        <v>2208</v>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>1320604673</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1320604673</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>버핏그라운드 판교</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>butfitground@naver.com</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>partner@butfitseoul.com</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>0507-1329-4325</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교역로 136 B3007</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>https://pt.butfitground.com/</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w42raj</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P70" t="n">
+        <v>1765</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>250</v>
+      </c>
+      <c r="R70" t="n">
+        <v>2015</v>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>1136752576</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1136752576</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>F45 정자</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>eunzzori@naver.com</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 정자일로198번길 24 2층</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/f45_jeongja</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P71" t="n">
+        <v>117</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>42</v>
+      </c>
+      <c r="R71" t="n">
+        <v>159</v>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>1893893702</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1893893702</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>와이짐 PT 분당미금점</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>ygym3018@naver.com</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>0507-1325-3018</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 성남대로 165 2층 223호, 224호 와이짐 PT 분당미금점</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wc3fm7</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P72" t="n">
+        <v>1077</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>446</v>
+      </c>
+      <c r="R72" t="n">
+        <v>1523</v>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>1598086500</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1598086500</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>스포애니 야탑역점</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>spoany90@naver.com</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>0507-1337-9618</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 성남대로 926 메트로빌딩 8층</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>http://m.spoany.co.kr/branch/branch_detail.html?base_seq=MTA1</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5il7f</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P73" t="n">
+        <v>708</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>1504</v>
+      </c>
+      <c r="R73" t="n">
+        <v>2212</v>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>1115298912</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1115298912</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>런던피트니스&amp;필라테스 분당이매점</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>londoner83@naver.com</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>0507-1406-9679</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 성남대로779번길 13 오성프라자빌딩 5층</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4pnpp</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P74" t="n">
+        <v>1340</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>473</v>
+      </c>
+      <c r="R74" t="n">
+        <v>1813</v>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>13530251</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/13530251</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>팀제이맥스 피티 서현점</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>linefit91@naver.com</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>031-702-8296</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 서현로180번길 13 2층 206호</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P75" t="n">
+        <v>910</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>548</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1458</v>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>1639683746</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1639683746</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>핏슈브 야탑이매점</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>9_bonhyuk@naver.com</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>0507-1486-9921</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교로 475 4층 404호</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/9_bonhyuk</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P76" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>163</v>
+      </c>
+      <c r="R76" t="n">
+        <v>180</v>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>2032296152</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2032296152</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/분당_PT.xlsx
+++ b/naver-place-crawler/results_health/분당_PT.xlsx
@@ -564,12 +564,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>뭉트니스 야탑</t>
+          <t>하이클래스짐 서현점 헬스 PT</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>mtns1@naver.com</t>
+          <t>highclassgym2@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
@@ -577,17 +577,17 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 장미로 55 장미마을 지하1층</t>
+          <t>경기도 성남시 분당구 불정로 382 3층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/mtns_leader</t>
+          <t>https://link.inpock.co.kr/highclassgym2</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -597,7 +597,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -617,13 +617,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>284</v>
+        <v>1339</v>
       </c>
       <c r="Q2" t="n">
-        <v>1037</v>
+        <v>1817</v>
       </c>
       <c r="R2" t="n">
-        <v>1321</v>
+        <v>3156</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -632,12 +632,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1657314482</t>
+          <t>1974917013</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1657314482</t>
+          <t>https://m.place.naver.com/place/1974917013</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -649,39 +649,39 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>밀라노짐 수내점</t>
+          <t>비전휘트니스 분당점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>milanos_1@naver.com</t>
+          <t>visionfitness555@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1335-9682</t>
+          <t>0507-1439-8755</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 내정로166번길 5 원전빌딩 B1층</t>
+          <t>경기도 성남시 분당구 돌마로 46 광천프라자 2층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/milanogym_s</t>
+          <t>https://litt.ly/visionfitness05</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -696,10 +696,14 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4gl28</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -711,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1141</v>
+        <v>2473</v>
       </c>
       <c r="Q3" t="n">
-        <v>696</v>
+        <v>1916</v>
       </c>
       <c r="R3" t="n">
-        <v>1837</v>
+        <v>4389</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -726,12 +730,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1843911670</t>
+          <t>1765794431</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1843911670</t>
+          <t>https://m.place.naver.com/place/1765794431</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -743,34 +747,34 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>리,무브먼트</t>
+          <t>제이치피트니스 헬스&amp;PT 미금점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>sujin6735@naver.com</t>
+          <t>redgym_migeum@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1310-5661</t>
+          <t>0507-1332-4462</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 운중로 140 메트로골드 203호</t>
+          <t>경기도 성남시 분당구 성남대로 165 지하1층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/re__movement</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -780,7 +784,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -790,10 +794,14 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wzxrxow</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -805,13 +813,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>242</v>
+        <v>1286</v>
       </c>
       <c r="Q4" t="n">
-        <v>246</v>
+        <v>274</v>
       </c>
       <c r="R4" t="n">
-        <v>488</v>
+        <v>1560</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -820,12 +828,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1149465061</t>
+          <t>1109176574</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1149465061</t>
+          <t>https://m.place.naver.com/place/1109176574</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -837,34 +845,34 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>스포애니 미금점</t>
+          <t>리,무브먼트</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>spoany_14s@naver.com</t>
+          <t>sujin6735@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1474-5855</t>
+          <t>0507-1310-5661</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 돌마로 75 미금프라자 8층</t>
+          <t>경기도 성남시 분당구 운중로 140 메트로골드 203호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/spoany14/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -874,7 +882,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -884,10 +892,14 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4ag69</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -899,13 +911,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1086</v>
+        <v>242</v>
       </c>
       <c r="Q5" t="n">
-        <v>1825</v>
+        <v>246</v>
       </c>
       <c r="R5" t="n">
-        <v>2911</v>
+        <v>488</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -914,12 +926,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>20065928</t>
+          <t>1149465061</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/20065928</t>
+          <t>https://m.place.naver.com/place/1149465061</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -936,29 +948,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>머슬짐 PT 분당정자점</t>
+          <t>핏불짐 판교점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>musclegym9679@naver.com</t>
+          <t>fitbullgym@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1405-9679</t>
+          <t>0507-1430-9683</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로343번길 10-6 동원빌딩 4층</t>
+          <t>경기도 성남시 분당구 동판교로 61 자유퍼스트프라자2 3층 304호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/musclegym9679</t>
+          <t>https://linktr.ee/fitbullgym</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -978,10 +990,14 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4eqla</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -989,17 +1005,17 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>215</v>
+        <v>92</v>
       </c>
       <c r="Q6" t="n">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="R6" t="n">
-        <v>496</v>
+        <v>376</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1008,12 +1024,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1975809201</t>
+          <t>37814535</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1975809201</t>
+          <t>https://m.place.naver.com/place/37814535</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1030,29 +1046,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>업투 휘트니스 분당판교점</t>
+          <t>펠릭스짐 분당점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>uptofitness-@naver.com</t>
+          <t>felixgym1@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1343-8274</t>
+          <t>0507-1393-3039</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 동판교로 59 6층 601-605호</t>
+          <t>경기도 성남시 분당구 장안로 39 2층 201호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/uptofitness-</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1062,20 +1078,24 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w43lts</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1087,13 +1107,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>620</v>
+        <v>24</v>
       </c>
       <c r="Q7" t="n">
-        <v>291</v>
+        <v>45</v>
       </c>
       <c r="R7" t="n">
-        <v>911</v>
+        <v>69</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1102,12 +1122,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1928497638</t>
+          <t>1125789234</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1928497638</t>
+          <t>https://m.place.naver.com/place/1125789234</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1124,29 +1144,25 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>피트니스비엠 분당 서현점</t>
+          <t>F45 정자</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ksk2023@naver.com</t>
+          <t>eunzzori@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0507-1443-0942</t>
-        </is>
-      </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 돌마로 482 주영빌딩 지하 1층</t>
+          <t>경기도 성남시 분당구 정자일로198번길 24 2층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/fitnessbm._.hyoja</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1156,7 +1172,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1181,13 +1197,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>515</v>
+        <v>117</v>
       </c>
       <c r="Q8" t="n">
-        <v>684</v>
+        <v>42</v>
       </c>
       <c r="R8" t="n">
-        <v>1199</v>
+        <v>159</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1196,12 +1212,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>36333115</t>
+          <t>1893893702</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36333115</t>
+          <t>https://m.place.naver.com/place/1893893702</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1218,29 +1234,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>헬스보이짐&amp;필라걸 수내점</t>
+          <t>구스짐 PT 판교점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>healthboy40@naver.com</t>
+          <t>chlgudrn1@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1380-2239</t>
+          <t>0507-1465-9683</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 내정로173번길 49 5층</t>
+          <t>경기도 성남시 분당구 판교로 374 스타식스코아2 3층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/healthboy40/223688037867</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1250,20 +1266,24 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wyuehl2</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1275,13 +1295,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>968</v>
+        <v>165</v>
       </c>
       <c r="Q9" t="n">
-        <v>737</v>
+        <v>143</v>
       </c>
       <c r="R9" t="n">
-        <v>1705</v>
+        <v>308</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1290,12 +1310,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1973151166</t>
+          <t>1088776551</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1973151166</t>
+          <t>https://m.place.naver.com/place/1088776551</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1317,7 +1337,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>cheonpt@naver.com</t>
+          <t>juhyunkk717@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -1334,7 +1354,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/cheonpt</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1344,20 +1364,24 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w47bjf</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1372,10 +1396,10 @@
         <v>84</v>
       </c>
       <c r="Q10" t="n">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="R10" t="n">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1406,29 +1430,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>포랩 이즈메디운동센터</t>
+          <t>크레이지핏 PT</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>for_lab2017@naver.com</t>
+          <t>krazyfit@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1432-1575</t>
+          <t>0507-1488-5883</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 서현로 192 야베스밸리 9층</t>
+          <t>경기도 성남시 분당구 정자일로198번길 6-5 3층 크레이지핏</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/for_lab2017</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1438,20 +1462,24 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w44lbo</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
           <t>X</t>
@@ -1463,13 +1491,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>289</v>
+        <v>539</v>
       </c>
       <c r="Q11" t="n">
-        <v>158</v>
+        <v>1438</v>
       </c>
       <c r="R11" t="n">
-        <v>447</v>
+        <v>1977</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1478,12 +1506,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>917204514</t>
+          <t>1628554288</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/917204514</t>
+          <t>https://m.place.naver.com/place/1628554288</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1500,29 +1528,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>운동생활 PT 분당야탑점</t>
+          <t>에버그린PT</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>an_athletic_life25@naver.com</t>
+          <t>evergreen_pt@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>031-701-1110</t>
+          <t>0507-1314-9993</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 야탑로69번길 18 2층 202호</t>
+          <t>경기도 성남시 분당구 불정로376번길 7 3층일부(304호)</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/an_athletic_life25</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1532,20 +1560,24 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w9aimuo</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr">
         <is>
           <t>X</t>
@@ -1553,17 +1585,17 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="Q12" t="n">
-        <v>549</v>
+        <v>252</v>
       </c>
       <c r="R12" t="n">
-        <v>635</v>
+        <v>334</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1572,12 +1604,12 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1275463246</t>
+          <t>1749890190</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1275463246</t>
+          <t>https://m.place.naver.com/place/1749890190</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -1594,29 +1626,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>유앤바디PT 분당수내점</t>
+          <t>린바디핏 PT 판교본점</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>unbody@naver.com</t>
+          <t>leanbodyfitv2@naver.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>031-714-4729</t>
+          <t>0507-1302-8312</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 백현로101번길 12 세인프라자 402호</t>
+          <t>경기도 성남시 분당구 대왕판교로 670 지하113호</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/unbody</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1626,38 +1658,42 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w3fqoyd</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>118</v>
+        <v>135</v>
       </c>
       <c r="Q13" t="n">
-        <v>167</v>
+        <v>108</v>
       </c>
       <c r="R13" t="n">
-        <v>285</v>
+        <v>243</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1666,12 +1702,12 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1853394852</t>
+          <t>1699238533</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1853394852</t>
+          <t>https://m.place.naver.com/place/1699238533</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -1683,34 +1719,34 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>카인드짐 휘트니스 헬스&amp;PT 야탑역점</t>
+          <t>포랩 이즈메디운동센터</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>kindgym28@naver.com</t>
+          <t>for_lab2017@naver.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0507-1361-3615</t>
+          <t>0507-1432-1575</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 야탑로81번길 10 아미고타워 B1층 카인드짐 휘트니스 헬스&amp;PT 야탑역점</t>
+          <t>경기도 성남시 분당구 서현로 192 야베스밸리 9층</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/kindgym28</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1720,20 +1756,24 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wc1hom</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr">
         <is>
           <t>X</t>
@@ -1745,13 +1785,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>2033</v>
+        <v>289</v>
       </c>
       <c r="Q14" t="n">
-        <v>1581</v>
+        <v>158</v>
       </c>
       <c r="R14" t="n">
-        <v>3614</v>
+        <v>447</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1760,12 +1800,12 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>36230651</t>
+          <t>917204514</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36230651</t>
+          <t>https://m.place.naver.com/place/917204514</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -1777,35 +1817,39 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>하이클래스짐 서현점 헬스 PT</t>
+          <t>브레이브 휘트니스 분당정자점</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>highclassgym2@naver.com</t>
+          <t>bravefitness_jeongja@naver.com</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0507-1484-0779</t>
+        </is>
+      </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 불정로 382 3층</t>
+          <t>경기도 성남시 분당구 내정로17번길 2 지하1층</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://link.inpock.co.kr/highclassgym2</t>
+          <t>https://blog.naver.com/bravefitness_jeongja</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1835,13 +1879,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1338</v>
+        <v>1419</v>
       </c>
       <c r="Q15" t="n">
-        <v>1815</v>
+        <v>1265</v>
       </c>
       <c r="R15" t="n">
-        <v>3153</v>
+        <v>2684</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1850,12 +1894,12 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>1974917013</t>
+          <t>1043618213</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1974917013</t>
+          <t>https://m.place.naver.com/place/1043618213</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -1872,29 +1916,29 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>비율라이프 바디코치 여성전용 체형필라테스 PT 야탑점</t>
+          <t>핏슈브 야탑이매점</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>rockrock1256@naver.com</t>
+          <t>9_bonhyuk@naver.com</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0507-1445-2430</t>
+          <t>0507-1486-9921</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 야탑로69번길 8 2층 바디코치 야탑점</t>
+          <t>경기도 성남시 분당구 판교로 475 4층 404호</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/official_bodycoach?igsh=MTF6cmlnd240MTdwMg%3D%3D&amp;utm_source=qr</t>
+          <t>https://blog.naver.com/9_bonhyuk</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1909,7 +1953,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1929,13 +1973,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>203</v>
+        <v>17</v>
       </c>
       <c r="Q16" t="n">
-        <v>787</v>
+        <v>163</v>
       </c>
       <c r="R16" t="n">
-        <v>990</v>
+        <v>180</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1944,12 +1988,12 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>1723811790</t>
+          <t>2032296152</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1723811790</t>
+          <t>https://m.place.naver.com/place/2032296152</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -1961,30 +2005,34 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>렛미PT&amp;필라테스스튜디오 분당야탑점</t>
+          <t>스포애니 서현역점</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>let_me_pt_official@naver.com</t>
+          <t>spoany22@naver.com</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>031-706-8522</t>
+        </is>
+      </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 야탑로69번길 21 영진다이비스상가 2층 210호</t>
+          <t>경기도 성남시 분당구 황새울로 324 좋은상호저축은행빌딩 B1층</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/let_me_pt_official</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1994,20 +2042,24 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w40q6m</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr">
         <is>
           <t>X</t>
@@ -2019,13 +2071,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>80</v>
+        <v>953</v>
       </c>
       <c r="Q17" t="n">
-        <v>49</v>
+        <v>2039</v>
       </c>
       <c r="R17" t="n">
-        <v>129</v>
+        <v>2992</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2034,12 +2086,12 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>1049956503</t>
+          <t>13025013</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1049956503</t>
+          <t>https://m.place.naver.com/place/13025013</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -2056,55 +2108,59 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>쓰리핏PT 분당정자점</t>
+          <t>라룬리픽스 재활운동PT센터</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>3fits@naver.com</t>
+          <t>crewj99@naver.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0507-1409-3559</t>
+          <t>0507-1327-0804</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 내정로113번길 4 2층 202호, 203-1호</t>
+          <t>경기도 성남시 분당구 느티로 16 젤존타워1 302호 라룬리픽스클리닉</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://3fitpt.com</t>
+          <t>https://www.lalunerefix.com</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wc51p4</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -2113,13 +2169,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>357</v>
+        <v>47</v>
       </c>
       <c r="Q18" t="n">
-        <v>800</v>
+        <v>231</v>
       </c>
       <c r="R18" t="n">
-        <v>1157</v>
+        <v>278</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2128,12 +2184,12 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>1845673431</t>
+          <t>1679722203</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1845673431</t>
+          <t>https://m.place.naver.com/place/1679722203</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -2145,34 +2201,34 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>핏불짐 판교점</t>
+          <t>헬스보이짐&amp;필라걸&amp;골프인 분당정자점</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>fitbullgym@naver.com</t>
+          <t>healthboy90_@naver.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0507-1430-9683</t>
+          <t>0507-1419-2436</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 동판교로 61 자유퍼스트프라자2 3층 304호</t>
+          <t>경기도 성남시 분당구 성남대로331번길 13 7층 701-706호</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://linktr.ee/fitbullgym</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2182,20 +2238,24 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wli4sqi</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr">
         <is>
           <t>X</t>
@@ -2207,13 +2267,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>92</v>
+        <v>457</v>
       </c>
       <c r="Q19" t="n">
-        <v>284</v>
+        <v>756</v>
       </c>
       <c r="R19" t="n">
-        <v>376</v>
+        <v>1213</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2222,12 +2282,12 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>37814535</t>
+          <t>1989525945</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37814535</t>
+          <t>https://m.place.naver.com/place/1989525945</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
@@ -2239,34 +2299,34 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>스포애니 수내점</t>
+          <t>와이짐 PT 분당미금점</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>spoany012@naver.com</t>
+          <t>ygym3018@naver.com</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>031-712-3362</t>
+          <t>0507-1325-3018</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 돌마로 364 현대제일상가 B1층</t>
+          <t>경기도 성남시 분당구 성남대로 165 2층 223호, 224호 와이짐 PT 분당미금점</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://m.spoany.co.kr/branch/branch_detail.html?base_seq=MjE=</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2276,7 +2336,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -2286,10 +2346,14 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wc3fm7</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr">
         <is>
           <t>X</t>
@@ -2301,13 +2365,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>296</v>
+        <v>1079</v>
       </c>
       <c r="Q20" t="n">
-        <v>1550</v>
+        <v>446</v>
       </c>
       <c r="R20" t="n">
-        <v>1846</v>
+        <v>1525</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -2316,12 +2380,12 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>31849989</t>
+          <t>1598086500</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/31849989</t>
+          <t>https://m.place.naver.com/place/1598086500</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
@@ -2338,29 +2402,29 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>머슬짐 PT 분당서현점</t>
+          <t>더바디핏PT 분당야탑2호점</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>musclegym_@naver.com</t>
+          <t>xhakxhqk@naver.com</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0507-1436-9680</t>
+          <t>0507-1302-9149</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 황새울로342번길 19 유성그린빌딩 6층</t>
+          <t>경기도 성남시 분당구 성남대로916번길 7 205호 더바디핏PT</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/musclegym_</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2370,20 +2434,24 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w1vowru</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr">
         <is>
           <t>X</t>
@@ -2395,13 +2463,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>200</v>
+        <v>452</v>
       </c>
       <c r="Q21" t="n">
-        <v>367</v>
+        <v>720</v>
       </c>
       <c r="R21" t="n">
-        <v>567</v>
+        <v>1172</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2410,12 +2478,12 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>1208748555</t>
+          <t>1564371057</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1208748555</t>
+          <t>https://m.place.naver.com/place/1564371057</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
@@ -2432,29 +2500,29 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>올뉴바디 운동맛집PT 야탑점</t>
+          <t>팀제이맥스 피티 서현점</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>allnewbody@naver.com</t>
+          <t>linefit91@naver.com</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0507-1329-3987</t>
+          <t>031-702-8296</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 벌말로 44 401호</t>
+          <t>경기도 성남시 분당구 서현로180번길 13 2층 206호</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/allnewbody</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2464,12 +2532,12 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2489,13 +2557,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>601</v>
+        <v>910</v>
       </c>
       <c r="Q22" t="n">
-        <v>618</v>
+        <v>548</v>
       </c>
       <c r="R22" t="n">
-        <v>1219</v>
+        <v>1458</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -2504,12 +2572,12 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>1203378061</t>
+          <t>1639683746</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1203378061</t>
+          <t>https://m.place.naver.com/place/1639683746</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
@@ -2531,7 +2599,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ksw8591@naver.com</t>
+          <t>wnszh1864@naver.com</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -2548,7 +2616,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ksw8591</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2558,20 +2626,24 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5y773</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr">
         <is>
           <t>X</t>
@@ -2586,10 +2658,10 @@
         <v>142</v>
       </c>
       <c r="Q23" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="R23" t="n">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -2615,34 +2687,38 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>구스짐 PT 판교점</t>
+          <t>버핏그라운드 판교</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>chlgudrn1@naver.com</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
+          <t>butfitground@naver.com</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>partner@butfitseoul.com</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0507-1465-9683</t>
+          <t>0507-1329-4325</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교로 374 스타식스코아2 3층</t>
+          <t>경기도 성남시 분당구 판교역로 136 B3007</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/9s_gym_pangyo/</t>
+          <t>https://pt.butfitground.com/</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2657,18 +2733,22 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w42raj</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -2677,13 +2757,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>164</v>
+        <v>1766</v>
       </c>
       <c r="Q24" t="n">
-        <v>143</v>
+        <v>250</v>
       </c>
       <c r="R24" t="n">
-        <v>307</v>
+        <v>2016</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -2692,12 +2772,12 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>1088776551</t>
+          <t>1136752576</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1088776551</t>
+          <t>https://m.place.naver.com/place/1136752576</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
@@ -2714,29 +2794,29 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>솔리드짐 PT 수내점</t>
+          <t>험블 휘트니스 PT</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>ppapers@naver.com</t>
+          <t>humblefitness@naver.com</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0507-1420-7858</t>
+          <t>031-697-8768</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 황새울로258번길 10-7 403호</t>
+          <t>경기도 성남시 분당구 성남대로331번길 3-3 701호</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/solid_gym1</t>
+          <t>https://blog.naver.com/humblefitness</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2751,7 +2831,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2771,13 +2851,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="Q25" t="n">
-        <v>652</v>
+        <v>1437</v>
       </c>
       <c r="R25" t="n">
-        <v>797</v>
+        <v>1578</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -2786,12 +2866,12 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>1205679892</t>
+          <t>1134171602</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1205679892</t>
+          <t>https://m.place.naver.com/place/1134171602</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
@@ -2803,39 +2883,39 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>리커브 피티 앤 본척척 재활 센터 야탑점</t>
+          <t>스포애니 미금점</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>recurvept@naver.com</t>
+          <t>spoany_14s@naver.com</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0507-1441-8303</t>
+          <t>0507-1474-5855</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로916번길 5 3층 302호</t>
+          <t>경기도 성남시 분당구 돌마로 75 미금프라자 8층</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://m.booking.naver.com/booking/12/bizes/1590839</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2850,10 +2930,14 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4hvwb</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr">
         <is>
           <t>X</t>
@@ -2865,13 +2949,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>13</v>
+        <v>1089</v>
       </c>
       <c r="Q26" t="n">
-        <v>249</v>
+        <v>1827</v>
       </c>
       <c r="R26" t="n">
-        <v>262</v>
+        <v>2916</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -2880,12 +2964,12 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2038767341</t>
+          <t>20065928</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2038767341</t>
+          <t>https://m.place.naver.com/place/20065928</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
@@ -2897,34 +2981,34 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>스포애니 서현역점</t>
+          <t>비아핏</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>spoany22@naver.com</t>
+          <t>viafit@naver.com</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>031-706-8522</t>
+          <t>0507-1379-7507</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 황새울로 324 좋은상호저축은행빌딩 B1층</t>
+          <t>경기도 성남시 분당구 판교대장로7길 15-2 지하1층,지상1층</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/spoany22</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2934,20 +3018,24 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w37pnp4</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr">
         <is>
           <t>X</t>
@@ -2959,13 +3047,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>953</v>
+        <v>26</v>
       </c>
       <c r="Q27" t="n">
-        <v>2039</v>
+        <v>24</v>
       </c>
       <c r="R27" t="n">
-        <v>2992</v>
+        <v>50</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -2974,12 +3062,12 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>13025013</t>
+          <t>1772663783</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13025013</t>
+          <t>https://m.place.naver.com/place/1772663783</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
@@ -2996,34 +3084,34 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>크레이지핏 PT</t>
+          <t>솔리드짐 PT 수내점</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>krazyfit@naver.com</t>
+          <t>ppapers@naver.com</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0507-1488-5883</t>
+          <t>0507-1420-7858</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 정자일로198번길 6-5 3층 크레이지핏</t>
+          <t>경기도 성남시 분당구 황새울로258번길 10-7 403호</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://m.booking.naver.com/booking/13/bizes/205740?theme=place&amp;entry=pll&amp;lang=ko&amp;area=pll</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3033,18 +3121,22 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5tbft</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -3053,13 +3145,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>538</v>
+        <v>145</v>
       </c>
       <c r="Q28" t="n">
-        <v>1438</v>
+        <v>652</v>
       </c>
       <c r="R28" t="n">
-        <v>1976</v>
+        <v>797</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -3068,12 +3160,12 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>1628554288</t>
+          <t>1205679892</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1628554288</t>
+          <t>https://m.place.naver.com/place/1205679892</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
@@ -3085,34 +3177,34 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>헬스보이짐&amp;필라걸&amp;골프인 분당정자점</t>
+          <t>석세스짐&amp;PT 분당무지개마을점</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>healthboy90_@naver.com</t>
+          <t>successgym-b3@naver.com</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>0507-1419-2436</t>
+          <t>0507-1331-7127</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로331번길 13 7층 701-706호</t>
+          <t>경기도 성남시 분당구 미금로 36 브리엘프라자 4층</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/healthboy90_/223799590825</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3122,20 +3214,24 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w45gyo</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr">
         <is>
           <t>X</t>
@@ -3147,13 +3243,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>457</v>
+        <v>104</v>
       </c>
       <c r="Q29" t="n">
-        <v>753</v>
+        <v>336</v>
       </c>
       <c r="R29" t="n">
-        <v>1210</v>
+        <v>440</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -3162,12 +3258,12 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>1989525945</t>
+          <t>1860293712</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1989525945</t>
+          <t>https://m.place.naver.com/place/1860293712</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
@@ -3179,44 +3275,40 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>비전휘트니스 분당점</t>
+          <t>렛미PT&amp;필라테스스튜디오 분당야탑점</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>visionfitness555@naver.com</t>
+          <t>let_me_pt_official@naver.com</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>0507-1439-8755</t>
-        </is>
-      </c>
+      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 돌마로 46 광천프라자 2층</t>
+          <t>경기도 성남시 분당구 야탑로69번길 21 영진다이비스상가 2층 210호</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://litt.ly/visionfitness05</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -3226,10 +3318,14 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w42m9n</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr">
         <is>
           <t>X</t>
@@ -3241,13 +3337,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>2472</v>
+        <v>80</v>
       </c>
       <c r="Q30" t="n">
-        <v>1917</v>
+        <v>49</v>
       </c>
       <c r="R30" t="n">
-        <v>4389</v>
+        <v>129</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -3256,12 +3352,12 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>1765794431</t>
+          <t>1049956503</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1765794431</t>
+          <t>https://m.place.naver.com/place/1049956503</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
@@ -3273,34 +3369,34 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>와이피트니스 헬스&amp;PT 분당야탑점</t>
+          <t>바디밸런스 PT 미금점</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>yfitness02@naver.com</t>
+          <t>xodbs2384@naver.com</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0507-1430-1729</t>
+          <t>0507-1369-2582</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 벌말로40번길 5-1 지하1층</t>
+          <t>경기도 성남시 분당구 미금일로 65 지하1층 바디밸런스</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/yfitness02?igsh=MTR6dDl6cW5sNWNxMg%3D%3D&amp;utm_source=qr</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3310,7 +3406,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -3320,13 +3416,17 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4ik0d</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -3335,13 +3435,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>105</v>
+        <v>153</v>
       </c>
       <c r="Q31" t="n">
-        <v>55</v>
+        <v>840</v>
       </c>
       <c r="R31" t="n">
-        <v>160</v>
+        <v>993</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -3350,12 +3450,12 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>2013735870</t>
+          <t>1400263548</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2013735870</t>
+          <t>https://m.place.naver.com/place/1400263548</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
@@ -3367,39 +3467,39 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>데스런 판교점</t>
+          <t>와이피트니스 헬스&amp;PT 분당야탑점</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>deslun@naver.com</t>
+          <t>yfitness02@naver.com</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0507-1412-6347</t>
+          <t>0507-1430-1729</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로2번길 38</t>
+          <t>경기도 성남시 분당구 벌말로40번길 5-1 지하1층</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>http://www.deslun.co.kr</t>
+          <t>https://www.instagram.com/yfitness02?igsh=MTR6dDl6cW5sNWNxMg%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -3420,7 +3520,7 @@
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -3429,13 +3529,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>22</v>
+        <v>106</v>
       </c>
       <c r="Q32" t="n">
-        <v>415</v>
+        <v>57</v>
       </c>
       <c r="R32" t="n">
-        <v>437</v>
+        <v>163</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -3444,12 +3544,12 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>31469573</t>
+          <t>2013735870</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/31469573</t>
+          <t>https://m.place.naver.com/place/2013735870</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
@@ -3466,29 +3566,29 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>험블 휘트니스 PT</t>
+          <t>제로업PT</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>humblefitness@naver.com</t>
+          <t>linefit91@naver.com</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>031-697-8768</t>
+          <t>031-623-2775</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로331번길 3-3 701호</t>
+          <t>경기도 성남시 분당구 느티로 16 7층</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/humblefitness</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3498,12 +3598,12 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -3523,13 +3623,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>141</v>
+        <v>775</v>
       </c>
       <c r="Q33" t="n">
-        <v>1438</v>
+        <v>729</v>
       </c>
       <c r="R33" t="n">
-        <v>1579</v>
+        <v>1504</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -3538,12 +3638,12 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>1134171602</t>
+          <t>1975822360</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1134171602</t>
+          <t>https://m.place.naver.com/place/1975822360</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
@@ -3555,34 +3655,34 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>석세스짐&amp;PT 분당무지개마을점</t>
+          <t>스포애니 야탑역점</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>successgym-b3@naver.com</t>
+          <t>spoany90@naver.com</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0507-1331-7127</t>
+          <t>0507-1337-9618</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 미금로 36 브리엘프라자 4층</t>
+          <t>경기도 성남시 분당구 성남대로 926 메트로빌딩 8층</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/successgym-b3</t>
+          <t>http://m.spoany.co.kr/branch/branch_detail.html?base_seq=MTA1</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3597,15 +3697,19 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5il7f</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr">
         <is>
           <t>X</t>
@@ -3617,13 +3721,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>103</v>
+        <v>710</v>
       </c>
       <c r="Q34" t="n">
-        <v>336</v>
+        <v>1507</v>
       </c>
       <c r="R34" t="n">
-        <v>439</v>
+        <v>2217</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -3632,12 +3736,12 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>1860293712</t>
+          <t>1115298912</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1860293712</t>
+          <t>https://m.place.naver.com/place/1115298912</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
@@ -3654,29 +3758,29 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>휘트니스클럽S 수내점</t>
+          <t>올뉴바디 운동맛집PT 야탑점</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>fitnessclubs12@naver.com</t>
+          <t>allnewbody@naver.com</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0507-1311-1188</t>
+          <t>0507-1329-3987</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 백현로101번길 11 5층</t>
+          <t>경기도 성남시 분당구 벌말로 44 401호</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://smartstore.naver.com/fitnessclubs12</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3686,7 +3790,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -3696,10 +3800,14 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4mcia</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr">
         <is>
           <t>X</t>
@@ -3711,13 +3819,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>308</v>
+        <v>601</v>
       </c>
       <c r="Q35" t="n">
-        <v>917</v>
+        <v>618</v>
       </c>
       <c r="R35" t="n">
-        <v>1225</v>
+        <v>1219</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -3726,12 +3834,12 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>1228787055</t>
+          <t>1203378061</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1228787055</t>
+          <t>https://m.place.naver.com/place/1203378061</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
@@ -3748,29 +3856,29 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>H GYM PT GT 판교2호점</t>
+          <t>바디센서리 판교점 헬스PT</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>hgym9408@naver.com</t>
+          <t>bodysensory@naver.com</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0507-1353-9408</t>
+          <t>0507-1344-2096</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 운중로 233 302호</t>
+          <t>경기도 성남시 분당구 대왕판교로606번길 41 프라임스퀘어 10층</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://hgym.imweb.me</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3780,20 +3888,24 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4124s</t>
+        </is>
+      </c>
       <c r="N36" t="inlineStr">
         <is>
           <t>X</t>
@@ -3805,13 +3917,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>279</v>
+        <v>46</v>
       </c>
       <c r="Q36" t="n">
-        <v>421</v>
+        <v>292</v>
       </c>
       <c r="R36" t="n">
-        <v>700</v>
+        <v>338</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -3820,12 +3932,12 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>1850894755</t>
+          <t>1786901360</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1850894755</t>
+          <t>https://m.place.naver.com/place/1786901360</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
@@ -3842,29 +3954,29 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>D gym PT 수내역점</t>
+          <t>피쓰리짐 PT</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>hyenggoo1@naver.com</t>
+          <t>p3gym@naver.com</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0507-1438-1374</t>
+          <t>0507-1346-9079</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 황새울로200번길 34 205, 206호</t>
+          <t>경기도 성남시 분당구 정자로 13 월드비터 B1 피쓰리짐</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/dgym_official/?igshid=YmMyMTA2M2Y%3D</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3874,7 +3986,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -3884,10 +3996,14 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w49ipv</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr">
         <is>
           <t>X</t>
@@ -3899,13 +4015,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>156</v>
+        <v>75</v>
       </c>
       <c r="Q37" t="n">
-        <v>367</v>
+        <v>514</v>
       </c>
       <c r="R37" t="n">
-        <v>523</v>
+        <v>589</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -3914,12 +4030,12 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>1234729561</t>
+          <t>1847926774</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1234729561</t>
+          <t>https://m.place.naver.com/place/1847926774</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
@@ -3936,29 +4052,29 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>레조나헬스랩PT 정자역점</t>
+          <t>밀라노짐 수내점</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>resonar_healthlab2@naver.com</t>
+          <t>milanos_1@naver.com</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0507-1415-7374</t>
+          <t>0507-1335-9682</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로331번길 11-15 봉우빌딩 3층 301호 레조나헬스랩</t>
+          <t>경기도 성남시 분당구 내정로166번길 5 원전빌딩 B1층</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/resonar_healthlab</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3968,7 +4084,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -3978,10 +4094,14 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5tvi5</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr">
         <is>
           <t>X</t>
@@ -3993,13 +4113,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>27</v>
+        <v>1141</v>
       </c>
       <c r="Q38" t="n">
-        <v>258</v>
+        <v>696</v>
       </c>
       <c r="R38" t="n">
-        <v>285</v>
+        <v>1837</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -4008,12 +4128,12 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>1265132759</t>
+          <t>1843911670</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1265132759</t>
+          <t>https://m.place.naver.com/place/1843911670</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
@@ -4030,29 +4150,29 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>리조트휘트니스 PT 판교점</t>
+          <t>D gym PT 수내역점</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>resort_5@naver.com</t>
+          <t>hyenggoo1@naver.com</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0507-1438-0677</t>
+          <t>0507-1438-1374</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 운중로 142 판교메디칼타워 6층, 7층</t>
+          <t>경기도 성남시 분당구 황새울로200번길 34 205, 206호</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/resortfitness__pangyo/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4062,7 +4182,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -4072,10 +4192,14 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w40pej</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr">
         <is>
           <t>X</t>
@@ -4087,13 +4211,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>413</v>
+        <v>156</v>
       </c>
       <c r="Q39" t="n">
-        <v>715</v>
+        <v>367</v>
       </c>
       <c r="R39" t="n">
-        <v>1128</v>
+        <v>523</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -4102,12 +4226,12 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>35524502</t>
+          <t>1234729561</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35524502</t>
+          <t>https://m.place.naver.com/place/1234729561</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
@@ -4119,49 +4243,49 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>빌드업피트니스 PT 야탑점</t>
+          <t>H GYM PT GT 판교2호점</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>buildupfitness02@naver.com</t>
+          <t>hgym9408@naver.com</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0507-1329-7003</t>
+          <t>0507-1353-9408</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 장미로 198 B1 빌드업피트니스PT 야탑점</t>
+          <t>경기도 성남시 분당구 운중로 233 302호</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://www.buildupfitness.co.kr</t>
+          <t>https://hgym.imweb.me</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -4181,13 +4305,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>2436</v>
+        <v>279</v>
       </c>
       <c r="Q40" t="n">
-        <v>1018</v>
+        <v>422</v>
       </c>
       <c r="R40" t="n">
-        <v>3454</v>
+        <v>701</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -4196,12 +4320,12 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>1233503897</t>
+          <t>1850894755</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1233503897</t>
+          <t>https://m.place.naver.com/place/1850894755</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
@@ -4218,29 +4342,29 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>써트짐 PT</t>
+          <t>바른몸PT센터</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>certgym@naver.com</t>
+          <t>wlsrkfdl1@naver.com</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0507-1367-7665</t>
+          <t>0507-1337-9711</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 황새울로214번길 8 207호(수내동, MS프라자)</t>
+          <t>경기도 성남시 분당구 백현로101번길 20 3층 301호</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/wlsrkfdl1</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4250,24 +4374,20 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4dpxc</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr">
         <is>
           <t>X</t>
@@ -4279,13 +4399,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>49</v>
+        <v>5</v>
       </c>
       <c r="Q41" t="n">
-        <v>237</v>
+        <v>71</v>
       </c>
       <c r="R41" t="n">
-        <v>286</v>
+        <v>76</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -4294,12 +4414,12 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>1331332549</t>
+          <t>2090651326</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1331332549</t>
+          <t>https://m.place.naver.com/place/2090651326</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
@@ -4316,24 +4436,24 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>팀윤짐 헬스PT</t>
+          <t>헬스보이짐 헬스 PT 판교역점</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>teamyoonsh@naver.com</t>
+          <t>healthboygym78@naver.com</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0507-1363-8855</t>
+          <t>0507-1402-1275</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 황새울로342번길 23 기영프라자 8층</t>
+          <t>경기도 성남시 분당구 대왕판교로606번길 58 지하1층</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -4363,7 +4483,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wc6ysr</t>
+          <t>https://talk.naver.com/ct/wi2wapb</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -4373,17 +4493,17 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P42" t="n">
-        <v>91</v>
+        <v>2543</v>
       </c>
       <c r="Q42" t="n">
-        <v>485</v>
+        <v>323</v>
       </c>
       <c r="R42" t="n">
-        <v>576</v>
+        <v>2866</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -4392,12 +4512,12 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>35523795</t>
+          <t>1835201778</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35523795</t>
+          <t>https://m.place.naver.com/place/1835201778</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
@@ -4414,29 +4534,29 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>쓰리핏 PT 분당미금점</t>
+          <t>레조나헬스랩PT 정자역점</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>3fitpt@naver.com</t>
+          <t>resonar_healthlab@naver.com</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0507-1302-3558</t>
+          <t>0507-1415-7374</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 돌마로 47 6층 607호</t>
+          <t>경기도 성남시 분당구 성남대로331번길 11-15 봉우빌딩 3층 301호 레조나헬스랩</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://3fitpt.com</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -4446,7 +4566,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -4461,7 +4581,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5wfyo</t>
+          <t>https://talk.naver.com/ct/wc1oegu</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -4475,13 +4595,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>427</v>
+        <v>28</v>
       </c>
       <c r="Q43" t="n">
-        <v>954</v>
+        <v>258</v>
       </c>
       <c r="R43" t="n">
-        <v>1381</v>
+        <v>286</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -4490,12 +4610,12 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>1135214262</t>
+          <t>1265132759</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1135214262</t>
+          <t>https://m.place.naver.com/place/1265132759</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
@@ -4512,51 +4632,59 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>그린공간운동센터 PT 분당미금점</t>
+          <t>쓰리핏 PT 분당미금점</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>greenplace2020@naver.com</t>
+          <t>3fitpt@naver.com</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>0507-1302-3558</t>
+        </is>
+      </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 미금일로90번길 32 웰파크 2층 201호</t>
+          <t>경기도 성남시 분당구 돌마로 47 6층 607호</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://3fitpt.com</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5wfyo</t>
+        </is>
+      </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
@@ -4565,13 +4693,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>157</v>
+        <v>427</v>
       </c>
       <c r="Q44" t="n">
-        <v>292</v>
+        <v>954</v>
       </c>
       <c r="R44" t="n">
-        <v>449</v>
+        <v>1381</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -4580,12 +4708,12 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>1364310838</t>
+          <t>1135214262</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1364310838</t>
+          <t>https://m.place.naver.com/place/1135214262</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
@@ -4602,29 +4730,29 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>쓰리핏 헬스&amp;PT 서현점</t>
+          <t>휘트니스클럽S 수내점</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>3fitpt@naver.com</t>
+          <t>fitnessclubs12@naver.com</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0507-1388-2211</t>
+          <t>0507-1311-1188</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 불정로 379 서현프라자 지하1층</t>
+          <t>경기도 성남시 분당구 백현로101번길 11 5층</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://3fitpt.com</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -4634,7 +4762,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -4649,7 +4777,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/we9jvgk</t>
+          <t>https://talk.naver.com/ct/w49zvx</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -4663,13 +4791,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>1030</v>
+        <v>308</v>
       </c>
       <c r="Q45" t="n">
-        <v>929</v>
+        <v>917</v>
       </c>
       <c r="R45" t="n">
-        <v>1959</v>
+        <v>1225</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -4678,12 +4806,12 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>1181952796</t>
+          <t>1228787055</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1181952796</t>
+          <t>https://m.place.naver.com/place/1228787055</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
@@ -4700,24 +4828,24 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>와이투짐 야탑역점</t>
+          <t>짐휴 PT 분당미금점</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>y2gym2@naver.com</t>
+          <t>gym_hue@naver.com</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0507-1352-8844</t>
+          <t>0507-1369-1180</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로 912 B1층</t>
+          <t>경기도 성남시 분당구 돌마로 47 이코노샤르망 5층 509호, 510호</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -4747,7 +4875,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4dbfc</t>
+          <t>https://talk.naver.com/ct/w486ct</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -4761,13 +4889,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>382</v>
+        <v>187</v>
       </c>
       <c r="Q46" t="n">
-        <v>1577</v>
+        <v>247</v>
       </c>
       <c r="R46" t="n">
-        <v>1959</v>
+        <v>434</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -4776,12 +4904,12 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>1930702763</t>
+          <t>1527774793</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1930702763</t>
+          <t>https://m.place.naver.com/place/1527774793</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
@@ -4793,29 +4921,29 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>더바디핏PT 분당야탑2호점</t>
+          <t>헤일로짐24시 헬스 PT 판교점</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>xhakxhqk@naver.com</t>
+          <t>halogym02@naver.com</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>0507-1302-9149</t>
+          <t>0507-1315-8840</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로916번길 7 205호 더바디핏PT</t>
+          <t>경기도 성남시 분당구 대왕판교로 660 유스페이스1 지하1층 127호</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -4845,27 +4973,27 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w1vowru</t>
+          <t>https://talk.naver.com/ct/wcfevb4</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P47" t="n">
-        <v>452</v>
+        <v>663</v>
       </c>
       <c r="Q47" t="n">
-        <v>720</v>
+        <v>934</v>
       </c>
       <c r="R47" t="n">
-        <v>1172</v>
+        <v>1597</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -4874,12 +5002,12 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>1564371057</t>
+          <t>1806695299</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1564371057</t>
+          <t>https://m.place.naver.com/place/1806695299</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
@@ -4994,24 +5122,24 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>피트니스웰시 헬스&amp;PT 분당정자점</t>
+          <t>리커브 피티 앤 본척척 재활 센터 야탑점</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>healthy-pt@naver.com</t>
+          <t>recurvept@naver.com</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>0507-1489-7037</t>
+          <t>0507-1441-8303</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로343번길 12-8 1동 4층</t>
+          <t>경기도 성남시 분당구 성남대로916번길 5 3층 302호</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -5041,7 +5169,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w35x8wg</t>
+          <t>https://talk.naver.com/ct/w4gwff2</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -5055,13 +5183,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>534</v>
+        <v>13</v>
       </c>
       <c r="Q49" t="n">
-        <v>470</v>
+        <v>249</v>
       </c>
       <c r="R49" t="n">
-        <v>1004</v>
+        <v>262</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -5070,12 +5198,12 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>1623406875</t>
+          <t>2038767341</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1623406875</t>
+          <t>https://m.place.naver.com/place/2038767341</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
@@ -5092,24 +5220,24 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>헬스보이짐 헬스 PT 판교역점</t>
+          <t>헬스보이짐&amp;필라걸 수내점</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>healthboygym78@naver.com</t>
+          <t>healthboy40@naver.com</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>0507-1402-1275</t>
+          <t>0507-1380-2239</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 대왕판교로606번길 58 지하1층</t>
+          <t>경기도 성남시 분당구 내정로173번길 49 5층</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -5139,7 +5267,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wi2wapb</t>
+          <t>https://talk.naver.com/ct/w4laa0</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -5153,13 +5281,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>2543</v>
+        <v>967</v>
       </c>
       <c r="Q50" t="n">
-        <v>323</v>
+        <v>737</v>
       </c>
       <c r="R50" t="n">
-        <v>2866</v>
+        <v>1704</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -5168,12 +5296,12 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>1835201778</t>
+          <t>1973151166</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1835201778</t>
+          <t>https://m.place.naver.com/place/1973151166</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
@@ -5185,29 +5313,29 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>브레이브 휘트니스 분당정자점</t>
+          <t>피트니스비엠 분당 서현점</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>bravefitness_jeongja@naver.com</t>
+          <t>ksk2023@naver.com</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>0507-1484-0779</t>
+          <t>0507-1443-0942</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 내정로17번길 2 지하1층</t>
+          <t>경기도 성남시 분당구 돌마로 482 주영빌딩 지하 1층</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -5237,7 +5365,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4lsiz</t>
+          <t>https://talk.naver.com/ct/wf09ma8</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -5251,13 +5379,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1419</v>
+        <v>515</v>
       </c>
       <c r="Q51" t="n">
-        <v>1253</v>
+        <v>684</v>
       </c>
       <c r="R51" t="n">
-        <v>2672</v>
+        <v>1199</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -5266,12 +5394,12 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>1043618213</t>
+          <t>36333115</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1043618213</t>
+          <t>https://m.place.naver.com/place/36333115</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
@@ -5283,34 +5411,34 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>라룬리픽스 재활운동PT센터</t>
+          <t>렛츠핏 야탑점 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>crewj99@naver.com</t>
+          <t>sm8893@naver.com</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>0507-1327-0804</t>
+          <t>0507-1305-0298</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 느티로 16 젤존타워1 302호 라룬리픽스클리닉</t>
+          <t>경기도 성남시 분당구 벌말로 37 4층 1, 2호</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://www.lalunerefix.com</t>
+          <t>https://bmarket.broj.co.kr/groups/413620357</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -5320,12 +5448,12 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -5335,12 +5463,12 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wc51p4</t>
+          <t>https://talk.naver.com/ct/w4w1w0</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
@@ -5349,13 +5477,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>47</v>
+        <v>917</v>
       </c>
       <c r="Q52" t="n">
-        <v>231</v>
+        <v>1289</v>
       </c>
       <c r="R52" t="n">
-        <v>278</v>
+        <v>2206</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -5364,12 +5492,12 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>1679722203</t>
+          <t>1320604673</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1679722203</t>
+          <t>https://m.place.naver.com/place/1320604673</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
@@ -5381,29 +5509,25 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>베러댄 휘트니스 분당야탑점</t>
+          <t>뭉트니스 야탑</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>56zqrwcwsv@naver.com</t>
+          <t>mtns1@naver.com</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>0507-1438-9698</t>
-        </is>
-      </c>
+      <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 야탑로75번길 15 세화빌딩 4층</t>
+          <t>경기도 성남시 분당구 장미로 55 장미마을 지하1층</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -5428,14 +5552,10 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4o2xj</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr">
         <is>
           <t>X</t>
@@ -5447,13 +5567,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>382</v>
+        <v>284</v>
       </c>
       <c r="Q53" t="n">
-        <v>2093</v>
+        <v>1038</v>
       </c>
       <c r="R53" t="n">
-        <v>2475</v>
+        <v>1322</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -5462,12 +5582,12 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>1013682807</t>
+          <t>1657314482</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1013682807</t>
+          <t>https://m.place.naver.com/place/1657314482</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
@@ -5479,25 +5599,29 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>바로선운동센터 판교점</t>
+          <t>카인드짐 휘트니스 헬스&amp;PT 야탑역점</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>coolksh11@naver.com</t>
+          <t>kindgym28@naver.com</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>0507-1361-3615</t>
+        </is>
+      </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 동판교로 61 2층 201호</t>
+          <t>경기도 성남시 분당구 야탑로81번길 10 아미고타워 B1층 카인드짐 휘트니스 헬스&amp;PT 야탑역점</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -5527,7 +5651,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wve1811</t>
+          <t>https://talk.naver.com/ct/wmuqdfb</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -5541,13 +5665,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>22</v>
+        <v>2033</v>
       </c>
       <c r="Q54" t="n">
-        <v>187</v>
+        <v>1586</v>
       </c>
       <c r="R54" t="n">
-        <v>209</v>
+        <v>3619</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -5556,12 +5680,12 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>2015061102</t>
+          <t>36230651</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2015061102</t>
+          <t>https://m.place.naver.com/place/36230651</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
@@ -5578,24 +5702,24 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>피쓰리짐 PT</t>
+          <t>운동생활 PT 분당야탑점</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>p3gym@naver.com</t>
+          <t>yataplife@naver.com</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>0507-1346-9079</t>
+          <t>031-701-1110</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 정자로 13 월드비터 B1 피쓰리짐</t>
+          <t>경기도 성남시 분당구 야탑로69번길 18 2층 202호</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -5625,7 +5749,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w49ipv</t>
+          <t>https://talk.naver.com/ct/w3a2nts</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -5635,17 +5759,17 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P55" t="n">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="Q55" t="n">
-        <v>513</v>
+        <v>549</v>
       </c>
       <c r="R55" t="n">
-        <v>588</v>
+        <v>635</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -5654,12 +5778,12 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>1847926774</t>
+          <t>1275463246</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1847926774</t>
+          <t>https://m.place.naver.com/place/1275463246</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
@@ -5676,24 +5800,24 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>제로업PT</t>
+          <t>머슬짐 PT 분당정자점</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>linefit91@naver.com</t>
+          <t>musclegympt_jeongja@naver.com</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>031-623-2775</t>
+          <t>0507-1405-9679</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 느티로 16 7층</t>
+          <t>경기도 성남시 분당구 성남대로343번길 10-6 동원빌딩 4층</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -5718,10 +5842,14 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M56" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w8j7lk2</t>
+        </is>
+      </c>
       <c r="N56" t="inlineStr">
         <is>
           <t>X</t>
@@ -5729,17 +5857,17 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P56" t="n">
-        <v>772</v>
+        <v>215</v>
       </c>
       <c r="Q56" t="n">
-        <v>723</v>
+        <v>281</v>
       </c>
       <c r="R56" t="n">
-        <v>1495</v>
+        <v>496</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -5748,12 +5876,12 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>1975822360</t>
+          <t>1975809201</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1975822360</t>
+          <t>https://m.place.naver.com/place/1975809201</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
@@ -5770,24 +5898,24 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>비아핏</t>
+          <t>유앤바디PT 분당수내점</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>viafit@naver.com</t>
+          <t>unbody@naver.com</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>0507-1379-7507</t>
+          <t>031-714-4729</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교대장로7길 15-2 지하1층,지상1층</t>
+          <t>경기도 성남시 분당구 백현로101번길 12 세인프라자 402호</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -5817,7 +5945,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w37pnp4</t>
+          <t>https://talk.naver.com/ct/w4b6la</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -5831,13 +5959,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>26</v>
+        <v>118</v>
       </c>
       <c r="Q57" t="n">
-        <v>24</v>
+        <v>168</v>
       </c>
       <c r="R57" t="n">
-        <v>50</v>
+        <v>286</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -5846,12 +5974,12 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>1772663783</t>
+          <t>1853394852</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1772663783</t>
+          <t>https://m.place.naver.com/place/1853394852</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
@@ -5868,24 +5996,20 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>좋은습관PTSTUDIO 판교운중</t>
+          <t>바로선운동센터 판교점</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>goodhabitpg@naver.com</t>
+          <t>coolksh11@naver.com</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>0507-1480-0677</t>
-        </is>
-      </c>
+      <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 운중로 142 6층</t>
+          <t>경기도 성남시 분당구 동판교로 61 2층 201호</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -5915,7 +6039,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5wyz9</t>
+          <t>https://talk.naver.com/ct/wve1811</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -5929,13 +6053,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>63</v>
+        <v>22</v>
       </c>
       <c r="Q58" t="n">
-        <v>29</v>
+        <v>189</v>
       </c>
       <c r="R58" t="n">
-        <v>92</v>
+        <v>211</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -5944,12 +6068,12 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>1070284726</t>
+          <t>2015061102</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1070284726</t>
+          <t>https://m.place.naver.com/place/2015061102</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
@@ -5966,24 +6090,24 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>바른몸PT센터</t>
+          <t>쿼드짐</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>wlsrkfdl1@naver.com</t>
+          <t>quadgym@naver.com</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>0507-1337-9711</t>
+          <t>0507-1303-9415</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 백현로101번길 20 3층 301호</t>
+          <t>경기도 성남시 분당구 정자일로 121 더샵스타파크 상가1층 b-18호</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -6013,7 +6137,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4frie</t>
+          <t>https://talk.naver.com/ct/wc5w2o</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -6027,13 +6151,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>5</v>
+        <v>82</v>
       </c>
       <c r="Q59" t="n">
-        <v>70</v>
+        <v>102</v>
       </c>
       <c r="R59" t="n">
-        <v>75</v>
+        <v>184</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -6042,12 +6166,12 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>2090651326</t>
+          <t>1759307500</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2090651326</t>
+          <t>https://m.place.naver.com/place/1759307500</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
@@ -6064,29 +6188,29 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>피티세븐 퍼스널트레이닝</t>
+          <t>쓰리핏PT 분당정자점</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>body2balance@naver.com</t>
+          <t>3fitpt@naver.com</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>0507-1400-9428</t>
+          <t>0507-1409-3559</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 황새울로132번길 22-1 1층 102호 피티세븐</t>
+          <t>경기도 성남시 분당구 내정로113번길 4 2층 202호, 203-1호</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>http://www.pts7.com</t>
+          <t>https://3fitpt.com</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -6101,7 +6225,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -6111,7 +6235,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4bej5</t>
+          <t>https://talk.naver.com/ct/w5vrph</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -6125,13 +6249,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>302</v>
+        <v>357</v>
       </c>
       <c r="Q60" t="n">
-        <v>290</v>
+        <v>800</v>
       </c>
       <c r="R60" t="n">
-        <v>592</v>
+        <v>1157</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -6140,12 +6264,12 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>13093618</t>
+          <t>1845673431</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13093618</t>
+          <t>https://m.place.naver.com/place/1845673431</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
@@ -6162,24 +6286,24 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>에버그린PT</t>
+          <t>업투 휘트니스 분당판교점</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>evergreen_pt@naver.com</t>
+          <t>uptofitness-@naver.com</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>0507-1314-9993</t>
+          <t>0507-1343-8274</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 불정로376번길 7 3층일부(304호)</t>
+          <t>경기도 성남시 분당구 동판교로 59 6층 601-605호</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -6209,7 +6333,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w9aimuo</t>
+          <t>https://talk.naver.com/ct/w5ijhg</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -6223,13 +6347,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>81</v>
+        <v>621</v>
       </c>
       <c r="Q61" t="n">
-        <v>252</v>
+        <v>291</v>
       </c>
       <c r="R61" t="n">
-        <v>333</v>
+        <v>912</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -6238,12 +6362,12 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>1749890190</t>
+          <t>1928497638</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1749890190</t>
+          <t>https://m.place.naver.com/place/1928497638</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
@@ -6255,29 +6379,29 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>헤일로짐24시 헬스 PT 판교점</t>
+          <t>피트니스웰시 헬스&amp;PT 분당정자점</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>halogym02@naver.com</t>
+          <t>healthy-pt@naver.com</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>0507-1315-8840</t>
+          <t>0507-1489-7037</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 대왕판교로 660 유스페이스1 지하1층 127호</t>
+          <t>경기도 성남시 분당구 성남대로343번길 12-8 1동 4층</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -6307,27 +6431,27 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wcfevb4</t>
+          <t>https://talk.naver.com/ct/w35x8wg</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P62" t="n">
-        <v>663</v>
+        <v>534</v>
       </c>
       <c r="Q62" t="n">
-        <v>933</v>
+        <v>470</v>
       </c>
       <c r="R62" t="n">
-        <v>1596</v>
+        <v>1004</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -6336,12 +6460,12 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>1806695299</t>
+          <t>1623406875</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1806695299</t>
+          <t>https://m.place.naver.com/place/1623406875</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
@@ -6358,24 +6482,24 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>펠릭스짐 분당점</t>
+          <t>비율라이프 바디코치 여성전용 체형필라테스 PT 야탑점</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>felixgym1@naver.com</t>
+          <t>rockrock1256@naver.com</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>0507-1393-3039</t>
+          <t>0507-1445-2430</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 장안로 39 2층 201호</t>
+          <t>경기도 성남시 분당구 야탑로69번길 8 2층 바디코치 야탑점</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -6405,7 +6529,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w43lts</t>
+          <t>https://talk.naver.com/ct/wng7pl1</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -6419,13 +6543,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>24</v>
+        <v>203</v>
       </c>
       <c r="Q63" t="n">
-        <v>45</v>
+        <v>787</v>
       </c>
       <c r="R63" t="n">
-        <v>69</v>
+        <v>990</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -6434,12 +6558,12 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>1125789234</t>
+          <t>1723811790</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1125789234</t>
+          <t>https://m.place.naver.com/place/1723811790</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
@@ -6456,39 +6580,39 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>짐휴 PT 분당미금점</t>
+          <t>피티세븐 퍼스널트레이닝</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>gym_hue@naver.com</t>
+          <t>body2balance@naver.com</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>0507-1369-1180</t>
+          <t>0507-1400-9428</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 돌마로 47 이코노샤르망 5층 509호, 510호</t>
+          <t>경기도 성남시 분당구 황새울로132번길 22-1 1층 102호 피티세븐</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.pts7.com</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -6503,12 +6627,12 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w486ct</t>
+          <t>https://talk.naver.com/ct/w4bej5</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
@@ -6517,13 +6641,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>187</v>
+        <v>302</v>
       </c>
       <c r="Q64" t="n">
-        <v>247</v>
+        <v>290</v>
       </c>
       <c r="R64" t="n">
-        <v>434</v>
+        <v>592</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -6532,12 +6656,12 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>1527774793</t>
+          <t>13093618</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1527774793</t>
+          <t>https://m.place.naver.com/place/13093618</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
@@ -6549,29 +6673,29 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>제이치피트니스 헬스&amp;PT 미금점</t>
+          <t>팀윤짐 헬스PT</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>redgym_migeum@naver.com</t>
+          <t>teamyoonsh@naver.com</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>0507-1332-4462</t>
+          <t>0507-1363-8855</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로 165 지하1층</t>
+          <t>경기도 성남시 분당구 황새울로342번길 23 기영프라자 8층</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -6601,7 +6725,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wzxrxow</t>
+          <t>https://talk.naver.com/ct/wc6ysr</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -6611,17 +6735,17 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P65" t="n">
-        <v>1286</v>
+        <v>91</v>
       </c>
       <c r="Q65" t="n">
-        <v>274</v>
+        <v>485</v>
       </c>
       <c r="R65" t="n">
-        <v>1560</v>
+        <v>576</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -6630,12 +6754,12 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>1109176574</t>
+          <t>35523795</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1109176574</t>
+          <t>https://m.place.naver.com/place/35523795</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
@@ -6652,44 +6776,44 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>바디밸런스 PT 미금점</t>
+          <t>쓰리핏 헬스&amp;PT 서현점</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>xodbs2384@naver.com</t>
+          <t>3fitpt@naver.com</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>0507-1369-2582</t>
+          <t>0507-1388-2211</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 미금일로 65 지하1층 바디밸런스</t>
+          <t>경기도 성남시 분당구 불정로 379 서현프라자 지하1층</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://3fitpt.com</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -6699,12 +6823,12 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4ik0d</t>
+          <t>https://talk.naver.com/ct/we9jvgk</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
@@ -6713,13 +6837,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>153</v>
+        <v>1030</v>
       </c>
       <c r="Q66" t="n">
-        <v>840</v>
+        <v>930</v>
       </c>
       <c r="R66" t="n">
-        <v>993</v>
+        <v>1960</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -6728,12 +6852,12 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>1400263548</t>
+          <t>1181952796</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1400263548</t>
+          <t>https://m.place.naver.com/place/1181952796</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
@@ -6750,24 +6874,24 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>쿼드짐</t>
+          <t>머슬짐 PT 분당서현점</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>quadgym@naver.com</t>
+          <t>musclegym_@naver.com</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>0507-1303-9415</t>
+          <t>0507-1436-9680</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 정자일로 121 더샵스타파크 상가1층 b-18호</t>
+          <t>경기도 성남시 분당구 황새울로342번길 19 유성그린빌딩 6층</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -6797,7 +6921,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wc5w2o</t>
+          <t>https://talk.naver.com/ct/wgye1u3</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -6811,13 +6935,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>82</v>
+        <v>200</v>
       </c>
       <c r="Q67" t="n">
-        <v>102</v>
+        <v>368</v>
       </c>
       <c r="R67" t="n">
-        <v>184</v>
+        <v>568</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -6826,12 +6950,12 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>1759307500</t>
+          <t>1208748555</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1759307500</t>
+          <t>https://m.place.naver.com/place/1208748555</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
@@ -6843,49 +6967,49 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>린바디핏 PT 판교본점</t>
+          <t>빌드업피트니스 PT 야탑점</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>leanbodyfitv2@naver.com</t>
+          <t>b2fitness@naver.com</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>0507-1302-8312</t>
+          <t>0507-1329-7003</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 대왕판교로 670 지하113호</t>
+          <t>경기도 성남시 분당구 장미로 198 B1 빌드업피트니스PT 야탑점</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.buildupfitness.co.kr</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -6895,27 +7019,27 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w3fqoyd</t>
+          <t>https://talk.naver.com/ct/w405jm</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P68" t="n">
-        <v>135</v>
+        <v>2437</v>
       </c>
       <c r="Q68" t="n">
-        <v>108</v>
+        <v>1020</v>
       </c>
       <c r="R68" t="n">
-        <v>243</v>
+        <v>3457</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -6924,12 +7048,12 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>1699238533</t>
+          <t>1233503897</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1699238533</t>
+          <t>https://m.place.naver.com/place/1233503897</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
@@ -6941,44 +7065,44 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>렛츠핏 야탑점 헬스&amp;PT</t>
+          <t>좋은습관PTSTUDIO 판교운중</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>sm8893@naver.com</t>
+          <t>goodhabitpg@naver.com</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>0507-1305-0298</t>
+          <t>0507-1480-0677</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 벌말로 37 4층 1, 2호</t>
+          <t>경기도 성남시 분당구 운중로 142 6층</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>https://bmarket.broj.co.kr/groups/413620357</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -6993,7 +7117,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4w1w0</t>
+          <t>https://talk.naver.com/ct/w5wyz9</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -7007,13 +7131,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>917</v>
+        <v>63</v>
       </c>
       <c r="Q69" t="n">
-        <v>1291</v>
+        <v>30</v>
       </c>
       <c r="R69" t="n">
-        <v>2208</v>
+        <v>93</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -7022,12 +7146,12 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>1320604673</t>
+          <t>1070284726</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1320604673</t>
+          <t>https://m.place.naver.com/place/1070284726</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
@@ -7039,43 +7163,39 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>버핏그라운드 판교</t>
+          <t>데스런 판교점</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>butfitground@naver.com</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>partner@butfitseoul.com</t>
-        </is>
-      </c>
+          <t>deslun@naver.com</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>0507-1329-4325</t>
+          <t>0507-1412-6347</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 136 B3007</t>
+          <t>경기도 성남시 분당구 판교역로2번길 38</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://pt.butfitground.com/</t>
+          <t>http://www.deslun.co.kr</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -7085,7 +7205,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -7095,12 +7215,12 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w42raj</t>
+          <t>https://talk.naver.com/ct/w5ty8f</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
@@ -7109,13 +7229,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>1765</v>
+        <v>22</v>
       </c>
       <c r="Q70" t="n">
-        <v>250</v>
+        <v>432</v>
       </c>
       <c r="R70" t="n">
-        <v>2015</v>
+        <v>454</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -7124,12 +7244,12 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>1136752576</t>
+          <t>31469573</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1136752576</t>
+          <t>https://m.place.naver.com/place/31469573</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
@@ -7141,17 +7261,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>F45 정자</t>
+          <t>그린공간운동센터 PT 분당미금점</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>eunzzori@naver.com</t>
+          <t>greenplace2020@naver.com</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
@@ -7159,12 +7279,12 @@
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 정자일로198번길 24 2층</t>
+          <t>경기도 성남시 분당구 미금일로90번길 32 웰파크 2층 201호</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/f45_jeongja</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -7174,7 +7294,7 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -7199,13 +7319,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>117</v>
+        <v>157</v>
       </c>
       <c r="Q71" t="n">
-        <v>42</v>
+        <v>296</v>
       </c>
       <c r="R71" t="n">
-        <v>159</v>
+        <v>453</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -7214,12 +7334,12 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>1893893702</t>
+          <t>1364310838</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1893893702</t>
+          <t>https://m.place.naver.com/place/1364310838</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
@@ -7231,29 +7351,29 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>와이짐 PT 분당미금점</t>
+          <t>런던피트니스&amp;필라테스 분당이매점</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>ygym3018@naver.com</t>
+          <t>londoner83@naver.com</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>0507-1325-3018</t>
+          <t>0507-1406-9679</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로 165 2층 223호, 224호 와이짐 PT 분당미금점</t>
+          <t>경기도 성남시 분당구 성남대로779번길 13 오성프라자빌딩 5층</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -7283,7 +7403,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wc3fm7</t>
+          <t>https://talk.naver.com/ct/w4pnpp</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -7297,13 +7417,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>1077</v>
+        <v>1341</v>
       </c>
       <c r="Q72" t="n">
-        <v>446</v>
+        <v>473</v>
       </c>
       <c r="R72" t="n">
-        <v>1523</v>
+        <v>1814</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -7312,12 +7432,12 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>1598086500</t>
+          <t>13530251</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1598086500</t>
+          <t>https://m.place.naver.com/place/13530251</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
@@ -7329,34 +7449,34 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>스포애니 야탑역점</t>
+          <t>리조트휘트니스 PT 판교점</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>spoany90@naver.com</t>
+          <t>resort_5@naver.com</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>0507-1337-9618</t>
+          <t>0507-1438-0677</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로 926 메트로빌딩 8층</t>
+          <t>경기도 성남시 분당구 운중로 142 판교메디칼타워 6층, 7층</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>http://m.spoany.co.kr/branch/branch_detail.html?base_seq=MTA1</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -7366,7 +7486,7 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -7381,7 +7501,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5il7f</t>
+          <t>https://talk.naver.com/ct/w5ixpk</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -7395,13 +7515,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>708</v>
+        <v>413</v>
       </c>
       <c r="Q73" t="n">
-        <v>1504</v>
+        <v>715</v>
       </c>
       <c r="R73" t="n">
-        <v>2212</v>
+        <v>1128</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
@@ -7410,12 +7530,12 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>1115298912</t>
+          <t>35524502</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1115298912</t>
+          <t>https://m.place.naver.com/place/35524502</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
@@ -7432,29 +7552,29 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>런던피트니스&amp;필라테스 분당이매점</t>
+          <t>스포애니 수내점</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>londoner83@naver.com</t>
+          <t>spoany012@naver.com</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>0507-1406-9679</t>
+          <t>031-712-3362</t>
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로779번길 13 오성프라자빌딩 5층</t>
+          <t>경기도 성남시 분당구 돌마로 364 현대제일상가 B1층</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://m.spoany.co.kr/branch/branch_detail.html?base_seq=MjE=</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -7464,7 +7584,7 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -7479,7 +7599,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4pnpp</t>
+          <t>https://talk.naver.com/ct/w40bmg</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -7493,13 +7613,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>1340</v>
+        <v>296</v>
       </c>
       <c r="Q74" t="n">
-        <v>473</v>
+        <v>1548</v>
       </c>
       <c r="R74" t="n">
-        <v>1813</v>
+        <v>1844</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -7508,12 +7628,12 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>13530251</t>
+          <t>31849989</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13530251</t>
+          <t>https://m.place.naver.com/place/31849989</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
@@ -7530,24 +7650,24 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>팀제이맥스 피티 서현점</t>
+          <t>와이투짐 야탑역점</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>linefit91@naver.com</t>
+          <t>y2gym2@naver.com</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>031-702-8296</t>
+          <t>0507-1352-8844</t>
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 서현로180번길 13 2층 206호</t>
+          <t>경기도 성남시 분당구 성남대로 912 B1층</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -7572,10 +7692,14 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M75" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4dbfc</t>
+        </is>
+      </c>
       <c r="N75" t="inlineStr">
         <is>
           <t>X</t>
@@ -7587,13 +7711,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>910</v>
+        <v>385</v>
       </c>
       <c r="Q75" t="n">
-        <v>548</v>
+        <v>1577</v>
       </c>
       <c r="R75" t="n">
-        <v>1458</v>
+        <v>1962</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
@@ -7602,12 +7726,12 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>1639683746</t>
+          <t>1930702763</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1639683746</t>
+          <t>https://m.place.naver.com/place/1930702763</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
@@ -7624,29 +7748,29 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>핏슈브 야탑이매점</t>
+          <t>베러댄 휘트니스 분당야탑점</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>9_bonhyuk@naver.com</t>
+          <t>56zqrwcwsv@naver.com</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>0507-1486-9921</t>
+          <t>0507-1438-9698</t>
         </is>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교로 475 4층 404호</t>
+          <t>경기도 성남시 분당구 야탑로75번길 15 세화빌딩 4층</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/9_bonhyuk</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -7656,20 +7780,24 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M76" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4o2xj</t>
+        </is>
+      </c>
       <c r="N76" t="inlineStr">
         <is>
           <t>X</t>
@@ -7681,13 +7809,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>17</v>
+        <v>382</v>
       </c>
       <c r="Q76" t="n">
-        <v>163</v>
+        <v>2093</v>
       </c>
       <c r="R76" t="n">
-        <v>180</v>
+        <v>2475</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -7696,12 +7824,12 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>2032296152</t>
+          <t>1013682807</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2032296152</t>
+          <t>https://m.place.naver.com/place/1013682807</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">

--- a/naver-place-crawler/results_health/분당_PT.xlsx
+++ b/naver-place-crawler/results_health/분당_PT.xlsx
@@ -417,17 +417,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="49" customWidth="1" min="7" max="7"/>
-    <col width="45" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -658,29 +658,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>레조나헬스랩PT 정자역점</t>
+          <t>레조나헬스랩PT 서판교점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>resonar_healthlab2@naver.com</t>
+          <t>resonar_healthlab@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1415-7374</t>
+          <t>0507-1411-1104</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로331번길 11-15 봉우빌딩 3층 301호 레조나헬스랩</t>
+          <t>경기도 성남시 분당구 판교공원로2길 9 4층 레조나헬스랩PT 서판교점</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/resonar_healthlab</t>
+          <t>https://blog.naver.com/resonar_healthlab</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -715,14 +715,14 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="Q3" t="n">
+        <v>202</v>
+      </c>
+      <c r="R3" t="n">
         <v>258</v>
       </c>
-      <c r="R3" t="n">
-        <v>286</v>
-      </c>
       <c r="S3" t="inlineStr">
         <is>
           <t>X</t>
@@ -730,12 +730,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1265132759</t>
+          <t>1644348689</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1265132759</t>
+          <t>https://m.place.naver.com/place/1644348689</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -812,10 +812,10 @@
         <v>562</v>
       </c>
       <c r="Q4" t="n">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="R4" t="n">
-        <v>1640</v>
+        <v>1641</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -839,36 +839,20 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>험블 휘트니스 PT</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>humblefitness@naver.com</t>
-        </is>
-      </c>
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>031-697-8768</t>
-        </is>
-      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로331번길 3-3 701호</t>
+          <t>주소</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/humblefitness</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -878,12 +862,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -899,17 +883,17 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>141</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>1437</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1578</v>
+        <v>0</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,12 +902,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1134171602</t>
+          <t>7544685</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1134171602</t>
+          <t>https://m.place.naver.com/place/7544685</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -996,12 +980,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>7544685</t>
+          <t>2600001</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/7544685</t>
+          <t>https://m.place.naver.com/place/2600001</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1074,12 +1058,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2600001</t>
+          <t>7167332</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2600001</t>
+          <t>https://m.place.naver.com/place/7167332</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1152,12 +1136,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>7167332</t>
+          <t>7536599</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/7167332</t>
+          <t>https://m.place.naver.com/place/7536599</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1230,12 +1214,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>7536599</t>
+          <t>7540516</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/7536599</t>
+          <t>https://m.place.naver.com/place/7540516</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1308,12 +1292,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>7540516</t>
+          <t>2400001</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/7540516</t>
+          <t>https://m.place.naver.com/place/2400001</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1386,93 +1370,15 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2400001</t>
+          <t>7619261</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2400001</t>
+          <t>https://m.place.naver.com/place/7619261</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr"/>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>주소</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>7619261</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/7619261</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
         <is>
           <t>2026-04-29</t>
         </is>
